--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -164,7 +164,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -234,7 +234,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -374,7 +374,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN_SEASON</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -17139,7 +17139,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -17769,7 +17769,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -18469,7 +18469,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -18959,7 +18959,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -19309,7 +19309,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -20219,7 +20219,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -20639,7 +20639,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -20709,7 +20709,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -20989,7 +20989,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -21269,7 +21269,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -21549,7 +21549,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -21689,7 +21689,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -22459,7 +22459,7 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t xml:space="preserve">REACH</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -22599,7 +22599,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -22739,7 +22739,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -23229,7 +23229,7 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -23439,7 +23439,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIR</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t xml:space="preserve">FADE</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -23579,7 +23579,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t xml:space="preserve">IN_SEASON</t>
+          <t xml:space="preserve">MODEL REVIEW</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t xml:space="preserve">cam bynum boasts an impressive track record in international games heading into sunday s matchup with the commanders at london s tottenham hotspur stadium the colts safety has made three previous international appearances two in london with the vikings and another in germany last year for indianapolis and has come away 3 0 with 17 tackles two passes defensed an interception and a forced fumble what has contributed to such a boost overseas for the 28 year old he believes a lot of it boils down to the atmosphere whenever i m having fun and feeling loose that s when i play the best football bynum told mike yam on thursday s episode of the nfl report so when i m overseas playing in front of diff</t>
+          <t xml:space="preserve">Will Marcus Mariota lead Washington to a second straight win in relief of Jayden Daniels? | cam bynum boasts an impressive track record in international games heading into sunday s matchup with the commanders at london s tottenham hotspur stadium the colts safety has made three previous international appearances two in london with the vikings and another in germany last year for indianapolis and has come away 3 0 with 17 tackles two passes defensed an interception and a forced fumble what has contributed to such a boost overseas for the 28 year old he believes a lot of it boils down to the atmosphere whenever i m having fun and feeling loose that s when i play the best football bynum told mi</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">first round quarterback who even the stingiest draft graders pegged as a day 2 selection teams use fifth rounders and later as qb dart throws all the time the giants lack of 2027 picks is of concern but they can deal with that later with jaxson dart out for the regular season after knee surgery the giants needed to make some sort of move jameis winston has shown he can hold the fort for a spell but it s a serious question if harbaugh will give the boom or bust passer enough | j j mccarthy is ready for a fresh start 34 i didn 39 t anticipate it 34 the 23 year old quarterback said friday four days after the new york giants acquired him from the minnesota vikings for a 2027 fifth round pick 34 </t>
+          <t xml:space="preserve">first round quarterback who even the stingiest draft graders pegged as a day 2 selection teams use fifth rounders and later as qb dart throws all the time the giants lack of 2027 picks is of concern but they can deal with that later with jaxson dart out for the regular season after knee surgery the giants needed to make some sort of move jameis winston has shown he can hold the fort for a spell but it s a serious question if harbaugh will give the boom or bust passer enough | Transaction: Placed QB Jaxson Dart on injured reserve. | Placed QB Jaxson Dart on injured reserve. | transaction placed qb jaxson dart on injured reserve placed qb jaxson dart on injured reserve</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t xml:space="preserve">the patriots don 39 t have any answers mack hollins who picked up a taunting penalty while his team trailed 28 3 is playing like the team 39 s best wide receiver which is great for hollins but not a great sign for the team romeo doubs isn 39 t playing like a 17 million player kyle williams was blanketed in coverage on what ended up as maye 39 s second interception and the offense remains totally unable to run the ball so if it 39 s going to get better it</t>
+          <t xml:space="preserve">Patriots preach patience when it comes to receiver WR Romeo Doubs' modest start | patriots preach patience when it comes to receiver wr romeo doubs modest start after the patriots signed him to a four year deal in march doubs is searching for his footing in the offense entering week 4</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">cam bynum boasts an impressive track record in international games heading into sunday s matchup with the commanders at london s tottenham hotspur stadium the colts safety has made three previous international appearances two in london with the vikings and another in germany last year for indianapolis and has come away 3 0 with 17 tackles two passes defensed an interception and a forced fumble what has contributed to such a boost overseas for the 28 year old he believes a lot of it boils down to the atmosphere whenever i m having fun and feeling loose that s when i play the best football bynum told mike yam on thursday s episode of the nfl report so when i m overseas playing in front of diff</t>
+          <t xml:space="preserve">Will Marcus Mariota lead Washington to a second straight win in relief of Jayden Daniels? | cam bynum boasts an impressive track record in international games heading into sunday s matchup with the commanders at london s tottenham hotspur stadium the colts safety has made three previous international appearances two in london with the vikings and another in germany last year for indianapolis and has come away 3 0 with 17 tackles two passes defensed an interception and a forced fumble what has contributed to such a boost overseas for the 28 year old he believes a lot of it boils down to the atmosphere whenever i m having fun and feeling loose that s when i play the best football bynum told mi</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t xml:space="preserve">the patriots don 39 t have any answers mack hollins who picked up a taunting penalty while his team trailed 28 3 is playing like the team 39 s best wide receiver which is great for hollins but not a great sign for the team romeo doubs isn 39 t playing like a 17 million player kyle williams was blanketed in coverage on what ended up as maye 39 s second interception and the offense remains totally unable to run the ball so if it 39 s going to get better it</t>
+          <t xml:space="preserve">Patriots preach patience when it comes to receiver WR Romeo Doubs' modest start | patriots preach patience when it comes to receiver wr romeo doubs modest start after the patriots signed him to a four year deal in march doubs is searching for his footing in the offense entering week 4</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t xml:space="preserve">first round quarterback who even the stingiest draft graders pegged as a day 2 selection teams use fifth rounders and later as qb dart throws all the time the giants lack of 2027 picks is of concern but they can deal with that later with jaxson dart out for the regular season after knee surgery the giants needed to make some sort of move jameis winston has shown he can hold the fort for a spell but it s a serious question if harbaugh will give the boom or bust passer enough | j j mccarthy is ready for a fresh start 34 i didn 39 t anticipate it 34 the 23 year old quarterback said friday four days after the new york giants acquired him from the minnesota vikings for a 2027 fifth round pick 34 </t>
+          <t xml:space="preserve">first round quarterback who even the stingiest draft graders pegged as a day 2 selection teams use fifth rounders and later as qb dart throws all the time the giants lack of 2027 picks is of concern but they can deal with that later with jaxson dart out for the regular season after knee surgery the giants needed to make some sort of move jameis winston has shown he can hold the fort for a spell but it s a serious question if harbaugh will give the boom or bust passer enough | Transaction: Placed QB Jaxson Dart on injured reserve. | Placed QB Jaxson Dart on injured reserve. | transaction placed qb jaxson dart on injured reserve placed qb jaxson dart on injured reserve</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -309,7 +309,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Donald out, Puka Nacua to play in Rams' game vs. | Rams defensive tackle Aaron Donald will not play against the Eagles as he deals with back soreness, while wide receiver Puka Nacua will return from a hip injury after missing the past two games. | aaron donald out puka nacua to play in rams game vs eagles rams defensive tackle aaron donald will not play against the eagles as he deals with back soreness while wide receiver puka nacua will return from a hip injury after missing the past two games | n count if there were offseason trophies to hand out los angeles would likely be first in line still for as loaded as this roster is it s imperative the rams stiff arm distractions and keep th</t>
+          <t xml:space="preserve">Sources: Rams don't intend to limit Puka Nacua's workload | The Rams do not intend to limit Puka Nacua's workload Sunday against the Eagles, sources told ESPN. | sources rams don t intend to limit puka nacua s workload the rams do not intend to limit puka nacua s workload sunday against the eagles sources told espn | Aaron Donald out, Puka Nacua to play in Rams' game vs. | Rams defensive tackle Aaron Donald will not play against the Eagles as he deals with back soreness, while wide receiver Puka Nacua will return from a hip injury after missing the past two games. | aaron donald out puka nacua to play in rams game vs eagles rams defensive tackle aaron donald will not play against the eagles </t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Can Terry McLaurin overcome a tough Eagles defense? | nfl fantasy 2026 start x27 em sit x27 em wide receivers for week 1 which jaguars receiver is primed to star in the opener can terry mclaurin overcome a tough eagles defense check out all of matt okada x27 s fantasy wr starts and sits for week 1 of the 2026 nfl season</t>
+          <t xml:space="preserve">Commanders WR Terry McLaurin inactive after Friday injury | Commanders wide receiver Terry McLaurin will not play against the Colts because of a hamstring injury suffered in practice Friday. | commanders wr terry mclaurin inactive after friday injury commanders wide receiver terry mclaurin will not play against the colts because of a hamstring injury suffered in practice friday</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t xml:space="preserve">en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of camp tight end sam laporta is the name to watch on offense but the defense has greater concerns brian branch suffered a late season achilles tear and while the lions haven t put a hard timeline on the safety s recovery it will be a surprise if he s good to go to ope</t>
+          <t xml:space="preserve">Sources: Sam LaPorta, Lions break off contract talks | The Lions and star tight end Sam LaPorta have broken off contract talks, sources told NFL Network, after attempting to work out a long-term deal for the first few weeks of the season. | sources sam laporta lions break off contract talks the lions and star tight end sam laporta have broken off contract talks sources told nfl network after attempting to work out a long term deal for the first few weeks of the season | en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of </t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Synchronized to Washington across team, Overall, Regression, Environment and Step 7; old unsigned/landing-spot wording removed.</t>
+          <t xml:space="preserve">com nfl player id 4361577 dyami brown dyami brown a and a href https www espn com nfl player id 4567156 treylon burks trey burks a can fill mclaurin s x receiver role as can a href https www espn com nfl player id 2976212 stefon diggs stefon diggs a who has started at the flanker position opposite mclaurin diggs leads washington with 13 receptions and three touchdown catches while mclaurin has a team best 141 receiving yards p p washington does return tight end a href https www espn com nfl</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Carolina Panthers are monitoring starting wide receiver Jalen Coker's quadriceps injury ahead of their Week 4 "Sunday Night Football" matchup with the Detroit Lions. | panthers in wait and see mode with leading receiver coker quad the carolina panthers are monitoring starting wide receiver jalen coker s quadriceps injury ahead of their week 4 sunday night football matchup with the detroit lions</t>
+          <t xml:space="preserve">Wide receiver Jalen Coker is also unlikely to play against the Lions, sources told ESPN. | panthers put legette on ir coker also likely out vs lions the panthers have placed 2024 first round pick xavier legette on injured reserve ahead of sunday s prime time matchup against the lions wide receiver jalen coker is also unlikely to play against the lions sources told espn</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t xml:space="preserve">see him go through the workouts the commanders leave for london on tuesday evening and are scheduled to practice wednesday through friday before hosting the colts at tottenham hotspur stadium on sunday at 9 30 a m et linebacker frankie luvu groin and tight end chig okonkwo hamstring will also return to practice in some form this week after missing the last two games because of injury the status of right guard sam cosmi concussion and safety nick cross internal injury however will be decided later after each player undergoes further testing</t>
+          <t xml:space="preserve">who has started at the flanker position opposite mclaurin diggs leads washington with 13 receptions and three touchdown catches while mclaurin has a team best 141 receiving yards p p washington does return tight end a href https www espn com nfl player id 4360635 chig okonkwo chig okonkwo a who missed the past two games with a hamstring injury p</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buccaneers QB Baker Mayfield out at least 3 weeks with thumb injury; | Jalon Daniels will start at quarterback for the Buccaneers with Baker Mayfield sidelined by his thumb injury. | for the first time in four years the buccaneers will be starting someone other than baker mayfield at quarterback in week 4 bucs head coach todd bowles told reporters on monday that mayfield will miss a minimum of three weeks after dislocating his right thumb in the team s 23 16 loss to the vikings on sunday tampa bay will start undrafted rookie jalon daniels in mayfield s place when it hosts the 1 2 packers on oct 4 daniels went 0 for 3 passing with a game ending interception after coming on in relief of mayfie</t>
+          <t xml:space="preserve">Sources: Baker Mayfield return hinges on when QB can grip football | Baker Mayfield is expected to miss anywhere from three to six weeks, sources told ESPN, depending on how quickly the Bucs QB can grip the football. | p a data clubhouse guid 13e8b157 a75a ff24 ae91 fa3d52ddf204 href https www espn com nfl team name tb tampa bay buccaneers tampa bay buccaneers a head coach todd bowles says a data player guid 5bb4376a d089 e3e4 e49a 44f1d709a012 href https www espn com nfl player id 3052587 baker mayfield baker mayfield a will miss at least three weeks due to his dislocated right thumb but that is the minimum p p there is a flipside scenario as well p p sources told espn that mayfield is deal</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Donald out, Puka Nacua to play in Rams' game vs. | Rams defensive tackle Aaron Donald will not play against the Eagles as he deals with back soreness, while wide receiver Puka Nacua will return from a hip injury after missing the past two games. | aaron donald out puka nacua to play in rams game vs eagles rams defensive tackle aaron donald will not play against the eagles as he deals with back soreness while wide receiver puka nacua will return from a hip injury after missing the past two games | n count if there were offseason trophies to hand out los angeles would likely be first in line still for as loaded as this roster is it s imperative the rams stiff arm distractions and keep th</t>
+          <t xml:space="preserve">Sources: Rams don't intend to limit Puka Nacua's workload | The Rams do not intend to limit Puka Nacua's workload Sunday against the Eagles, sources told ESPN. | sources rams don t intend to limit puka nacua s workload the rams do not intend to limit puka nacua s workload sunday against the eagles sources told espn | Aaron Donald out, Puka Nacua to play in Rams' game vs. | Rams defensive tackle Aaron Donald will not play against the Eagles as he deals with back soreness, while wide receiver Puka Nacua will return from a hip injury after missing the past two games. | aaron donald out puka nacua to play in rams game vs eagles rams defensive tackle aaron donald will not play against the eagles </t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Can Terry McLaurin overcome a tough Eagles defense? | nfl fantasy 2026 start x27 em sit x27 em wide receivers for week 1 which jaguars receiver is primed to star in the opener can terry mclaurin overcome a tough eagles defense check out all of matt okada x27 s fantasy wr starts and sits for week 1 of the 2026 nfl season</t>
+          <t xml:space="preserve">Commanders WR Terry McLaurin inactive after Friday injury | Commanders wide receiver Terry McLaurin will not play against the Colts because of a hamstring injury suffered in practice Friday. | commanders wr terry mclaurin inactive after friday injury commanders wide receiver terry mclaurin will not play against the colts because of a hamstring injury suffered in practice friday</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t xml:space="preserve">en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of camp tight end sam laporta is the name to watch on offense but the defense has greater concerns brian branch suffered a late season achilles tear and while the lions haven t put a hard timeline on the safety s recovery it will be a surprise if he s good to go to ope</t>
+          <t xml:space="preserve">Sources: Sam LaPorta, Lions break off contract talks | The Lions and star tight end Sam LaPorta have broken off contract talks, sources told NFL Network, after attempting to work out a long-term deal for the first few weeks of the season. | sources sam laporta lions break off contract talks the lions and star tight end sam laporta have broken off contract talks sources told nfl network after attempting to work out a long term deal for the first few weeks of the season | en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of </t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Carolina Panthers are monitoring starting wide receiver Jalen Coker's quadriceps injury ahead of their Week 4 "Sunday Night Football" matchup with the Detroit Lions. | panthers in wait and see mode with leading receiver coker quad the carolina panthers are monitoring starting wide receiver jalen coker s quadriceps injury ahead of their week 4 sunday night football matchup with the detroit lions</t>
+          <t xml:space="preserve">Wide receiver Jalen Coker is also unlikely to play against the Lions, sources told ESPN. | panthers put legette on ir coker also likely out vs lions the panthers have placed 2024 first round pick xavier legette on injured reserve ahead of sunday s prime time matchup against the lions wide receiver jalen coker is also unlikely to play against the lions sources told espn</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t xml:space="preserve">see him go through the workouts the commanders leave for london on tuesday evening and are scheduled to practice wednesday through friday before hosting the colts at tottenham hotspur stadium on sunday at 9 30 a m et linebacker frankie luvu groin and tight end chig okonkwo hamstring will also return to practice in some form this week after missing the last two games because of injury the status of right guard sam cosmi concussion and safety nick cross internal injury however will be decided later after each player undergoes further testing</t>
+          <t xml:space="preserve">who has started at the flanker position opposite mclaurin diggs leads washington with 13 receptions and three touchdown catches while mclaurin has a team best 141 receiving yards p p washington does return tight end a href https www espn com nfl player id 4360635 chig okonkwo chig okonkwo a who missed the past two games with a hamstring injury p</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Synchronized to Washington across team, Overall, Regression, Environment and Step 7; old unsigned/landing-spot wording removed.</t>
+          <t xml:space="preserve">com nfl player id 4361577 dyami brown dyami brown a and a href https www espn com nfl player id 4567156 treylon burks trey burks a can fill mclaurin s x receiver role as can a href https www espn com nfl player id 2976212 stefon diggs stefon diggs a who has started at the flanker position opposite mclaurin diggs leads washington with 13 receptions and three touchdown catches while mclaurin has a team best 141 receiving yards p p washington does return tight end a href https www espn com nfl</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buccaneers QB Baker Mayfield out at least 3 weeks with thumb injury; | Jalon Daniels will start at quarterback for the Buccaneers with Baker Mayfield sidelined by his thumb injury. | for the first time in four years the buccaneers will be starting someone other than baker mayfield at quarterback in week 4 bucs head coach todd bowles told reporters on monday that mayfield will miss a minimum of three weeks after dislocating his right thumb in the team s 23 16 loss to the vikings on sunday tampa bay will start undrafted rookie jalon daniels in mayfield s place when it hosts the 1 2 packers on oct 4 daniels went 0 for 3 passing with a game ending interception after coming on in relief of mayfie</t>
+          <t xml:space="preserve">Sources: Baker Mayfield return hinges on when QB can grip football | Baker Mayfield is expected to miss anywhere from three to six weeks, sources told ESPN, depending on how quickly the Bucs QB can grip the football. | p a data clubhouse guid 13e8b157 a75a ff24 ae91 fa3d52ddf204 href https www espn com nfl team name tb tampa bay buccaneers tampa bay buccaneers a head coach todd bowles says a data player guid 5bb4376a d089 e3e4 e49a 44f1d709a012 href https www espn com nfl player id 3052587 baker mayfield baker mayfield a will miss at least three weeks due to his dislocated right thumb but that is the minimum p p there is a flipside scenario as well p p sources told espn that mayfield is deal</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -309,7 +309,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sources: Rams don't intend to limit Puka Nacua's workload | The Rams do not intend to limit Puka Nacua's workload Sunday against the Eagles, sources told ESPN. | sources rams don t intend to limit puka nacua s workload the rams do not intend to limit puka nacua s workload sunday against the eagles sources told espn | Aaron Donald out, Puka Nacua to play in Rams' game vs. | Rams defensive tackle Aaron Donald will not play against the Eagles as he deals with back soreness, while wide receiver Puka Nacua will return from a hip injury after missing the past two games. | aaron donald out puka nacua to play in rams game vs eagles rams defensive tackle aaron donald will not play against the eagles </t>
+          <t xml:space="preserve">n count if there were offseason trophies to hand out los angeles would likely be first in line still for as loaded as this roster is it s imperative the rams stiff arm distractions and keep their heads from getting too high into the clouds puka nacua has a looming potentially top of the market extension and he needs to continue working on himself after a stint in rehab l a already caused a stir when it shocked the nfl world by drafting quarterback ty simpson with the 13th overall pick</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -379,7 +379,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bengals WR Ja'Marr Chase suffers concussion in loss to Jaguars | Bengals wide receiver Ja'Marr Chase has been ruled out against the Jaguars with a concussion.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">p with 28 seconds left in the fourth quarter sunday afternoon a data clubhouse guid 38248455 3da4 84e4 8090 98b5cc38ffdc href https www espn com nfl team name bal baltimore ravens baltimore ravens a cornerback a data player guid 0fa246a4 1068 3be1 9d79 42844aeedbce href https www espn com nfl player id 4601278 nate wiggins nate wiggins a batted away a pass from a data clubhouse guid b0fc8fb7 9dbe e574 9008 6f0ee7c6b234 href https www espn com nfl team name dal dallas cowboys dallas cowboys a wide receiver a data player guid 2994891b 8927 33cb 6999 e809560d0545 href https www espn com nfl player id 4241389 ceedee lamb ceedee lamb a near the goal line making what many thought was a clutch defe</t>
+          <t xml:space="preserve">CeeDee Lamb's 17 catches, go-ahead score power Cowboys | CeeDee Lamb returned to Houston and caught 17 passes for 189 yards, including the game-winning, 12-yard touchdown with 40 seconds to go, as a large number of family members watched from the stands. | ceedee lamb s 17 catches go ahead score power cowboys ceedee lamb returned to houston and caught 17 passes for 189 yards including the game winning 12 yard touchdown with 40 seconds to go as a large number of family members watched from the stands | Can CeeDee Lamb finish as the overall WR1 in fantasy this season? | can ceedee lamb finish as the overall wr1 in fantasy this season can ceedee lamb finish as the overall wr1 in fantasy this se</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikings WR Justin Jefferson (ankle) out Sunday against Dolphins | Justin Jefferson (ankle) has been ruled out of the team&amp;#x27;s upcoming game against the Dolphins, head coach Kevin O&amp;#x27;Connell said Friday. | vikings wr justin jefferson ankle out sunday against dolphins the minnesota vikings will be without their two time all pro wide receiver on sunday justin jefferson ankle has been ruled out of the team x27 s upcoming game against the dolphins head coach kevin o x27 connell said friday | Vikings' Justin Jefferson out vs. | Vikings WR Justin Jefferson won't play against the Dolphins because of a sprained left ankle, but coach Kevin O'Connell is hopeful he can return in Week 5 vs. | viki</t>
+          <t xml:space="preserve">Vikings WR Justin Jefferson (ankle) out Sunday against Dolphins | Justin Jefferson (ankle) has been ruled out of the team&amp;#x27;s upcoming game against the Dolphins, head coach Kevin O&amp;#x27;Connell said Friday. | vikings wr justin jefferson ankle out sunday against dolphins the minnesota vikings will be without their two time all pro wide receiver on sunday justin jefferson ankle has been ruled out of the team x27 s upcoming game against the dolphins head coach kevin o x27 connell said friday</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">very big down for us in these first two games and today we were not good enough and i wasn 39 t good enough fourth down i wasn 39 t good enough as well 34 the first half included encouraging signs for the running game saquon barkley returned from last week 39 s stinger and rushed for 73 yards before halftime his second most in the first half since the start of last season but he finished with 82 yards that shows you how the second half went 34 we know the</t>
+          <t xml:space="preserve">Eagles RB Saquon Barkley leaves loss with hamstring injury | Eagles running back Saquon Barkley has been ruled out of Sunday's game against the Rams with a hamstring injury. | eagles rb saquon barkley leaves loss with hamstring injury eagles running back saquon barkley has been ruled out of sunday s game against the rams with a hamstring injury</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who unseats Josh Allen at the top of Nick Shook&amp;#x27;s QB rankings? | nfl and the longest of herbert s career the chargers failed to capitalize on five forced turnovers on sunday as the offense struggled to punch in scores going 1 of 4 in the red zone as the defense gave l a repeated chances to thwart josh allen s bills herbert and co never found a groove after three weeks it s been a rusty operation and herbert doesn t appear comfortable in the scheme yet the interior of the offensive line getting repeatedly blasted doesn t help also the pass catching corps</t>
+          <t xml:space="preserve">is still turning the ball over at a discomforting rate the running game remains an issue the pass rush hasn 39 t been anything special but with their quarterback finally playing like the guy who can carry a team and with their defense slowing down josh allen and the bills like no other unit had everything is on the table for the patriots of course a lot of that is because of maye the disasters of his first three weeks were pretty much gone with allen on the opposing sideline maye certainly</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">— Carolina Panthers coach Dave Canales was a little worried after Bryce Young and Tetairoa McMillan had some issues connecting on passes in practice. | young mcmillan connect for 2 tds to lead panthers past lions 32 26 carolina panthers coach dave canales was a little worried after bryce young and tetairoa mcmillan had some issues connecting on passes in practice</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">jacksonville fla jacksonville jaguars cornerback travis hunter ended up with the football from his first nfl interception hunter spun the ball in celebration and then danced in the end zone after picking off a pass from new england patriots quarterback drake maye late in the second quarter sunday a patriots ball boy picked it up and refused to give it to jaguars veteran defensive end josh hines allen even screaming hey you can t touch me when hines allen tried to grab the ball the ball boy appeared to try to push hines allen away nfl players are allowed to keep game balls although they get charged a hefty price by the league hines allen tried to knock this one out of the ball boy s hands bef</t>
+          <t xml:space="preserve">Drake Maye rebounds as Patriots hand Bills first defeat | Drake Maye snapped out of his early-season slide with a clutch performance as the New England Patriots upset the Buffalo Bills 29-26 at Highmark Stadium in a result that coach Mike Vrabel highlighted as critical for the defending AFC champions. | drake maye rebounds as patriots hand bills first defeat drake maye snapped out of his early season slide with a clutch performance as the new england patriots upset the buffalo bills 29 26 at highmark stadium in a result that coach mike vrabel highlighted as critical for the defending afc champions | Why Adam Rank is still rolling with Drake Maye as a fantasy starter for now | why adam rank i</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NFL news roundup: Lamar Jackson (back) limited at practice; | nfl news roundup lamar jackson back limited at practice falcons extend dt gervon dexter nfl com keeps you up to date with all of the latest league news from around the nfl visit nfl com x27 s transaction hub for a daily breakdown</t>
+          <t xml:space="preserve">Ravens quarterback Lamar Jackson exits win over Titans early due to ankle injury | Baltimore Ravens quarterback Lamar Jackson suffered an ankle injury in the first half of Sunday&amp;#x27;s 24-18 win over the Tennessee Titans and did not return. | baltimore ravens quarterback lamar jackson suffered an ankle injury in the first half of sunday s 24 18 win over the tennessee titans and did not return jackson appeared to suffer the injury when he was sacked on one of the final plays of the first half lamar s dealing with a little bit of an ankle head coach jesse minter told reporters after the game don t know enough about it right now we ll have to see where that s at nfl network insider ian rapopor</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Michael Florio: Fantasy managers shouldn't think twice about starting Javonte Williams | michael florio fantasy managers shouldn t think twice about starting javonte williams michael florio fantasy managers shouldn t think twice about starting javonte williams</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sources: Sam LaPorta, Lions break off contract talks | The Lions and star tight end Sam LaPorta have broken off contract talks, sources told NFL Network, after attempting to work out a long-term deal for the first few weeks of the season. | sources sam laporta lions break off contract talks the lions and star tight end sam laporta have broken off contract talks sources told nfl network after attempting to work out a long term deal for the first few weeks of the season | en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of </t>
+          <t xml:space="preserve">en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of camp tight end sam laporta is the name to watch on offense but the defense has greater concerns brian branch suffered a late season achilles tear and while the lions haven t put a hard timeline on the safety s recovery it will be a surprise if he s good to go to ope</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Will Marcus Mariota lead Washington to a second straight win in relief of Jayden Daniels? | cam bynum boasts an impressive track record in international games heading into sunday s matchup with the commanders at london s tottenham hotspur stadium the colts safety has made three previous international appearances two in london with the vikings and another in germany last year for indianapolis and has come away 3 0 with 17 tackles two passes defensed an interception and a forced fumble what has contributed to such a boost overseas for the 28 year old he believes a lot of it boils down to the atmosphere whenever i m having fun and feeling loose that s when i play the best football bynum told mi</t>
+          <t xml:space="preserve">ruled out at halftime mariota was playing in place of washington starter jayden daniels who has been sidelined the last two weeks after dislocating his left elbow on sept 20 commanders coach dan quinn said after the loss that mariota is feared to have aggravated an mcl injury that sidelined him in 2022 the vet qb will undergo testing to confirm the nature of the injury mariota suffered the knee injury on a third down sack midway through the first quarter when indy defensive end laiatu latu landed on the veteran qb s right leg mariota went to the locker room and was replaced by kaliakmanis with washington leading 6 0 this was kaliakmanis first nfl regular season game appearance the 23 year ol</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t xml:space="preserve">— The Carolina Panthers found themselves in a precarious position last November, facing a red hot Matthew Stafford without three defensive starters, including standout cornerback Jaycee Horn.</t>
+          <t xml:space="preserve">Matthew Stafford says Nacua 'played like Puka' in return for Rams</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placed WR Jayden Reed on injured reserve. | transaction signed g kevin zeitler placed wr jayden reed on injured reserve signed dt david blay and wr coleman owen to the practice squad signed g kevin zeitler placed wr jayden reed on injured reserve signed dt david blay and wr coleman owen to the practice squad | Placed WR Jayden Reed on injured reserve.</t>
+          <t xml:space="preserve">39 s such an impact player on our defense 34 if cooper 39 s injury ends his season it will be the third such hit to green bay 39 s starting lineup this season right tackle zach bako bewele torn patellar tendon and wide receiver jayden reed neck are both out for the year too the packers will now rely on special teams captain and linebacker isaiah mcduffie to fill cooper 39 s spot in the starting lineup alongside veteran zaire franklin lafleur was visibly frustrated during his postgame press conference likely | Placed WR Jayden Reed on injured reserve. | transaction signed g kevin zeitler placed wr jayden reed on injured reserve signed dt david blay and wr coleman owen to the practice squad si</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seahawks place RB Jadarian Price (chest) on injured reserve | Running back Jadarian Price&amp;#x27;s slow start to his rookie season just hit another snag. | seahawks place rb jadarian price chest on injured reserve running back jadarian price x27 s slow start to his rookie season just hit another snag the seahawks are placing price on injured reserve due to a chest injury espn x27 s adam schefter reported saturday | Seahawks place RB Jadarian Price (chest) on IR | The Seattle Seahawks are placing starting running back Jadarian Price on injured reserve, the team announced Saturday. | seahawks place rb jadarian price chest on ir the seattle seahawks are placing starting running back jadarian pric</t>
+          <t xml:space="preserve">Seahawks place RB Jadarian Price (chest) on injured reserve | Running back Jadarian Price&amp;#x27;s slow start to his rookie season just hit another snag. | seahawks place rb jadarian price chest on injured reserve running back jadarian price x27 s slow start to his rookie season just hit another snag the seahawks are placing price on injured reserve due to a chest injury espn x27 s adam schefter reported saturday</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sources: Baker Mayfield return hinges on when QB can grip football | Baker Mayfield is expected to miss anywhere from three to six weeks, sources told ESPN, depending on how quickly the Bucs QB can grip the football. | p a data clubhouse guid 13e8b157 a75a ff24 ae91 fa3d52ddf204 href https www espn com nfl team name tb tampa bay buccaneers tampa bay buccaneers a head coach todd bowles says a data player guid 5bb4376a d089 e3e4 e49a 44f1d709a012 href https www espn com nfl player id 3052587 baker mayfield baker mayfield a will miss at least three weeks due to his dislocated right thumb but that is the minimum p p there is a flipside scenario as well p p sources told espn that mayfield is deal</t>
+          <t xml:space="preserve">Sources: Baker Mayfield return hinges on when QB can grip football | Baker Mayfield is expected to miss anywhere from three to six weeks, sources told ESPN, depending on how quickly the Buccaneers quarterback can grip the football. | sources baker mayfield return hinges on when qb can grip football baker mayfield is expected to miss anywhere from three to six weeks sources told espn depending on how quickly the buccaneers quarterback can grip the football</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t xml:space="preserve">an offense playing as if it s in quicksand the shuffled offensive line is a mess it can t pass block or open holes the running game is crippling bad with rbs who miss holes rarely break tackles or try to bounce everything outside and jordan love has been an inaccurate disaster whether the pressure has gotten to the qb who entered his fourth year as a starter or he s simply panicking love s play has been dismal through three games love was pressured 23 times 41 8 pressure rate in</t>
+          <t xml:space="preserve">midway through the third quarter cooper fell to the ground shortly after the snap without being touched and reached for the back of his lower left leg he was visibly distraught on the field and later carted off 34 i 39 m sick 34 quarterback jordan love said 34 he 39 s such an impact player on our defense 34 if cooper 39 s injury ends his season it will be the third such hit to green bay 39 s starting lineup this season right tackle zach bako bewele torn patellar tendon</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t xml:space="preserve">defensive end a href http www espn com college sports football recruiting player id 259636 zion elee zion elee a the no 2 player in the class in 2025 in state quarterback a href http www espn com college sports football recruiting player id 254623 malik washington malik washington a was one of seven four star sc next 300 signees and immediately won the starting job p p maryland s top graded recruit in 2027 sc next 300 four star wide receiver myles mcafee comes from the same archbishop spalding high school</t>
+          <t xml:space="preserve">maryland 2 3 at no 5 ohio state 4 1 oct 10 at 4 15 p m edt opening line ohio state by 34 5 against the spread ohio state 4 1 maryland 2 3 how to watch btn em key stats em ohio state offense overall 514 4 yards per game 7th in fbs passing 357 yards per game 2nd rushing 157 4 yards per game 71st scoring 42 2 points per game 14th ohio state defense overall 267 yards per game 18th in fbs passing 168 yards per game 24th rushing 99 yards per game 25th scoring 12 6 points per game 8th maryland offense overall 424 yards per game 48th in fbs passing 277 2 yards per game 30th rushing 146 8 yards per game 88th scoring 30 4 points per game 69th maryland defense overall 335 yards per game 56th in fbs pas</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bengals WR Ja'Marr Chase suffers concussion in loss to Jaguars | Bengals wide receiver Ja'Marr Chase has been ruled out against the Jaguars with a concussion.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sources: Rams don't intend to limit Puka Nacua's workload | The Rams do not intend to limit Puka Nacua's workload Sunday against the Eagles, sources told ESPN. | sources rams don t intend to limit puka nacua s workload the rams do not intend to limit puka nacua s workload sunday against the eagles sources told espn | Aaron Donald out, Puka Nacua to play in Rams' game vs. | Rams defensive tackle Aaron Donald will not play against the Eagles as he deals with back soreness, while wide receiver Puka Nacua will return from a hip injury after missing the past two games. | aaron donald out puka nacua to play in rams game vs eagles rams defensive tackle aaron donald will not play against the eagles </t>
+          <t xml:space="preserve">n count if there were offseason trophies to hand out los angeles would likely be first in line still for as loaded as this roster is it s imperative the rams stiff arm distractions and keep their heads from getting too high into the clouds puka nacua has a looming potentially top of the market extension and he needs to continue working on himself after a stint in rehab l a already caused a stir when it shocked the nfl world by drafting quarterback ty simpson with the 13th overall pick</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">p with 28 seconds left in the fourth quarter sunday afternoon a data clubhouse guid 38248455 3da4 84e4 8090 98b5cc38ffdc href https www espn com nfl team name bal baltimore ravens baltimore ravens a cornerback a data player guid 0fa246a4 1068 3be1 9d79 42844aeedbce href https www espn com nfl player id 4601278 nate wiggins nate wiggins a batted away a pass from a data clubhouse guid b0fc8fb7 9dbe e574 9008 6f0ee7c6b234 href https www espn com nfl team name dal dallas cowboys dallas cowboys a wide receiver a data player guid 2994891b 8927 33cb 6999 e809560d0545 href https www espn com nfl player id 4241389 ceedee lamb ceedee lamb a near the goal line making what many thought was a clutch defe</t>
+          <t xml:space="preserve">CeeDee Lamb's 17 catches, go-ahead score power Cowboys | CeeDee Lamb returned to Houston and caught 17 passes for 189 yards, including the game-winning, 12-yard touchdown with 40 seconds to go, as a large number of family members watched from the stands. | ceedee lamb s 17 catches go ahead score power cowboys ceedee lamb returned to houston and caught 17 passes for 189 yards including the game winning 12 yard touchdown with 40 seconds to go as a large number of family members watched from the stands | Can CeeDee Lamb finish as the overall WR1 in fantasy this season? | can ceedee lamb finish as the overall wr1 in fantasy this season can ceedee lamb finish as the overall wr1 in fantasy this se</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikings WR Justin Jefferson (ankle) out Sunday against Dolphins | Justin Jefferson (ankle) has been ruled out of the team&amp;#x27;s upcoming game against the Dolphins, head coach Kevin O&amp;#x27;Connell said Friday. | vikings wr justin jefferson ankle out sunday against dolphins the minnesota vikings will be without their two time all pro wide receiver on sunday justin jefferson ankle has been ruled out of the team x27 s upcoming game against the dolphins head coach kevin o x27 connell said friday | Vikings' Justin Jefferson out vs. | Vikings WR Justin Jefferson won't play against the Dolphins because of a sprained left ankle, but coach Kevin O'Connell is hopeful he can return in Week 5 vs. | viki</t>
+          <t xml:space="preserve">Vikings WR Justin Jefferson (ankle) out Sunday against Dolphins | Justin Jefferson (ankle) has been ruled out of the team&amp;#x27;s upcoming game against the Dolphins, head coach Kevin O&amp;#x27;Connell said Friday. | vikings wr justin jefferson ankle out sunday against dolphins the minnesota vikings will be without their two time all pro wide receiver on sunday justin jefferson ankle has been ruled out of the team x27 s upcoming game against the dolphins head coach kevin o x27 connell said friday</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">very big down for us in these first two games and today we were not good enough and i wasn 39 t good enough fourth down i wasn 39 t good enough as well 34 the first half included encouraging signs for the running game saquon barkley returned from last week 39 s stinger and rushed for 73 yards before halftime his second most in the first half since the start of last season but he finished with 82 yards that shows you how the second half went 34 we know the</t>
+          <t xml:space="preserve">Eagles RB Saquon Barkley leaves loss with hamstring injury | Eagles running back Saquon Barkley has been ruled out of Sunday's game against the Rams with a hamstring injury. | eagles rb saquon barkley leaves loss with hamstring injury eagles running back saquon barkley has been ruled out of sunday s game against the rams with a hamstring injury</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">— Carolina Panthers coach Dave Canales was a little worried after Bryce Young and Tetairoa McMillan had some issues connecting on passes in practice. | young mcmillan connect for 2 tds to lead panthers past lions 32 26 carolina panthers coach dave canales was a little worried after bryce young and tetairoa mcmillan had some issues connecting on passes in practice</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who unseats Josh Allen at the top of Nick Shook&amp;#x27;s QB rankings? | nfl and the longest of herbert s career the chargers failed to capitalize on five forced turnovers on sunday as the offense struggled to punch in scores going 1 of 4 in the red zone as the defense gave l a repeated chances to thwart josh allen s bills herbert and co never found a groove after three weeks it s been a rusty operation and herbert doesn t appear comfortable in the scheme yet the interior of the offensive line getting repeatedly blasted doesn t help also the pass catching corps</t>
+          <t xml:space="preserve">is still turning the ball over at a discomforting rate the running game remains an issue the pass rush hasn 39 t been anything special but with their quarterback finally playing like the guy who can carry a team and with their defense slowing down josh allen and the bills like no other unit had everything is on the table for the patriots of course a lot of that is because of maye the disasters of his first three weeks were pretty much gone with allen on the opposing sideline maye certainly</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">NFL news roundup: Lamar Jackson (back) limited at practice; | nfl news roundup lamar jackson back limited at practice falcons extend dt gervon dexter nfl com keeps you up to date with all of the latest league news from around the nfl visit nfl com x27 s transaction hub for a daily breakdown</t>
+          <t xml:space="preserve">Ravens quarterback Lamar Jackson exits win over Titans early due to ankle injury | Baltimore Ravens quarterback Lamar Jackson suffered an ankle injury in the first half of Sunday&amp;#x27;s 24-18 win over the Tennessee Titans and did not return. | baltimore ravens quarterback lamar jackson suffered an ankle injury in the first half of sunday s 24 18 win over the tennessee titans and did not return jackson appeared to suffer the injury when he was sacked on one of the final plays of the first half lamar s dealing with a little bit of an ankle head coach jesse minter told reporters after the game don t know enough about it right now we ll have to see where that s at nfl network insider ian rapopor</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">jacksonville fla jacksonville jaguars cornerback travis hunter ended up with the football from his first nfl interception hunter spun the ball in celebration and then danced in the end zone after picking off a pass from new england patriots quarterback drake maye late in the second quarter sunday a patriots ball boy picked it up and refused to give it to jaguars veteran defensive end josh hines allen even screaming hey you can t touch me when hines allen tried to grab the ball the ball boy appeared to try to push hines allen away nfl players are allowed to keep game balls although they get charged a hefty price by the league hines allen tried to knock this one out of the ball boy s hands bef</t>
+          <t xml:space="preserve">Drake Maye rebounds as Patriots hand Bills first defeat | Drake Maye snapped out of his early-season slide with a clutch performance as the New England Patriots upset the Buffalo Bills 29-26 at Highmark Stadium in a result that coach Mike Vrabel highlighted as critical for the defending AFC champions. | drake maye rebounds as patriots hand bills first defeat drake maye snapped out of his early season slide with a clutch performance as the new england patriots upset the buffalo bills 29 26 at highmark stadium in a result that coach mike vrabel highlighted as critical for the defending afc champions | Why Adam Rank is still rolling with Drake Maye as a fantasy starter for now | why adam rank i</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Michael Florio: Fantasy managers shouldn't think twice about starting Javonte Williams | michael florio fantasy managers shouldn t think twice about starting javonte williams michael florio fantasy managers shouldn t think twice about starting javonte williams</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sources: Sam LaPorta, Lions break off contract talks | The Lions and star tight end Sam LaPorta have broken off contract talks, sources told NFL Network, after attempting to work out a long-term deal for the first few weeks of the season. | sources sam laporta lions break off contract talks the lions and star tight end sam laporta have broken off contract talks sources told nfl network after attempting to work out a long term deal for the first few weeks of the season | en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of </t>
+          <t xml:space="preserve">en in front of extensions in recent years so everyone expects a top of the rb market contract for gibbs to come barreling down the pike 3 can detroit return to health detroit has significant injuries to track at the onset of camp tight end sam laporta is the name to watch on offense but the defense has greater concerns brian branch suffered a late season achilles tear and while the lions haven t put a hard timeline on the safety s recovery it will be a surprise if he s good to go to ope</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Will Marcus Mariota lead Washington to a second straight win in relief of Jayden Daniels? | cam bynum boasts an impressive track record in international games heading into sunday s matchup with the commanders at london s tottenham hotspur stadium the colts safety has made three previous international appearances two in london with the vikings and another in germany last year for indianapolis and has come away 3 0 with 17 tackles two passes defensed an interception and a forced fumble what has contributed to such a boost overseas for the 28 year old he believes a lot of it boils down to the atmosphere whenever i m having fun and feeling loose that s when i play the best football bynum told mi</t>
+          <t xml:space="preserve">ruled out at halftime mariota was playing in place of washington starter jayden daniels who has been sidelined the last two weeks after dislocating his left elbow on sept 20 commanders coach dan quinn said after the loss that mariota is feared to have aggravated an mcl injury that sidelined him in 2022 the vet qb will undergo testing to confirm the nature of the injury mariota suffered the knee injury on a third down sack midway through the first quarter when indy defensive end laiatu latu landed on the veteran qb s right leg mariota went to the locker room and was replaced by kaliakmanis with washington leading 6 0 this was kaliakmanis first nfl regular season game appearance the 23 year ol</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placed WR Jayden Reed on injured reserve. | transaction signed g kevin zeitler placed wr jayden reed on injured reserve signed dt david blay and wr coleman owen to the practice squad signed g kevin zeitler placed wr jayden reed on injured reserve signed dt david blay and wr coleman owen to the practice squad | Placed WR Jayden Reed on injured reserve.</t>
+          <t xml:space="preserve">39 s such an impact player on our defense 34 if cooper 39 s injury ends his season it will be the third such hit to green bay 39 s starting lineup this season right tackle zach bako bewele torn patellar tendon and wide receiver jayden reed neck are both out for the year too the packers will now rely on special teams captain and linebacker isaiah mcduffie to fill cooper 39 s spot in the starting lineup alongside veteran zaire franklin lafleur was visibly frustrated during his postgame press conference likely | Placed WR Jayden Reed on injured reserve. | transaction signed g kevin zeitler placed wr jayden reed on injured reserve signed dt david blay and wr coleman owen to the practice squad si</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seahawks place RB Jadarian Price (chest) on injured reserve | Running back Jadarian Price&amp;#x27;s slow start to his rookie season just hit another snag. | seahawks place rb jadarian price chest on injured reserve running back jadarian price x27 s slow start to his rookie season just hit another snag the seahawks are placing price on injured reserve due to a chest injury espn x27 s adam schefter reported saturday | Seahawks place RB Jadarian Price (chest) on IR | The Seattle Seahawks are placing starting running back Jadarian Price on injured reserve, the team announced Saturday. | seahawks place rb jadarian price chest on ir the seattle seahawks are placing starting running back jadarian pric</t>
+          <t xml:space="preserve">Seahawks place RB Jadarian Price (chest) on injured reserve | Running back Jadarian Price&amp;#x27;s slow start to his rookie season just hit another snag. | seahawks place rb jadarian price chest on injured reserve running back jadarian price x27 s slow start to his rookie season just hit another snag the seahawks are placing price on injured reserve due to a chest injury espn x27 s adam schefter reported saturday</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t xml:space="preserve">defensive end a href http www espn com college sports football recruiting player id 259636 zion elee zion elee a the no 2 player in the class in 2025 in state quarterback a href http www espn com college sports football recruiting player id 254623 malik washington malik washington a was one of seven four star sc next 300 signees and immediately won the starting job p p maryland s top graded recruit in 2027 sc next 300 four star wide receiver myles mcafee comes from the same archbishop spalding high school</t>
+          <t xml:space="preserve">maryland 2 3 at no 5 ohio state 4 1 oct 10 at 4 15 p m edt opening line ohio state by 34 5 against the spread ohio state 4 1 maryland 2 3 how to watch btn em key stats em ohio state offense overall 514 4 yards per game 7th in fbs passing 357 yards per game 2nd rushing 157 4 yards per game 71st scoring 42 2 points per game 14th ohio state defense overall 267 yards per game 18th in fbs passing 168 yards per game 24th rushing 99 yards per game 25th scoring 12 6 points per game 8th maryland offense overall 424 yards per game 48th in fbs passing 277 2 yards per game 30th rushing 146 8 yards per game 88th scoring 30 4 points per game 69th maryland defense overall 335 yards per game 56th in fbs pas</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t xml:space="preserve">— The Carolina Panthers found themselves in a precarious position last November, facing a red hot Matthew Stafford without three defensive starters, including standout cornerback Jaycee Horn.</t>
+          <t xml:space="preserve">Matthew Stafford says Nacua 'played like Puka' in return for Rams</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sources: Baker Mayfield return hinges on when QB can grip football | Baker Mayfield is expected to miss anywhere from three to six weeks, sources told ESPN, depending on how quickly the Bucs QB can grip the football. | p a data clubhouse guid 13e8b157 a75a ff24 ae91 fa3d52ddf204 href https www espn com nfl team name tb tampa bay buccaneers tampa bay buccaneers a head coach todd bowles says a data player guid 5bb4376a d089 e3e4 e49a 44f1d709a012 href https www espn com nfl player id 3052587 baker mayfield baker mayfield a will miss at least three weeks due to his dislocated right thumb but that is the minimum p p there is a flipside scenario as well p p sources told espn that mayfield is deal</t>
+          <t xml:space="preserve">Sources: Baker Mayfield return hinges on when QB can grip football | Baker Mayfield is expected to miss anywhere from three to six weeks, sources told ESPN, depending on how quickly the Buccaneers quarterback can grip the football. | sources baker mayfield return hinges on when qb can grip football baker mayfield is expected to miss anywhere from three to six weeks sources told espn depending on how quickly the buccaneers quarterback can grip the football</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t xml:space="preserve">an offense playing as if it s in quicksand the shuffled offensive line is a mess it can t pass block or open holes the running game is crippling bad with rbs who miss holes rarely break tackles or try to bounce everything outside and jordan love has been an inaccurate disaster whether the pressure has gotten to the qb who entered his fourth year as a starter or he s simply panicking love s play has been dismal through three games love was pressured 23 times 41 8 pressure rate in</t>
+          <t xml:space="preserve">midway through the third quarter cooper fell to the ground shortly after the snap without being touched and reached for the back of his lower left leg he was visibly distraught on the field and later carted off 34 i 39 m sick 34 quarterback jordan love said 34 he 39 s such an impact player on our defense 34 if cooper 39 s injury ends his season it will be the third such hit to green bay 39 s starting lineup this season right tackle zach bako bewele torn patellar tendon</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -13971,17 +13971,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes II</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D2">
@@ -13997,8 +13997,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G2">
-        <v>9.29568</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -14006,33 +14008,33 @@
         </is>
       </c>
       <c r="I2">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D3">
@@ -14048,8 +14050,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G3">
-        <v>8.91456</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -14057,28 +14061,28 @@
         </is>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14099,37 +14103,39 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G4">
-        <v>8.74848</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">EXPECTED_INACTIVE</t>
         </is>
       </c>
       <c r="I4">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14150,8 +14156,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G5">
-        <v>8.66688</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -14159,33 +14167,33 @@
         </is>
       </c>
       <c r="I5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D6">
@@ -14201,8 +14209,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G6">
-        <v>8.6592</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -14210,33 +14220,33 @@
         </is>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D7">
@@ -14252,8 +14262,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G7">
-        <v>8.65152</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -14261,23 +14273,23 @@
         </is>
       </c>
       <c r="I7">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14287,7 +14299,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D8">
@@ -14303,8 +14315,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G8">
-        <v>8.63146</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -14312,11 +14326,11 @@
         </is>
       </c>
       <c r="I8">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14328,17 +14342,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D9">
@@ -14354,8 +14368,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G9">
-        <v>8.63136</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14363,23 +14379,23 @@
         </is>
       </c>
       <c r="I9">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14389,7 +14405,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D10">
@@ -14405,8 +14421,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G10">
-        <v>8.56896</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14414,11 +14432,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14430,7 +14448,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -14440,7 +14458,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D11">
@@ -14456,20 +14474,22 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G11">
-        <v>8.325</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXPECTED_ACTIVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I11">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14481,17 +14501,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D12">
@@ -14507,32 +14527,34 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G12">
-        <v>8.25696</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">EXPECTED_INACTIVE</t>
         </is>
       </c>
       <c r="I12">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -14558,20 +14580,22 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G13">
-        <v>8.19264</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">EXPECTED_ACTIVE</t>
         </is>
       </c>
       <c r="I13">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14583,17 +14607,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Patrick Mahomes II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D14">
@@ -14609,8 +14633,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G14">
-        <v>8.0064</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -14618,33 +14644,33 @@
         </is>
       </c>
       <c r="I14">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">QB13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D15">
@@ -14660,8 +14686,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G15">
-        <v>7.944</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14669,28 +14697,28 @@
         </is>
       </c>
       <c r="I15">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14711,8 +14739,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G16">
-        <v>7.87104</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -14720,28 +14750,28 @@
         </is>
       </c>
       <c r="I16">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14762,8 +14792,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G17">
-        <v>7.79362</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -14771,33 +14803,33 @@
         </is>
       </c>
       <c r="I17">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D18">
@@ -14813,42 +14845,44 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G18">
-        <v>7.7328</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">EXPECTED_INACTIVE</t>
         </is>
       </c>
       <c r="I18">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D19">
@@ -14864,8 +14898,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G19">
-        <v>7.54176</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -14873,28 +14909,28 @@
         </is>
       </c>
       <c r="I19">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14915,8 +14951,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G20">
-        <v>7.47936</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -14924,11 +14962,11 @@
         </is>
       </c>
       <c r="I20">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14940,17 +14978,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D21">
@@ -14966,8 +15004,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G21">
-        <v>7.1856</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -14975,23 +15015,23 @@
         </is>
       </c>
       <c r="I21">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -15001,7 +15041,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D22">
@@ -15017,8 +15057,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G22">
-        <v>7.18176</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -15026,11 +15068,11 @@
         </is>
       </c>
       <c r="I22">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -15042,12 +15084,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15068,8 +15110,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G23">
-        <v>7.15776</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -15077,33 +15121,33 @@
         </is>
       </c>
       <c r="I23">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D24">
@@ -15119,42 +15163,44 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G24">
-        <v>7.15536</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">EXPECTED_INACTIVE</t>
         </is>
       </c>
       <c r="I24">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D25">
@@ -15170,42 +15216,44 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G25">
-        <v>6.85894</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXPECTED_INACTIVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I25">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D26">
@@ -15221,37 +15269,39 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G26">
-        <v>6.2085</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXPECTED_INACTIVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I26">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15272,42 +15322,44 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G27">
-        <v>5.9925</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXPECTED_INACTIVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I27">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D28">
@@ -15323,8 +15375,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G28">
-        <v>5.84321</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -15332,11 +15386,11 @@
         </is>
       </c>
       <c r="I28">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -15348,12 +15402,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15374,8 +15428,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G29">
-        <v>5.31</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -15383,11 +15439,11 @@
         </is>
       </c>
       <c r="I29">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -15399,17 +15455,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D30">
@@ -15425,42 +15481,44 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G30">
-        <v>5.0025</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXPECTED_INACTIVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I30">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D31">
@@ -15476,8 +15534,10 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G31">
-        <v>4.94625</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -15485,11 +15545,11 @@
         </is>
       </c>
       <c r="I31">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -13971,17 +13971,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahmyr Gibbs</t>
+          <t xml:space="preserve">Josh Allen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D2">
@@ -13992,11 +13992,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="G2">
-        <v>9.884</v>
+        <v>9.815</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -14004,11 +14004,11 @@
         </is>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -14020,7 +14020,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D3">
@@ -14041,11 +14041,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="G3">
-        <v>9.815</v>
+        <v>9.268</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -14053,11 +14053,11 @@
         </is>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -14069,17 +14069,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bijan Robinson</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D4">
@@ -14090,11 +14090,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="G4">
-        <v>9.645</v>
+        <v>9.256</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -14102,11 +14102,11 @@
         </is>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -14118,17 +14118,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amon-Ra St. Brown</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D5">
@@ -14139,11 +14139,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="G5">
-        <v>9.605</v>
+        <v>9.022</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -14151,11 +14151,11 @@
         </is>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -14167,17 +14167,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D6">
@@ -14188,11 +14188,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="G6">
-        <v>9.386</v>
+        <v>8.834</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -14200,11 +14200,11 @@
         </is>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>182</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -14216,17 +14216,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian McCaffrey</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D7">
@@ -14237,23 +14237,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="G7">
-        <v>9.34</v>
+        <v>8.73125</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -14265,12 +14265,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14286,11 +14286,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="G8">
-        <v>9.305</v>
+        <v>8.333</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -14298,11 +14298,11 @@
         </is>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>111</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14314,17 +14314,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Tyler Higbee</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D9">
@@ -14335,11 +14335,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="G9">
-        <v>9.268</v>
+        <v>8.18835</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14347,11 +14347,11 @@
         </is>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14363,7 +14363,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14384,11 +14384,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="G10">
-        <v>9.256</v>
+        <v>8.0934</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14396,11 +14396,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14412,17 +14412,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D11">
@@ -14433,11 +14433,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="G11">
-        <v>9.101</v>
+        <v>7.765</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -14445,11 +14445,11 @@
         </is>
       </c>
       <c r="I11">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14461,12 +14461,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">Khalil Shakir</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14482,11 +14482,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="G12">
-        <v>9.09</v>
+        <v>7.626</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -14494,11 +14494,11 @@
         </is>
       </c>
       <c r="I12">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14510,17 +14510,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D13">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="G13">
-        <v>9.06</v>
+        <v>7.37</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14543,11 +14543,11 @@
         </is>
       </c>
       <c r="I13">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14559,61 +14559,65 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
-      <c r="E14">
-        <v>13</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>9.058</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I14">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14624,16 +14628,20 @@
       <c r="D15">
         <v>5</v>
       </c>
-      <c r="E15">
-        <v>14</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>9.022</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14641,146 +14649,158 @@
         </is>
       </c>
       <c r="I15">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
-      <c r="E16">
-        <v>15</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>9.0216</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I16">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
-      <c r="E17">
-        <v>16</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>8.834</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I17">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zay Flowers</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
-      <c r="E18">
-        <v>17</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>8.776</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -14788,28 +14808,28 @@
         </is>
       </c>
       <c r="I18">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14820,114 +14840,126 @@
       <c r="D19">
         <v>5</v>
       </c>
-      <c r="E19">
-        <v>18</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>8.73125</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I19">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
-      <c r="E20">
-        <v>19</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>8.6</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I20">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21">
-        <v>20</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>8.549</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -14935,28 +14967,28 @@
         </is>
       </c>
       <c r="I21">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14967,65 +14999,73 @@
       <c r="D22">
         <v>5</v>
       </c>
-      <c r="E22">
-        <v>21</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>8.448</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I22">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
-      <c r="E23">
-        <v>22</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>8.335</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -15033,48 +15073,52 @@
         </is>
       </c>
       <c r="I23">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">Bijan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
-      <c r="E24">
-        <v>23</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>8.333</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -15082,48 +15126,52 @@
         </is>
       </c>
       <c r="I24">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25">
-        <v>24</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>8.285</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -15131,48 +15179,52 @@
         </is>
       </c>
       <c r="I25">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Higbee</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
-      <c r="E26">
-        <v>25</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>8.18835</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -15180,77 +15232,81 @@
         </is>
       </c>
       <c r="I26">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
-      <c r="E27">
-        <v>26</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>8.188</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I27">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -15261,16 +15317,20 @@
       <c r="D28">
         <v>5</v>
       </c>
-      <c r="E28">
-        <v>27</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>8.148</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -15278,48 +15338,52 @@
         </is>
       </c>
       <c r="I28">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
-      <c r="E29">
-        <v>28</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>8.095</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -15327,28 +15391,28 @@
         </is>
       </c>
       <c r="I29">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15359,16 +15423,20 @@
       <c r="D30">
         <v>5</v>
       </c>
-      <c r="E30">
-        <v>29</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>8.0934</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -15376,28 +15444,28 @@
         </is>
       </c>
       <c r="I30">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15408,16 +15476,20 @@
       <c r="D31">
         <v>5</v>
       </c>
-      <c r="E31">
-        <v>30</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>7.963</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -15425,48 +15497,52 @@
         </is>
       </c>
       <c r="I31">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
-      <c r="E32">
-        <v>31</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
-        </is>
-      </c>
-      <c r="G32">
-        <v>7.9413</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -15474,28 +15550,28 @@
         </is>
       </c>
       <c r="I32">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15506,16 +15582,20 @@
       <c r="D33">
         <v>5</v>
       </c>
-      <c r="E33">
-        <v>32</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
-        </is>
-      </c>
-      <c r="G33">
-        <v>7.802</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -15523,48 +15603,52 @@
         </is>
       </c>
       <c r="I33">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
-      <c r="E34">
-        <v>33</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
-        </is>
-      </c>
-      <c r="G34">
-        <v>7.765</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -15572,28 +15656,28 @@
         </is>
       </c>
       <c r="I34">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15604,94 +15688,102 @@
       <c r="D35">
         <v>5</v>
       </c>
-      <c r="E35">
-        <v>34</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>7.632</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I35">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khalil Shakir</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
-      <c r="E36">
-        <v>35</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>7.626</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I36">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -15702,16 +15794,20 @@
       <c r="D37">
         <v>5</v>
       </c>
-      <c r="E37">
-        <v>36</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
-        </is>
-      </c>
-      <c r="G37">
-        <v>7.62325</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -15719,28 +15815,28 @@
         </is>
       </c>
       <c r="I37">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -15751,65 +15847,73 @@
       <c r="D38">
         <v>5</v>
       </c>
-      <c r="E38">
-        <v>37</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
-        </is>
-      </c>
-      <c r="G38">
-        <v>7.601</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I38">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D39">
         <v>5</v>
       </c>
-      <c r="E39">
-        <v>38</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
-        </is>
-      </c>
-      <c r="G39">
-        <v>7.37485</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -15817,28 +15921,28 @@
         </is>
       </c>
       <c r="I39">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -15849,16 +15953,20 @@
       <c r="D40">
         <v>5</v>
       </c>
-      <c r="E40">
-        <v>39</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
-        </is>
-      </c>
-      <c r="G40">
-        <v>7.37</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -15866,48 +15974,52 @@
         </is>
       </c>
       <c r="I40">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
-      <c r="E41">
-        <v>40</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
-        </is>
-      </c>
-      <c r="G41">
-        <v>7.27</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -15915,48 +16027,52 @@
         </is>
       </c>
       <c r="I41">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
-      <c r="E42">
-        <v>41</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>6.9</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -15964,28 +16080,28 @@
         </is>
       </c>
       <c r="I42">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -16013,37 +16129,37 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I43">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D44">
@@ -16070,11 +16186,11 @@
         </is>
       </c>
       <c r="I44">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -16086,17 +16202,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D45">
@@ -16119,37 +16235,37 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I45">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Christian McCaffrey</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D46">
@@ -16172,37 +16288,37 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I46">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D47">
@@ -16225,15 +16341,15 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I47">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -16245,12 +16361,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16278,37 +16394,37 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I48">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D49">
@@ -16335,11 +16451,11 @@
         </is>
       </c>
       <c r="I49">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16351,17 +16467,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D50">
@@ -16384,37 +16500,37 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I50">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D51">
@@ -16441,11 +16557,11 @@
         </is>
       </c>
       <c r="I51">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -16457,17 +16573,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D52">
@@ -16494,11 +16610,11 @@
         </is>
       </c>
       <c r="I52">
-        <v>165</v>
+        <v>61</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -16510,17 +16626,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D53">
@@ -16547,11 +16663,11 @@
         </is>
       </c>
       <c r="I53">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -16563,17 +16679,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D54">
@@ -16596,32 +16712,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I54">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16653,11 +16769,11 @@
         </is>
       </c>
       <c r="I55">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -16669,17 +16785,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D56">
@@ -16706,11 +16822,11 @@
         </is>
       </c>
       <c r="I56">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -16722,17 +16838,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D57">
@@ -16759,11 +16875,11 @@
         </is>
       </c>
       <c r="I57">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16775,17 +16891,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D58">
@@ -16812,23 +16928,23 @@
         </is>
       </c>
       <c r="I58">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -16838,7 +16954,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D59">
@@ -16861,15 +16977,15 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I59">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16881,7 +16997,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -16891,7 +17007,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D60">
@@ -16914,15 +17030,15 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I60">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16934,17 +17050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D61">
@@ -16967,37 +17083,37 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I61">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D62">
@@ -17024,11 +17140,11 @@
         </is>
       </c>
       <c r="I62">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17040,17 +17156,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D63">
@@ -17073,15 +17189,15 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I63">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17093,12 +17209,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17126,15 +17242,15 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I64">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17146,17 +17262,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D65">
@@ -17179,37 +17295,37 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I65">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D66">
@@ -17236,11 +17352,11 @@
         </is>
       </c>
       <c r="I66">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -17252,12 +17368,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -17289,11 +17405,11 @@
         </is>
       </c>
       <c r="I67">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -17305,12 +17421,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -17342,11 +17458,11 @@
         </is>
       </c>
       <c r="I68">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -17358,17 +17474,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D69">
@@ -17395,11 +17511,11 @@
         </is>
       </c>
       <c r="I69">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -17411,12 +17527,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17448,11 +17564,11 @@
         </is>
       </c>
       <c r="I70">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -17464,12 +17580,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17501,11 +17617,11 @@
         </is>
       </c>
       <c r="I71">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -17517,12 +17633,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17554,11 +17670,11 @@
         </is>
       </c>
       <c r="I72">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -17570,17 +17686,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D73">
@@ -17607,11 +17723,11 @@
         </is>
       </c>
       <c r="I73">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -17623,12 +17739,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17656,15 +17772,15 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I74">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -17676,17 +17792,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D75">
@@ -17713,11 +17829,11 @@
         </is>
       </c>
       <c r="I75">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -17729,17 +17845,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D76">
@@ -17766,11 +17882,11 @@
         </is>
       </c>
       <c r="I76">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -17782,17 +17898,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D77">
@@ -17819,11 +17935,11 @@
         </is>
       </c>
       <c r="I77">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -17835,12 +17951,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17872,11 +17988,11 @@
         </is>
       </c>
       <c r="I78">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -17888,12 +18004,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17925,11 +18041,11 @@
         </is>
       </c>
       <c r="I79">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -17941,17 +18057,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D80">
@@ -17974,37 +18090,37 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I80">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D81">
@@ -18031,11 +18147,11 @@
         </is>
       </c>
       <c r="I81">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -18047,17 +18163,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">Ja'Marr Chase</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D82">
@@ -18080,32 +18196,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I82">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -18133,32 +18249,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I83">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -18190,11 +18306,11 @@
         </is>
       </c>
       <c r="I84">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -18206,17 +18322,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D85">
@@ -18243,11 +18359,11 @@
         </is>
       </c>
       <c r="I85">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -18259,17 +18375,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D86">
@@ -18296,11 +18412,11 @@
         </is>
       </c>
       <c r="I86">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -18312,12 +18428,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -18345,32 +18461,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I87">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -18398,27 +18514,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I88">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -18428,7 +18544,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D89">
@@ -18455,11 +18571,11 @@
         </is>
       </c>
       <c r="I89">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -18471,17 +18587,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D90">
@@ -18504,27 +18620,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I90">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18534,7 +18650,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D91">
@@ -18557,15 +18673,15 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I91">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -18577,17 +18693,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D92">
@@ -18614,28 +18730,28 @@
         </is>
       </c>
       <c r="I92">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18667,11 +18783,11 @@
         </is>
       </c>
       <c r="I93">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -18683,17 +18799,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D94">
@@ -18720,11 +18836,11 @@
         </is>
       </c>
       <c r="I94">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -18736,17 +18852,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D95">
@@ -18773,11 +18889,11 @@
         </is>
       </c>
       <c r="I95">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -18789,17 +18905,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D96">
@@ -18826,11 +18942,11 @@
         </is>
       </c>
       <c r="I96">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -18842,7 +18958,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -18852,7 +18968,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D97">
@@ -18875,37 +18991,37 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I97">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D98">
@@ -18928,37 +19044,37 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I98">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D99">
@@ -18981,32 +19097,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I99">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja'Marr Chase</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -19034,37 +19150,37 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I100">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D101">
@@ -19091,11 +19207,11 @@
         </is>
       </c>
       <c r="I101">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -19107,12 +19223,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -19140,37 +19256,37 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I102">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D103">
@@ -19193,15 +19309,15 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I103">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -19213,17 +19329,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Jeremiyah Love</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D104">
@@ -19250,11 +19366,11 @@
         </is>
       </c>
       <c r="I104">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -19266,17 +19382,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D105">
@@ -19299,37 +19415,37 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I105">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D106">
@@ -19352,37 +19468,37 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I106">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D107">
@@ -19405,37 +19521,37 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I107">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D108">
@@ -19458,37 +19574,37 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I108">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D109">
@@ -19515,11 +19631,11 @@
         </is>
       </c>
       <c r="I109">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -19531,17 +19647,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D110">
@@ -19564,32 +19680,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I110">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19617,37 +19733,37 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I111">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Daniels</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D112">
@@ -19670,32 +19786,32 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I112">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Higgins</t>
+          <t xml:space="preserve">Jordyn Tyson</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19723,32 +19839,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I113">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR75</t>
+          <t xml:space="preserve">WR73</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Reed</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -19776,37 +19892,37 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I114">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D115">
@@ -19829,15 +19945,15 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I115">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -19849,17 +19965,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Justin Herbert</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D116">
@@ -19886,11 +20002,11 @@
         </is>
       </c>
       <c r="I116">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -19902,17 +20018,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D117">
@@ -19939,11 +20055,11 @@
         </is>
       </c>
       <c r="I117">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -19955,17 +20071,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D118">
@@ -19992,11 +20108,11 @@
         </is>
       </c>
       <c r="I118">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -20008,12 +20124,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -20041,32 +20157,32 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I119">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -20098,11 +20214,11 @@
         </is>
       </c>
       <c r="I120">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -20114,17 +20230,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Kalif Raymond</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D121">
@@ -20147,37 +20263,37 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I121">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Kaytron Allen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D122">
@@ -20200,15 +20316,15 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I122">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">RB60</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -20220,12 +20336,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -20253,37 +20369,37 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I123">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">Keaton Mitchell</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D124">
@@ -20310,11 +20426,11 @@
         </is>
       </c>
       <c r="I124">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">RB59</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -20326,17 +20442,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Mason</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D125">
@@ -20359,27 +20475,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I125">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordyn Tyson</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -20389,7 +20505,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D126">
@@ -20416,11 +20532,11 @@
         </is>
       </c>
       <c r="I126">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR73</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -20432,17 +20548,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D127">
@@ -20465,15 +20581,15 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I127">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -20485,12 +20601,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20518,37 +20634,37 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I128">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Herbert</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D129">
@@ -20571,15 +20687,15 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I129">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20591,17 +20707,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D130">
@@ -20624,15 +20740,15 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I130">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -20644,17 +20760,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D131">
@@ -20677,37 +20793,37 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I131">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D132">
@@ -20734,11 +20850,11 @@
         </is>
       </c>
       <c r="I132">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -20750,17 +20866,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalif Raymond</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D133">
@@ -20787,11 +20903,11 @@
         </is>
       </c>
       <c r="I133">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -20803,17 +20919,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaytron Allen</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D134">
@@ -20836,15 +20952,15 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I134">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB60</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -20856,17 +20972,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">Lamar Jackson</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D135">
@@ -20893,11 +21009,11 @@
         </is>
       </c>
       <c r="I135">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -20909,17 +21025,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keaton Mitchell</t>
+          <t xml:space="preserve">Luther Burden III</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D136">
@@ -20946,11 +21062,11 @@
         </is>
       </c>
       <c r="I136">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB59</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -20962,12 +21078,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20995,37 +21111,37 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I137">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D138">
@@ -21052,11 +21168,11 @@
         </is>
       </c>
       <c r="I138">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -21068,17 +21184,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D139">
@@ -21101,15 +21217,15 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I139">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -21121,17 +21237,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D140">
@@ -21158,33 +21274,33 @@
         </is>
       </c>
       <c r="I140">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D141">
@@ -21207,32 +21323,32 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I141">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21260,37 +21376,37 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I142">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D143">
@@ -21313,37 +21429,37 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I143">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D144">
@@ -21370,11 +21486,11 @@
         </is>
       </c>
       <c r="I144">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -21386,12 +21502,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -21419,37 +21535,37 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I145">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Jackson</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D146">
@@ -21472,37 +21588,37 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I146">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luther Burden III</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D147">
@@ -21529,11 +21645,11 @@
         </is>
       </c>
       <c r="I147">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -21545,17 +21661,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D148">
@@ -21578,32 +21694,32 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I148">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -21631,32 +21747,32 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I149">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -21688,11 +21804,11 @@
         </is>
       </c>
       <c r="I150">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -21704,12 +21820,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">Mike Evans</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21741,11 +21857,11 @@
         </is>
       </c>
       <c r="I151">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -21757,17 +21873,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D152">
@@ -21794,11 +21910,11 @@
         </is>
       </c>
       <c r="I152">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -21810,17 +21926,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D153">
@@ -21843,32 +21959,32 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I153">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21900,11 +22016,11 @@
         </is>
       </c>
       <c r="I154">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -21916,17 +22032,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D155">
@@ -21949,37 +22065,37 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I155">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D156">
@@ -22006,11 +22122,11 @@
         </is>
       </c>
       <c r="I156">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -22022,17 +22138,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D157">
@@ -22059,11 +22175,11 @@
         </is>
       </c>
       <c r="I157">
-        <v>179</v>
+        <v>60</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -22075,17 +22191,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Patrick Mahomes II</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D158">
@@ -22108,37 +22224,37 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I158">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">QB13</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D159">
@@ -22161,37 +22277,37 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I159">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D160">
@@ -22214,15 +22330,15 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I160">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -22234,12 +22350,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -22271,11 +22387,11 @@
         </is>
       </c>
       <c r="I161">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -22287,17 +22403,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D162">
@@ -22320,37 +22436,37 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I162">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D163">
@@ -22377,11 +22493,11 @@
         </is>
       </c>
       <c r="I163">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -22393,12 +22509,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -22430,11 +22546,11 @@
         </is>
       </c>
       <c r="I164">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -22446,17 +22562,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes II</t>
+          <t xml:space="preserve">Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D165">
@@ -22479,37 +22595,37 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I165">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D166">
@@ -22536,11 +22652,11 @@
         </is>
       </c>
       <c r="I166">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -22552,12 +22668,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22589,11 +22705,11 @@
         </is>
       </c>
       <c r="I167">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -22605,17 +22721,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">Rome Odunze</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D168">
@@ -22642,11 +22758,11 @@
         </is>
       </c>
       <c r="I168">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -22658,12 +22774,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -22691,37 +22807,37 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I169">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rhamondre Stevenson</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D170">
@@ -22744,15 +22860,15 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I170">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -22764,17 +22880,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D171">
@@ -22797,32 +22913,32 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I171">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -22850,32 +22966,32 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I172">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rome Odunze</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -22903,37 +23019,37 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I173">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D174">
@@ -22956,37 +23072,37 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I174">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D175">
@@ -23009,15 +23125,15 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I175">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -23029,12 +23145,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -23062,37 +23178,37 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I176">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D177">
@@ -23115,32 +23231,32 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I177">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -23168,32 +23284,32 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I178">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -23225,33 +23341,33 @@
         </is>
       </c>
       <c r="I179">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D180">
@@ -23274,15 +23390,15 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I180">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -23294,17 +23410,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D181">
@@ -23327,37 +23443,37 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I181">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D182">
@@ -23384,11 +23500,11 @@
         </is>
       </c>
       <c r="I182">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -23400,17 +23516,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D183">
@@ -23437,11 +23553,11 @@
         </is>
       </c>
       <c r="I183">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -23453,17 +23569,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D184">
@@ -23486,37 +23602,37 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I184">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D185">
@@ -23539,37 +23655,37 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I185">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Trevor Lawrence</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D186">
@@ -23596,11 +23712,11 @@
         </is>
       </c>
       <c r="I186">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23612,17 +23728,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D187">
@@ -23649,11 +23765,11 @@
         </is>
       </c>
       <c r="I187">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23665,17 +23781,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">TreVeyon Henderson</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D188">
@@ -23698,37 +23814,37 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I188">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trevor Lawrence</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D189">
@@ -23755,11 +23871,11 @@
         </is>
       </c>
       <c r="I189">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -23771,17 +23887,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D190">
@@ -23808,11 +23924,11 @@
         </is>
       </c>
       <c r="I190">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -23824,17 +23940,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Tyler Shough</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D191">
@@ -23861,11 +23977,11 @@
         </is>
       </c>
       <c r="I191">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">QB24</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -23877,17 +23993,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Shough</t>
+          <t xml:space="preserve">Tyler Warren</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D192">
@@ -23914,11 +24030,11 @@
         </is>
       </c>
       <c r="I192">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB24</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -23930,17 +24046,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Warren</t>
+          <t xml:space="preserve">Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D193">
@@ -23967,11 +24083,11 @@
         </is>
       </c>
       <c r="I193">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">RB56</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -23983,17 +24099,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrone Tracy Jr.</t>
+          <t xml:space="preserve">Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D194">
@@ -24020,11 +24136,11 @@
         </is>
       </c>
       <c r="I194">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB56</t>
+          <t xml:space="preserve">WR68</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -24036,17 +24152,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wan'Dale Robinson</t>
+          <t xml:space="preserve">Woody Marks</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D195">
@@ -24073,11 +24189,11 @@
         </is>
       </c>
       <c r="I195">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR68</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -24089,17 +24205,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woody Marks</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D196">
@@ -24126,33 +24242,33 @@
         </is>
       </c>
       <c r="I196">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Zach Charbonnet</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D197">
@@ -24175,37 +24291,37 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I197">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">RB66</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zach Charbonnet</t>
+          <t xml:space="preserve">Zay Flowers</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D198">
@@ -24228,20 +24344,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I198">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB66</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -13971,17 +13971,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahmyr Gibbs</t>
+          <t xml:space="preserve">Josh Allen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D2">
@@ -13992,11 +13992,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="G2">
-        <v>9.884</v>
+        <v>9.815</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -14004,11 +14004,11 @@
         </is>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -14020,7 +14020,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D3">
@@ -14041,11 +14041,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="G3">
-        <v>9.815</v>
+        <v>9.268</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -14053,11 +14053,11 @@
         </is>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -14069,17 +14069,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bijan Robinson</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D4">
@@ -14090,11 +14090,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="G4">
-        <v>9.645</v>
+        <v>9.256</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -14102,11 +14102,11 @@
         </is>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -14118,17 +14118,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amon-Ra St. Brown</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D5">
@@ -14139,11 +14139,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="G5">
-        <v>9.605</v>
+        <v>9.022</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -14151,11 +14151,11 @@
         </is>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -14167,17 +14167,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D6">
@@ -14188,11 +14188,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="G6">
-        <v>9.386</v>
+        <v>8.834</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -14200,11 +14200,11 @@
         </is>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>182</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -14216,17 +14216,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian McCaffrey</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D7">
@@ -14237,23 +14237,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="G7">
-        <v>9.34</v>
+        <v>8.73125</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -14265,12 +14265,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14286,11 +14286,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="G8">
-        <v>9.305</v>
+        <v>8.333</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -14298,11 +14298,11 @@
         </is>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>111</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14314,17 +14314,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Tyler Higbee</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D9">
@@ -14335,11 +14335,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="G9">
-        <v>9.268</v>
+        <v>8.18835</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14347,11 +14347,11 @@
         </is>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14363,7 +14363,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14384,11 +14384,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="G10">
-        <v>9.256</v>
+        <v>8.0934</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14396,11 +14396,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14412,17 +14412,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D11">
@@ -14433,11 +14433,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="G11">
-        <v>9.101</v>
+        <v>7.765</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -14445,11 +14445,11 @@
         </is>
       </c>
       <c r="I11">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14461,12 +14461,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">Khalil Shakir</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14482,11 +14482,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="G12">
-        <v>9.09</v>
+        <v>7.626</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -14494,11 +14494,11 @@
         </is>
       </c>
       <c r="I12">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14510,17 +14510,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D13">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="G13">
-        <v>9.06</v>
+        <v>7.37</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14543,11 +14543,11 @@
         </is>
       </c>
       <c r="I13">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14559,61 +14559,65 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
-      <c r="E14">
-        <v>13</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>9.058</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I14">
-        <v>170</v>
+        <v>25</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14624,16 +14628,20 @@
       <c r="D15">
         <v>5</v>
       </c>
-      <c r="E15">
-        <v>14</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>9.022</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14641,146 +14649,158 @@
         </is>
       </c>
       <c r="I15">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
-      <c r="E16">
-        <v>15</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>9.0216</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I16">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
-      <c r="E17">
-        <v>16</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>8.834</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I17">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zay Flowers</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
-      <c r="E18">
-        <v>17</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>8.776</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -14788,28 +14808,28 @@
         </is>
       </c>
       <c r="I18">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14820,114 +14840,126 @@
       <c r="D19">
         <v>5</v>
       </c>
-      <c r="E19">
-        <v>18</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>8.73125</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I19">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
-      <c r="E20">
-        <v>19</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>8.6</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I20">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21">
-        <v>20</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>8.549</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -14935,28 +14967,28 @@
         </is>
       </c>
       <c r="I21">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14967,65 +14999,73 @@
       <c r="D22">
         <v>5</v>
       </c>
-      <c r="E22">
-        <v>21</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>8.448</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I22">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
-      <c r="E23">
-        <v>22</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>8.335</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -15033,48 +15073,52 @@
         </is>
       </c>
       <c r="I23">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">Bijan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
-      <c r="E24">
-        <v>23</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>8.333</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -15082,48 +15126,52 @@
         </is>
       </c>
       <c r="I24">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25">
-        <v>24</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>8.285</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -15131,48 +15179,52 @@
         </is>
       </c>
       <c r="I25">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Higbee</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
-      <c r="E26">
-        <v>25</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>8.18835</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -15180,77 +15232,81 @@
         </is>
       </c>
       <c r="I26">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
-      <c r="E27">
-        <v>26</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>8.188</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I27">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -15261,16 +15317,20 @@
       <c r="D28">
         <v>5</v>
       </c>
-      <c r="E28">
-        <v>27</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>8.148</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -15278,48 +15338,52 @@
         </is>
       </c>
       <c r="I28">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
-      <c r="E29">
-        <v>28</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>8.095</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -15327,28 +15391,28 @@
         </is>
       </c>
       <c r="I29">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15359,16 +15423,20 @@
       <c r="D30">
         <v>5</v>
       </c>
-      <c r="E30">
-        <v>29</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>8.0934</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -15376,28 +15444,28 @@
         </is>
       </c>
       <c r="I30">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15408,16 +15476,20 @@
       <c r="D31">
         <v>5</v>
       </c>
-      <c r="E31">
-        <v>30</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>7.963</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -15425,48 +15497,52 @@
         </is>
       </c>
       <c r="I31">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
-      <c r="E32">
-        <v>31</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
-        </is>
-      </c>
-      <c r="G32">
-        <v>7.9413</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -15474,28 +15550,28 @@
         </is>
       </c>
       <c r="I32">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15506,16 +15582,20 @@
       <c r="D33">
         <v>5</v>
       </c>
-      <c r="E33">
-        <v>32</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
-        </is>
-      </c>
-      <c r="G33">
-        <v>7.802</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -15523,48 +15603,52 @@
         </is>
       </c>
       <c r="I33">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
-      <c r="E34">
-        <v>33</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
-        </is>
-      </c>
-      <c r="G34">
-        <v>7.765</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -15572,28 +15656,28 @@
         </is>
       </c>
       <c r="I34">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15604,94 +15688,102 @@
       <c r="D35">
         <v>5</v>
       </c>
-      <c r="E35">
-        <v>34</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>7.632</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I35">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khalil Shakir</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
-      <c r="E36">
-        <v>35</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>7.626</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I36">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -15702,16 +15794,20 @@
       <c r="D37">
         <v>5</v>
       </c>
-      <c r="E37">
-        <v>36</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
-        </is>
-      </c>
-      <c r="G37">
-        <v>7.62325</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -15719,28 +15815,28 @@
         </is>
       </c>
       <c r="I37">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -15751,65 +15847,73 @@
       <c r="D38">
         <v>5</v>
       </c>
-      <c r="E38">
-        <v>37</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
-        </is>
-      </c>
-      <c r="G38">
-        <v>7.601</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I38">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D39">
         <v>5</v>
       </c>
-      <c r="E39">
-        <v>38</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
-        </is>
-      </c>
-      <c r="G39">
-        <v>7.37485</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -15817,28 +15921,28 @@
         </is>
       </c>
       <c r="I39">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -15849,16 +15953,20 @@
       <c r="D40">
         <v>5</v>
       </c>
-      <c r="E40">
-        <v>39</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
-        </is>
-      </c>
-      <c r="G40">
-        <v>7.37</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -15866,48 +15974,52 @@
         </is>
       </c>
       <c r="I40">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
-      <c r="E41">
-        <v>40</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
-        </is>
-      </c>
-      <c r="G41">
-        <v>7.27</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -15915,48 +16027,52 @@
         </is>
       </c>
       <c r="I41">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
-      <c r="E42">
-        <v>41</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>6.9</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -15964,28 +16080,28 @@
         </is>
       </c>
       <c r="I42">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -16013,37 +16129,37 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I43">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D44">
@@ -16070,11 +16186,11 @@
         </is>
       </c>
       <c r="I44">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -16086,17 +16202,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D45">
@@ -16119,37 +16235,37 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I45">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Christian McCaffrey</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D46">
@@ -16172,37 +16288,37 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I46">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D47">
@@ -16225,15 +16341,15 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I47">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -16245,12 +16361,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16278,37 +16394,37 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I48">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D49">
@@ -16335,11 +16451,11 @@
         </is>
       </c>
       <c r="I49">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16351,17 +16467,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D50">
@@ -16384,37 +16500,37 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I50">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D51">
@@ -16441,11 +16557,11 @@
         </is>
       </c>
       <c r="I51">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -16457,17 +16573,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D52">
@@ -16494,11 +16610,11 @@
         </is>
       </c>
       <c r="I52">
-        <v>165</v>
+        <v>61</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -16510,17 +16626,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D53">
@@ -16547,11 +16663,11 @@
         </is>
       </c>
       <c r="I53">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -16563,17 +16679,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D54">
@@ -16596,32 +16712,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I54">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16653,11 +16769,11 @@
         </is>
       </c>
       <c r="I55">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -16669,17 +16785,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D56">
@@ -16706,11 +16822,11 @@
         </is>
       </c>
       <c r="I56">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -16722,17 +16838,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D57">
@@ -16759,11 +16875,11 @@
         </is>
       </c>
       <c r="I57">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16775,17 +16891,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D58">
@@ -16812,23 +16928,23 @@
         </is>
       </c>
       <c r="I58">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -16838,7 +16954,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D59">
@@ -16861,15 +16977,15 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">DOUBTFUL</t>
         </is>
       </c>
       <c r="I59">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16881,7 +16997,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -16891,7 +17007,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D60">
@@ -16914,15 +17030,15 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I60">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16934,17 +17050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D61">
@@ -16967,37 +17083,37 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I61">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D62">
@@ -17024,11 +17140,11 @@
         </is>
       </c>
       <c r="I62">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17040,17 +17156,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D63">
@@ -17073,15 +17189,15 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I63">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17093,12 +17209,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17126,15 +17242,15 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I64">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17146,17 +17262,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D65">
@@ -17179,37 +17295,37 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I65">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D66">
@@ -17236,11 +17352,11 @@
         </is>
       </c>
       <c r="I66">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -17252,12 +17368,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -17289,11 +17405,11 @@
         </is>
       </c>
       <c r="I67">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -17305,12 +17421,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -17342,11 +17458,11 @@
         </is>
       </c>
       <c r="I68">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -17358,17 +17474,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D69">
@@ -17395,11 +17511,11 @@
         </is>
       </c>
       <c r="I69">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -17411,12 +17527,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17448,11 +17564,11 @@
         </is>
       </c>
       <c r="I70">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -17464,12 +17580,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17501,11 +17617,11 @@
         </is>
       </c>
       <c r="I71">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -17517,12 +17633,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17554,11 +17670,11 @@
         </is>
       </c>
       <c r="I72">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -17570,17 +17686,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D73">
@@ -17607,11 +17723,11 @@
         </is>
       </c>
       <c r="I73">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -17623,12 +17739,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17656,15 +17772,15 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I74">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -17676,17 +17792,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D75">
@@ -17713,11 +17829,11 @@
         </is>
       </c>
       <c r="I75">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -17729,17 +17845,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D76">
@@ -17766,11 +17882,11 @@
         </is>
       </c>
       <c r="I76">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -17782,17 +17898,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D77">
@@ -17819,11 +17935,11 @@
         </is>
       </c>
       <c r="I77">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -17835,12 +17951,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17872,11 +17988,11 @@
         </is>
       </c>
       <c r="I78">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -17888,12 +18004,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17925,11 +18041,11 @@
         </is>
       </c>
       <c r="I79">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -17941,17 +18057,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D80">
@@ -17974,37 +18090,37 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I80">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D81">
@@ -18031,11 +18147,11 @@
         </is>
       </c>
       <c r="I81">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -18047,17 +18163,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">Ja'Marr Chase</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D82">
@@ -18080,32 +18196,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I82">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -18133,32 +18249,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I83">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -18190,11 +18306,11 @@
         </is>
       </c>
       <c r="I84">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -18206,17 +18322,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D85">
@@ -18243,11 +18359,11 @@
         </is>
       </c>
       <c r="I85">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -18259,17 +18375,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D86">
@@ -18296,11 +18412,11 @@
         </is>
       </c>
       <c r="I86">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -18312,12 +18428,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -18345,32 +18461,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I87">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -18398,27 +18514,27 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I88">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -18428,7 +18544,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D89">
@@ -18455,11 +18571,11 @@
         </is>
       </c>
       <c r="I89">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -18471,17 +18587,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D90">
@@ -18504,27 +18620,27 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I90">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18534,7 +18650,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D91">
@@ -18557,15 +18673,15 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I91">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -18577,17 +18693,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D92">
@@ -18614,28 +18730,28 @@
         </is>
       </c>
       <c r="I92">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18667,11 +18783,11 @@
         </is>
       </c>
       <c r="I93">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -18683,17 +18799,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D94">
@@ -18720,11 +18836,11 @@
         </is>
       </c>
       <c r="I94">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -18736,17 +18852,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D95">
@@ -18773,11 +18889,11 @@
         </is>
       </c>
       <c r="I95">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -18789,17 +18905,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D96">
@@ -18826,11 +18942,11 @@
         </is>
       </c>
       <c r="I96">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -18842,7 +18958,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -18852,7 +18968,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D97">
@@ -18875,37 +18991,37 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I97">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D98">
@@ -18928,37 +19044,37 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I98">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D99">
@@ -18981,32 +19097,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I99">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja'Marr Chase</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -19034,37 +19150,37 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I100">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D101">
@@ -19091,11 +19207,11 @@
         </is>
       </c>
       <c r="I101">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -19107,12 +19223,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -19140,37 +19256,37 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I102">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D103">
@@ -19193,15 +19309,15 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I103">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -19213,17 +19329,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Jeremiyah Love</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D104">
@@ -19250,11 +19366,11 @@
         </is>
       </c>
       <c r="I104">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -19266,17 +19382,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D105">
@@ -19299,37 +19415,37 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I105">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D106">
@@ -19352,37 +19468,37 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I106">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D107">
@@ -19405,37 +19521,37 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I107">
-        <v>178</v>
+        <v>10</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D108">
@@ -19458,37 +19574,37 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I108">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D109">
@@ -19515,11 +19631,11 @@
         </is>
       </c>
       <c r="I109">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -19531,17 +19647,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D110">
@@ -19564,32 +19680,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I110">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19617,37 +19733,37 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I111">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Daniels</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D112">
@@ -19670,32 +19786,32 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I112">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Higgins</t>
+          <t xml:space="preserve">Jordyn Tyson</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -19723,32 +19839,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I113">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR75</t>
+          <t xml:space="preserve">WR73</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Reed</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -19776,37 +19892,37 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I114">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D115">
@@ -19829,15 +19945,15 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I115">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -19849,17 +19965,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Justin Herbert</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D116">
@@ -19886,11 +20002,11 @@
         </is>
       </c>
       <c r="I116">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -19902,17 +20018,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D117">
@@ -19939,11 +20055,11 @@
         </is>
       </c>
       <c r="I117">
-        <v>155</v>
+        <v>13</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -19955,17 +20071,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D118">
@@ -19992,11 +20108,11 @@
         </is>
       </c>
       <c r="I118">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -20008,12 +20124,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -20041,32 +20157,32 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I119">
-        <v>154</v>
+        <v>197</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -20098,11 +20214,11 @@
         </is>
       </c>
       <c r="I120">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -20114,17 +20230,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Kalif Raymond</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D121">
@@ -20147,37 +20263,37 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I121">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Kaytron Allen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D122">
@@ -20200,15 +20316,15 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I122">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">RB60</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -20220,12 +20336,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -20253,37 +20369,37 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I123">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">Keaton Mitchell</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D124">
@@ -20310,11 +20426,11 @@
         </is>
       </c>
       <c r="I124">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">RB59</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -20326,17 +20442,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Mason</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D125">
@@ -20359,27 +20475,27 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I125">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordyn Tyson</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -20389,7 +20505,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D126">
@@ -20416,11 +20532,11 @@
         </is>
       </c>
       <c r="I126">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR73</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -20432,17 +20548,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D127">
@@ -20465,15 +20581,15 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I127">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -20485,12 +20601,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20518,37 +20634,37 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I128">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Herbert</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D129">
@@ -20571,15 +20687,15 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I129">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20591,17 +20707,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D130">
@@ -20624,15 +20740,15 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I130">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -20644,17 +20760,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D131">
@@ -20677,37 +20793,37 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I131">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D132">
@@ -20734,11 +20850,11 @@
         </is>
       </c>
       <c r="I132">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -20750,17 +20866,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalif Raymond</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D133">
@@ -20787,11 +20903,11 @@
         </is>
       </c>
       <c r="I133">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -20803,17 +20919,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaytron Allen</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D134">
@@ -20836,15 +20952,15 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I134">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB60</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -20856,17 +20972,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">Lamar Jackson</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D135">
@@ -20893,11 +21009,11 @@
         </is>
       </c>
       <c r="I135">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -20909,17 +21025,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keaton Mitchell</t>
+          <t xml:space="preserve">Luther Burden III</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D136">
@@ -20946,11 +21062,11 @@
         </is>
       </c>
       <c r="I136">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB59</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -20962,12 +21078,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20995,37 +21111,37 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I137">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D138">
@@ -21052,11 +21168,11 @@
         </is>
       </c>
       <c r="I138">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -21068,17 +21184,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D139">
@@ -21101,15 +21217,15 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I139">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -21121,17 +21237,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D140">
@@ -21158,33 +21274,33 @@
         </is>
       </c>
       <c r="I140">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D141">
@@ -21207,32 +21323,32 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I141">
-        <v>86</v>
+        <v>190</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21260,37 +21376,37 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I142">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D143">
@@ -21313,37 +21429,37 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I143">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D144">
@@ -21370,11 +21486,11 @@
         </is>
       </c>
       <c r="I144">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -21386,12 +21502,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -21419,37 +21535,37 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I145">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Jackson</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D146">
@@ -21472,37 +21588,37 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I146">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luther Burden III</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D147">
@@ -21529,11 +21645,11 @@
         </is>
       </c>
       <c r="I147">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -21545,17 +21661,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D148">
@@ -21578,32 +21694,32 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I148">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -21631,32 +21747,32 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I149">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -21688,11 +21804,11 @@
         </is>
       </c>
       <c r="I150">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -21704,12 +21820,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">Mike Evans</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21741,11 +21857,11 @@
         </is>
       </c>
       <c r="I151">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -21757,17 +21873,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D152">
@@ -21794,11 +21910,11 @@
         </is>
       </c>
       <c r="I152">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -21810,17 +21926,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D153">
@@ -21843,32 +21959,32 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I153">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21900,11 +22016,11 @@
         </is>
       </c>
       <c r="I154">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -21916,17 +22032,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D155">
@@ -21949,37 +22065,37 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I155">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D156">
@@ -22006,11 +22122,11 @@
         </is>
       </c>
       <c r="I156">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -22022,17 +22138,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D157">
@@ -22059,11 +22175,11 @@
         </is>
       </c>
       <c r="I157">
-        <v>179</v>
+        <v>60</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -22075,17 +22191,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Patrick Mahomes II</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D158">
@@ -22108,37 +22224,37 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I158">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">QB13</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D159">
@@ -22161,37 +22277,37 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I159">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D160">
@@ -22214,15 +22330,15 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I160">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -22234,12 +22350,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -22271,11 +22387,11 @@
         </is>
       </c>
       <c r="I161">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -22287,17 +22403,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D162">
@@ -22320,37 +22436,37 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I162">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D163">
@@ -22377,11 +22493,11 @@
         </is>
       </c>
       <c r="I163">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -22393,12 +22509,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -22430,11 +22546,11 @@
         </is>
       </c>
       <c r="I164">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -22446,17 +22562,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes II</t>
+          <t xml:space="preserve">Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D165">
@@ -22479,37 +22595,37 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I165">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D166">
@@ -22536,11 +22652,11 @@
         </is>
       </c>
       <c r="I166">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -22552,12 +22668,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22589,11 +22705,11 @@
         </is>
       </c>
       <c r="I167">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -22605,17 +22721,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">Rome Odunze</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D168">
@@ -22642,11 +22758,11 @@
         </is>
       </c>
       <c r="I168">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -22658,12 +22774,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -22691,37 +22807,37 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I169">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rhamondre Stevenson</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D170">
@@ -22744,15 +22860,15 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I170">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -22764,17 +22880,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D171">
@@ -22797,32 +22913,32 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I171">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -22850,32 +22966,32 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I172">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rome Odunze</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -22903,37 +23019,37 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I173">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D174">
@@ -22956,37 +23072,37 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I174">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D175">
@@ -23013,11 +23129,11 @@
         </is>
       </c>
       <c r="I175">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -23029,12 +23145,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -23062,37 +23178,37 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I176">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D177">
@@ -23115,32 +23231,32 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I177">
-        <v>181</v>
+        <v>44</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -23168,32 +23284,32 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I178">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -23225,33 +23341,33 @@
         </is>
       </c>
       <c r="I179">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D180">
@@ -23274,15 +23390,15 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I180">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -23294,17 +23410,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D181">
@@ -23327,37 +23443,37 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I181">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D182">
@@ -23384,11 +23500,11 @@
         </is>
       </c>
       <c r="I182">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -23400,17 +23516,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D183">
@@ -23437,11 +23553,11 @@
         </is>
       </c>
       <c r="I183">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -23453,17 +23569,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D184">
@@ -23486,37 +23602,37 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I184">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D185">
@@ -23539,37 +23655,37 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I185">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Trevor Lawrence</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D186">
@@ -23596,11 +23712,11 @@
         </is>
       </c>
       <c r="I186">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23612,17 +23728,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D187">
@@ -23649,11 +23765,11 @@
         </is>
       </c>
       <c r="I187">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23665,17 +23781,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">TreVeyon Henderson</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D188">
@@ -23698,37 +23814,37 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I188">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trevor Lawrence</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D189">
@@ -23755,11 +23871,11 @@
         </is>
       </c>
       <c r="I189">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -23771,17 +23887,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D190">
@@ -23808,11 +23924,11 @@
         </is>
       </c>
       <c r="I190">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -23824,17 +23940,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Tyler Shough</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D191">
@@ -23861,11 +23977,11 @@
         </is>
       </c>
       <c r="I191">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">QB24</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -23877,17 +23993,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Shough</t>
+          <t xml:space="preserve">Tyler Warren</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D192">
@@ -23914,11 +24030,11 @@
         </is>
       </c>
       <c r="I192">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB24</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -23930,17 +24046,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Warren</t>
+          <t xml:space="preserve">Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D193">
@@ -23967,11 +24083,11 @@
         </is>
       </c>
       <c r="I193">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">RB56</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -23983,17 +24099,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrone Tracy Jr.</t>
+          <t xml:space="preserve">Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D194">
@@ -24020,11 +24136,11 @@
         </is>
       </c>
       <c r="I194">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB56</t>
+          <t xml:space="preserve">WR68</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -24036,17 +24152,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wan'Dale Robinson</t>
+          <t xml:space="preserve">Woody Marks</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D195">
@@ -24073,11 +24189,11 @@
         </is>
       </c>
       <c r="I195">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR68</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -24089,17 +24205,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woody Marks</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D196">
@@ -24126,33 +24242,33 @@
         </is>
       </c>
       <c r="I196">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Zach Charbonnet</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D197">
@@ -24175,37 +24291,37 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I197">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">RB66</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zach Charbonnet</t>
+          <t xml:space="preserve">Zay Flowers</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D198">
@@ -24228,20 +24344,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I198">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB66</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -13971,61 +13971,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
-        </is>
-      </c>
-      <c r="G2">
-        <v>9.815</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14036,16 +14040,20 @@
       <c r="D3">
         <v>5</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
-        </is>
-      </c>
-      <c r="G3">
-        <v>9.268</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -14053,28 +14061,28 @@
         </is>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14085,143 +14093,155 @@
       <c r="D4">
         <v>5</v>
       </c>
-      <c r="E4">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>9.256</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
-      <c r="E5">
-        <v>4</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>9.022</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I5">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D6">
         <v>5</v>
       </c>
-      <c r="E6">
-        <v>5</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>8.834</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I6">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14232,114 +14252,126 @@
       <c r="D7">
         <v>5</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+        </is>
+      </c>
+      <c r="I7">
         <v>6</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WR2</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>8.73125</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
-        </is>
-      </c>
-      <c r="I7">
-        <v>34</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
-      <c r="E8">
-        <v>7</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
-        </is>
-      </c>
-      <c r="G8">
-        <v>8.333</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I8">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Higbee</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
-      <c r="E9">
-        <v>8</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
-        </is>
-      </c>
-      <c r="G9">
-        <v>8.18835</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14347,97 +14379,105 @@
         </is>
       </c>
       <c r="I9">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10">
-        <v>9</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
-        </is>
-      </c>
-      <c r="G10">
-        <v>8.0934</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I10">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D11">
         <v>5</v>
       </c>
-      <c r="E11">
-        <v>10</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>7.765</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -14445,48 +14485,52 @@
         </is>
       </c>
       <c r="I11">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khalil Shakir</t>
+          <t xml:space="preserve">Bijan Robinson</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12">
-        <v>11</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>7.626</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -14494,16 +14538,16 @@
         </is>
       </c>
       <c r="I12">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
@@ -14526,16 +14570,20 @@
       <c r="D13">
         <v>5</v>
       </c>
-      <c r="E13">
-        <v>12</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>7.37</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14552,24 +14600,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D14">
@@ -14592,32 +14640,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I14">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14649,11 +14697,11 @@
         </is>
       </c>
       <c r="I15">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14665,7 +14713,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -14675,7 +14723,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D16">
@@ -14702,11 +14750,11 @@
         </is>
       </c>
       <c r="I16">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14718,17 +14766,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D17">
@@ -14751,32 +14799,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I17">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14804,15 +14852,15 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I18">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14824,12 +14872,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amon-Ra St. Brown</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14861,11 +14909,11 @@
         </is>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14877,7 +14925,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -14887,7 +14935,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D20">
@@ -14910,15 +14958,15 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I20">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14930,17 +14978,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D21">
@@ -14967,11 +15015,11 @@
         </is>
       </c>
       <c r="I21">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14983,7 +15031,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -14993,7 +15041,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D22">
@@ -15016,37 +15064,37 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I22">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D23">
@@ -15073,11 +15121,11 @@
         </is>
       </c>
       <c r="I23">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -15089,17 +15137,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bijan Robinson</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D24">
@@ -15122,32 +15170,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15175,32 +15223,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I25">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15232,11 +15280,11 @@
         </is>
       </c>
       <c r="I26">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -15248,17 +15296,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D27">
@@ -15281,37 +15329,37 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I27">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D28">
@@ -15334,15 +15382,15 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I28">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -15354,12 +15402,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15391,11 +15439,11 @@
         </is>
       </c>
       <c r="I29">
-        <v>171</v>
+        <v>17</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -15407,17 +15455,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D30">
@@ -15444,11 +15492,11 @@
         </is>
       </c>
       <c r="I30">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -15460,17 +15508,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D31">
@@ -15497,11 +15545,11 @@
         </is>
       </c>
       <c r="I31">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15513,17 +15561,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D32">
@@ -15550,11 +15598,11 @@
         </is>
       </c>
       <c r="I32">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15566,17 +15614,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D33">
@@ -15603,11 +15651,11 @@
         </is>
       </c>
       <c r="I33">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -15619,17 +15667,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D34">
@@ -15656,11 +15704,11 @@
         </is>
       </c>
       <c r="I34">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -15672,17 +15720,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">Christian McCaffrey</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D35">
@@ -15705,37 +15753,37 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I35">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D36">
@@ -15758,32 +15806,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I36">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -15815,33 +15863,33 @@
         </is>
       </c>
       <c r="I37">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D38">
@@ -15864,15 +15912,15 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I38">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15884,17 +15932,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D39">
@@ -15917,15 +15965,15 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I39">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -15937,17 +15985,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D40">
@@ -15974,11 +16022,11 @@
         </is>
       </c>
       <c r="I40">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -15990,17 +16038,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D41">
@@ -16027,11 +16075,11 @@
         </is>
       </c>
       <c r="I41">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -16043,17 +16091,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D42">
@@ -16080,11 +16128,11 @@
         </is>
       </c>
       <c r="I42">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -16096,17 +16144,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D43">
@@ -16133,11 +16181,11 @@
         </is>
       </c>
       <c r="I43">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -16149,17 +16197,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D44">
@@ -16186,11 +16234,11 @@
         </is>
       </c>
       <c r="I44">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -16202,17 +16250,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D45">
@@ -16239,11 +16287,11 @@
         </is>
       </c>
       <c r="I45">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -16255,17 +16303,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian McCaffrey</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D46">
@@ -16292,11 +16340,11 @@
         </is>
       </c>
       <c r="I46">
-        <v>7</v>
+        <v>164</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -16308,12 +16356,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -16345,11 +16393,11 @@
         </is>
       </c>
       <c r="I47">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -16361,7 +16409,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -16371,7 +16419,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D48">
@@ -16398,11 +16446,11 @@
         </is>
       </c>
       <c r="I48">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -16414,17 +16462,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D49">
@@ -16451,11 +16499,11 @@
         </is>
       </c>
       <c r="I49">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16467,12 +16515,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16500,15 +16548,15 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">DOUBTFUL</t>
         </is>
       </c>
       <c r="I50">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -16520,17 +16568,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D51">
@@ -16553,37 +16601,37 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I51">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D52">
@@ -16606,37 +16654,37 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I52">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D53">
@@ -16663,11 +16711,11 @@
         </is>
       </c>
       <c r="I53">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -16679,17 +16727,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D54">
@@ -16716,11 +16764,11 @@
         </is>
       </c>
       <c r="I54">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -16732,17 +16780,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D55">
@@ -16769,11 +16817,11 @@
         </is>
       </c>
       <c r="I55">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -16785,17 +16833,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D56">
@@ -16818,32 +16866,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I56">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16871,37 +16919,37 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I57">
-        <v>177</v>
+        <v>34</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D58">
@@ -16928,33 +16976,33 @@
         </is>
       </c>
       <c r="I58">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D59">
@@ -16977,15 +17025,15 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOUBTFUL</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I59">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16997,17 +17045,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D60">
@@ -17030,37 +17078,37 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D61">
@@ -17083,15 +17131,15 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I61">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -17103,17 +17151,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D62">
@@ -17140,11 +17188,11 @@
         </is>
       </c>
       <c r="I62">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17156,17 +17204,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D63">
@@ -17193,11 +17241,11 @@
         </is>
       </c>
       <c r="I63">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17209,17 +17257,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D64">
@@ -17246,28 +17294,28 @@
         </is>
       </c>
       <c r="I64">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -17295,37 +17343,37 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I65">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D66">
@@ -17348,15 +17396,15 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I66">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -17368,17 +17416,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D67">
@@ -17405,11 +17453,11 @@
         </is>
       </c>
       <c r="I67">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -17421,12 +17469,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -17458,11 +17506,11 @@
         </is>
       </c>
       <c r="I68">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -17474,17 +17522,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D69">
@@ -17511,11 +17559,11 @@
         </is>
       </c>
       <c r="I69">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -17527,17 +17575,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D70">
@@ -17564,11 +17612,11 @@
         </is>
       </c>
       <c r="I70">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -17580,17 +17628,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D71">
@@ -17617,11 +17665,11 @@
         </is>
       </c>
       <c r="I71">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -17633,12 +17681,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17666,37 +17714,37 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I72">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D73">
@@ -17723,11 +17771,11 @@
         </is>
       </c>
       <c r="I73">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -17739,17 +17787,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">Ja'Marr Chase</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D74">
@@ -17776,11 +17824,11 @@
         </is>
       </c>
       <c r="I74">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -17792,17 +17840,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D75">
@@ -17829,11 +17877,11 @@
         </is>
       </c>
       <c r="I75">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -17845,17 +17893,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D76">
@@ -17878,37 +17926,37 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I76">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D77">
@@ -17935,11 +17983,11 @@
         </is>
       </c>
       <c r="I77">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -17951,12 +17999,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17988,11 +18036,11 @@
         </is>
       </c>
       <c r="I78">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -18004,17 +18052,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D79">
@@ -18041,11 +18089,11 @@
         </is>
       </c>
       <c r="I79">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -18057,17 +18105,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D80">
@@ -18090,37 +18138,37 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I80">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D81">
@@ -18147,11 +18195,11 @@
         </is>
       </c>
       <c r="I81">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -18163,12 +18211,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja'Marr Chase</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -18196,37 +18244,37 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D83">
@@ -18249,15 +18297,15 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I83">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -18269,17 +18317,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D84">
@@ -18302,32 +18350,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I84">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahmyr Gibbs</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -18359,11 +18407,11 @@
         </is>
       </c>
       <c r="I85">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -18375,17 +18423,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D86">
@@ -18412,11 +18460,11 @@
         </is>
       </c>
       <c r="I86">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -18428,17 +18476,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D87">
@@ -18465,11 +18513,11 @@
         </is>
       </c>
       <c r="I87">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -18481,17 +18529,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D88">
@@ -18514,37 +18562,37 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I88">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D89">
@@ -18567,15 +18615,15 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I89">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -18587,17 +18635,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D90">
@@ -18620,15 +18668,15 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I90">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -18640,12 +18688,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -18673,15 +18721,15 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I91">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -18693,17 +18741,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D92">
@@ -18726,32 +18774,32 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I92">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18779,37 +18827,37 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I93">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D94">
@@ -18836,11 +18884,11 @@
         </is>
       </c>
       <c r="I94">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -18852,12 +18900,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -18889,11 +18937,11 @@
         </is>
       </c>
       <c r="I95">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -18905,17 +18953,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D96">
@@ -18938,15 +18986,15 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I96">
-        <v>5</v>
+        <v>155</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -18958,17 +19006,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Jeremiyah Love</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D97">
@@ -18991,32 +19039,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I97">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Daniels</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -19048,11 +19096,11 @@
         </is>
       </c>
       <c r="I98">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -19064,17 +19112,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Higgins</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D99">
@@ -19101,11 +19149,11 @@
         </is>
       </c>
       <c r="I99">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR75</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -19117,17 +19165,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Reed</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D100">
@@ -19150,37 +19198,37 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I100">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D101">
@@ -19203,37 +19251,37 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I101">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D102">
@@ -19260,11 +19308,11 @@
         </is>
       </c>
       <c r="I102">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -19276,17 +19324,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D103">
@@ -19309,37 +19357,37 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I103">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D104">
@@ -19366,11 +19414,11 @@
         </is>
       </c>
       <c r="I104">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -19382,17 +19430,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D105">
@@ -19415,37 +19463,37 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I105">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Jordyn Tyson</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D106">
@@ -19472,11 +19520,11 @@
         </is>
       </c>
       <c r="I106">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">WR73</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -19488,17 +19536,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Josh Allen</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D107">
@@ -19525,11 +19573,11 @@
         </is>
       </c>
       <c r="I107">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -19541,17 +19589,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D108">
@@ -19574,27 +19622,27 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I108">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -19604,7 +19652,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D109">
@@ -19627,15 +19675,15 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I109">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -19647,17 +19695,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">Justin Herbert</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D110">
@@ -19680,37 +19728,37 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I110">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D111">
@@ -19733,15 +19781,15 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I111">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -19753,17 +19801,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Mason</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D112">
@@ -19786,37 +19834,37 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I112">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordyn Tyson</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D113">
@@ -19843,11 +19891,11 @@
         </is>
       </c>
       <c r="I113">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR73</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -19859,17 +19907,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D114">
@@ -19896,11 +19944,11 @@
         </is>
       </c>
       <c r="I114">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -19912,17 +19960,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Kalif Raymond</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D115">
@@ -19945,15 +19993,15 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I115">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -19965,17 +20013,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Herbert</t>
+          <t xml:space="preserve">Kaytron Allen</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D116">
@@ -19998,15 +20046,15 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I116">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">RB60</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -20018,12 +20066,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -20055,11 +20103,11 @@
         </is>
       </c>
       <c r="I117">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -20071,17 +20119,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">Keaton Mitchell</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D118">
@@ -20108,11 +20156,11 @@
         </is>
       </c>
       <c r="I118">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB59</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -20124,17 +20172,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D119">
@@ -20157,15 +20205,15 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I119">
-        <v>197</v>
+        <v>94</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -20177,12 +20225,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -20214,11 +20262,11 @@
         </is>
       </c>
       <c r="I120">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -20230,17 +20278,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalif Raymond</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D121">
@@ -20263,15 +20311,15 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I121">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -20283,12 +20331,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaytron Allen</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -20316,37 +20364,37 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I122">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB60</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D123">
@@ -20373,11 +20421,11 @@
         </is>
       </c>
       <c r="I123">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -20389,17 +20437,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keaton Mitchell</t>
+          <t xml:space="preserve">Khalil Shakir</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D124">
@@ -20426,11 +20474,11 @@
         </is>
       </c>
       <c r="I124">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB59</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -20442,17 +20490,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D125">
@@ -20475,15 +20523,15 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I125">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -20495,17 +20543,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D126">
@@ -20532,11 +20580,11 @@
         </is>
       </c>
       <c r="I126">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -20548,12 +20596,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -20581,37 +20629,37 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I127">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D128">
@@ -20638,33 +20686,33 @@
         </is>
       </c>
       <c r="I128">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D129">
@@ -20687,15 +20735,15 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I129">
-        <v>86</v>
+        <v>175</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20707,17 +20755,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D130">
@@ -20744,11 +20792,11 @@
         </is>
       </c>
       <c r="I130">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -20760,17 +20808,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D131">
@@ -20793,37 +20841,37 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I131">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Lamar Jackson</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D132">
@@ -20846,37 +20894,37 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I132">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">Luther Burden III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D133">
@@ -20903,11 +20951,11 @@
         </is>
       </c>
       <c r="I133">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -20919,12 +20967,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -20952,37 +21000,37 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I134">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Jackson</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D135">
@@ -21005,32 +21053,32 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I135">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luther Burden III</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -21062,11 +21110,11 @@
         </is>
       </c>
       <c r="I136">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -21078,12 +21126,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -21111,37 +21159,37 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I137">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D138">
@@ -21168,11 +21216,11 @@
         </is>
       </c>
       <c r="I138">
-        <v>99</v>
+        <v>190</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -21184,17 +21232,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D139">
@@ -21217,37 +21265,37 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I139">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D140">
@@ -21274,11 +21322,11 @@
         </is>
       </c>
       <c r="I140">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -21290,17 +21338,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D141">
@@ -21327,11 +21375,11 @@
         </is>
       </c>
       <c r="I141">
-        <v>190</v>
+        <v>121</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -21343,17 +21391,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D142">
@@ -21380,11 +21428,11 @@
         </is>
       </c>
       <c r="I142">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -21396,17 +21444,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D143">
@@ -21433,11 +21481,11 @@
         </is>
       </c>
       <c r="I143">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -21449,17 +21497,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D144">
@@ -21486,11 +21534,11 @@
         </is>
       </c>
       <c r="I144">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -21502,17 +21550,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D145">
@@ -21535,37 +21583,37 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I145">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D146">
@@ -21588,15 +21636,15 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I146">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -21608,17 +21656,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D147">
@@ -21641,37 +21689,37 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I147">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D148">
@@ -21694,15 +21742,15 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I148">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21714,12 +21762,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Mike Evans</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -21747,37 +21795,37 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I149">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D150">
@@ -21804,11 +21852,11 @@
         </is>
       </c>
       <c r="I150">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -21820,12 +21868,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21857,11 +21905,11 @@
         </is>
       </c>
       <c r="I151">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -21873,12 +21921,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21910,11 +21958,11 @@
         </is>
       </c>
       <c r="I152">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -21926,17 +21974,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D153">
@@ -21963,11 +22011,11 @@
         </is>
       </c>
       <c r="I153">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -21979,17 +22027,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D154">
@@ -22016,11 +22064,11 @@
         </is>
       </c>
       <c r="I154">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -22032,17 +22080,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D155">
@@ -22069,11 +22117,11 @@
         </is>
       </c>
       <c r="I155">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -22085,17 +22133,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Patrick Mahomes II</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D156">
@@ -22122,28 +22170,28 @@
         </is>
       </c>
       <c r="I156">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">QB13</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -22175,11 +22223,11 @@
         </is>
       </c>
       <c r="I157">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -22191,17 +22239,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes II</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D158">
@@ -22224,37 +22272,37 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I158">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D159">
@@ -22277,32 +22325,32 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I159">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -22330,15 +22378,15 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I160">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -22350,17 +22398,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D161">
@@ -22383,32 +22431,32 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I161">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -22436,32 +22484,32 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I162">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -22493,11 +22541,11 @@
         </is>
       </c>
       <c r="I163">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -22509,17 +22557,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D164">
@@ -22542,15 +22590,15 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I164">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -22562,12 +22610,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rhamondre Stevenson</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -22595,32 +22643,32 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I165">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -22648,37 +22696,37 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I166">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Rome Odunze</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D167">
@@ -22705,11 +22753,11 @@
         </is>
       </c>
       <c r="I167">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -22721,12 +22769,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rome Odunze</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -22758,11 +22806,11 @@
         </is>
       </c>
       <c r="I168">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -22774,17 +22822,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D169">
@@ -22811,11 +22859,11 @@
         </is>
       </c>
       <c r="I169">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -22827,17 +22875,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D170">
@@ -22864,11 +22912,11 @@
         </is>
       </c>
       <c r="I170">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -22880,17 +22928,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D171">
@@ -22913,37 +22961,37 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I171">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D172">
@@ -22970,11 +23018,11 @@
         </is>
       </c>
       <c r="I172">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -22986,17 +23034,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D173">
@@ -23019,15 +23067,15 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I173">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -23039,17 +23087,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D174">
@@ -23072,15 +23120,15 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I174">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -23092,12 +23140,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -23125,32 +23173,32 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I175">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -23178,15 +23226,15 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I176">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -23198,12 +23246,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -23235,11 +23283,11 @@
         </is>
       </c>
       <c r="I177">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -23251,12 +23299,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -23284,37 +23332,37 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I178">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D179">
@@ -23341,28 +23389,28 @@
         </is>
       </c>
       <c r="I179">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -23390,37 +23438,37 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I180">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D181">
@@ -23443,37 +23491,37 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I181">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D182">
@@ -23500,28 +23548,28 @@
         </is>
       </c>
       <c r="I182">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -23549,15 +23597,15 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">DOUBTFUL</t>
         </is>
       </c>
       <c r="I183">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -23569,17 +23617,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D184">
@@ -23606,11 +23654,11 @@
         </is>
       </c>
       <c r="I184">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -23622,17 +23670,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">TreVeyon Henderson</t>
+          <t xml:space="preserve">Trevor Lawrence</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D185">
@@ -23655,15 +23703,15 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I185">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -23675,17 +23723,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trevor Lawrence</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D186">
@@ -23712,11 +23760,11 @@
         </is>
       </c>
       <c r="I186">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23728,12 +23776,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -23765,11 +23813,11 @@
         </is>
       </c>
       <c r="I187">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23781,17 +23829,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D188">
@@ -23818,11 +23866,11 @@
         </is>
       </c>
       <c r="I188">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -23834,12 +23882,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -23871,11 +23919,11 @@
         </is>
       </c>
       <c r="I189">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -23887,17 +23935,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Tyler Higbee</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D190">
@@ -23924,11 +23972,11 @@
         </is>
       </c>
       <c r="I190">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -14069,17 +14069,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bijan Robinson</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D4">
@@ -14090,11 +14090,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="G4">
-        <v>9.645</v>
+        <v>9.386</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -14102,11 +14102,11 @@
         </is>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -14118,17 +14118,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Christian McCaffrey</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D5">
@@ -14139,11 +14139,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="G5">
-        <v>9.46</v>
+        <v>9.34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -14151,11 +14151,11 @@
         </is>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -14167,17 +14167,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D6">
@@ -14188,11 +14188,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="G6">
-        <v>9.386</v>
+        <v>9.286</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -14200,11 +14200,11 @@
         </is>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -14216,17 +14216,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D7">
@@ -14237,11 +14237,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="G7">
-        <v>9.3675</v>
+        <v>9.276</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -14249,11 +14249,11 @@
         </is>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -14265,12 +14265,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian McCaffrey</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14286,11 +14286,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="G8">
-        <v>9.34</v>
+        <v>9.268</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -14298,11 +14298,11 @@
         </is>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14314,17 +14314,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D9">
@@ -14335,11 +14335,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="G9">
-        <v>9.286</v>
+        <v>9.26</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14347,11 +14347,11 @@
         </is>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14363,17 +14363,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Daniels</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D10">
@@ -14384,11 +14384,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="G10">
-        <v>9.276</v>
+        <v>9.256</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14396,11 +14396,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14412,17 +14412,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Justin Herbert</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D11">
@@ -14433,11 +14433,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="G11">
-        <v>9.268</v>
+        <v>9.185</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -14445,11 +14445,11 @@
         </is>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14461,17 +14461,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D12">
@@ -14482,11 +14482,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="G12">
-        <v>9.26</v>
+        <v>9.06</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -14494,11 +14494,11 @@
         </is>
       </c>
       <c r="I12">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14510,12 +14510,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="G13">
-        <v>9.256</v>
+        <v>9.028</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14543,11 +14543,11 @@
         </is>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14559,17 +14559,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Herbert</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D14">
@@ -14580,11 +14580,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="G14">
-        <v>9.185</v>
+        <v>9.022</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -14592,11 +14592,11 @@
         </is>
       </c>
       <c r="I14">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14608,17 +14608,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D15">
@@ -14629,23 +14629,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="G15">
-        <v>9.14525</v>
+        <v>9.02</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14657,12 +14657,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14682,19 +14682,19 @@
         </is>
       </c>
       <c r="G16">
-        <v>9.142</v>
+        <v>9.012</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I16">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14706,17 +14706,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D17">
@@ -14727,11 +14727,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="G17">
-        <v>9.101</v>
+        <v>8.9616</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -14739,11 +14739,11 @@
         </is>
       </c>
       <c r="I17">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -14755,17 +14755,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D18">
@@ -14776,11 +14776,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="G18">
-        <v>9.09</v>
+        <v>8.949</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -14788,11 +14788,11 @@
         </is>
       </c>
       <c r="I18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14804,17 +14804,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D19">
@@ -14825,11 +14825,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="G19">
-        <v>9.06</v>
+        <v>8.88</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -14837,11 +14837,11 @@
         </is>
       </c>
       <c r="I19">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14853,17 +14853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D20">
@@ -14874,11 +14874,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="G20">
-        <v>9.028</v>
+        <v>8.834</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -14886,11 +14886,11 @@
         </is>
       </c>
       <c r="I20">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14902,17 +14902,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D21">
@@ -14923,11 +14923,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="G21">
-        <v>9.022</v>
+        <v>8.75</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -14935,11 +14935,11 @@
         </is>
       </c>
       <c r="I21">
-        <v>26</v>
+        <v>188</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14951,17 +14951,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D22">
@@ -14972,23 +14972,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="G22">
-        <v>9.0216</v>
+        <v>8.73125</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I22">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -15000,12 +15000,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>9.02</v>
+        <v>8.601</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -15033,11 +15033,11 @@
         </is>
       </c>
       <c r="I23">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -15049,17 +15049,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D24">
@@ -15070,11 +15070,11 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="G24">
-        <v>9.012</v>
+        <v>8.528</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -15082,11 +15082,11 @@
         </is>
       </c>
       <c r="I24">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -15098,17 +15098,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D25">
@@ -15119,23 +15119,23 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="G25">
-        <v>8.9911</v>
+        <v>8.333</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I25">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -15147,12 +15147,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15168,11 +15168,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="G26">
-        <v>8.991</v>
+        <v>8.28</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -15180,11 +15180,11 @@
         </is>
       </c>
       <c r="I26">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -15196,17 +15196,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D27">
@@ -15217,45 +15217,45 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="G27">
-        <v>8.9816</v>
+        <v>8.278</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I27">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D28">
@@ -15266,11 +15266,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="G28">
-        <v>8.9616</v>
+        <v>8.275</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -15278,11 +15278,11 @@
         </is>
       </c>
       <c r="I28">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -15294,12 +15294,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15319,7 +15319,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>8.949</v>
+        <v>8.24425</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -15327,11 +15327,11 @@
         </is>
       </c>
       <c r="I29">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -15343,12 +15343,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15364,23 +15364,23 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="G30">
-        <v>8.91525</v>
+        <v>8.235</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I30">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -15392,17 +15392,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D31">
@@ -15413,11 +15413,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="G31">
-        <v>8.88</v>
+        <v>8.199</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -15425,11 +15425,11 @@
         </is>
       </c>
       <c r="I31">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15441,17 +15441,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Tyler Higbee</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D32">
@@ -15462,11 +15462,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="G32">
-        <v>8.864</v>
+        <v>8.18835</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -15474,11 +15474,11 @@
         </is>
       </c>
       <c r="I32">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15490,17 +15490,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Mike Evans</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D33">
@@ -15511,23 +15511,23 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="G33">
-        <v>8.834</v>
+        <v>8.188</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I33">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -15539,17 +15539,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D34">
@@ -15560,11 +15560,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="G34">
-        <v>8.825</v>
+        <v>8.1355</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -15572,11 +15572,11 @@
         </is>
       </c>
       <c r="I34">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -15588,12 +15588,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zay Flowers</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15609,11 +15609,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="G35">
-        <v>8.776</v>
+        <v>8.0934</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -15621,11 +15621,11 @@
         </is>
       </c>
       <c r="I35">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -15637,17 +15637,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D36">
@@ -15658,11 +15658,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="G36">
-        <v>8.75</v>
+        <v>7.963</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -15670,11 +15670,11 @@
         </is>
       </c>
       <c r="I36">
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -15686,17 +15686,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D37">
@@ -15707,23 +15707,23 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="G37">
-        <v>8.73125</v>
+        <v>7.953</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I37">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -15735,12 +15735,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -15756,11 +15756,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="G38">
-        <v>8.68</v>
+        <v>7.948</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -15768,11 +15768,11 @@
         </is>
       </c>
       <c r="I38">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15784,17 +15784,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Shough</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D39">
@@ -15805,11 +15805,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="G39">
-        <v>8.62625</v>
+        <v>7.873</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -15817,11 +15817,11 @@
         </is>
       </c>
       <c r="I39">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB24</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -15833,17 +15833,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D40">
@@ -15854,11 +15854,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="G40">
-        <v>8.601</v>
+        <v>7.765</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -15866,11 +15866,11 @@
         </is>
       </c>
       <c r="I40">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -15882,12 +15882,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15903,11 +15903,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="G41">
-        <v>8.6</v>
+        <v>7.711</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -15915,11 +15915,11 @@
         </is>
       </c>
       <c r="I41">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -15931,17 +15931,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D42">
@@ -15952,11 +15952,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="G42">
-        <v>8.534</v>
+        <v>7.707</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -15964,11 +15964,11 @@
         </is>
       </c>
       <c r="I42">
-        <v>36</v>
+        <v>119</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -15980,17 +15980,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D43">
@@ -16001,11 +16001,11 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="G43">
-        <v>8.528</v>
+        <v>7.634</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -16013,11 +16013,11 @@
         </is>
       </c>
       <c r="I43">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -16029,12 +16029,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -16054,7 +16054,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>8.4431</v>
+        <v>7.632</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -16062,11 +16062,11 @@
         </is>
       </c>
       <c r="I44">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -16078,17 +16078,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">Khalil Shakir</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D45">
@@ -16099,11 +16099,11 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="G45">
-        <v>8.435</v>
+        <v>7.626</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -16111,11 +16111,11 @@
         </is>
       </c>
       <c r="I45">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -16127,17 +16127,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rome Odunze</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D46">
@@ -16148,11 +16148,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="G46">
-        <v>8.405</v>
+        <v>7.62325</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -16160,11 +16160,11 @@
         </is>
       </c>
       <c r="I46">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -16176,17 +16176,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">TreVeyon Henderson</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D47">
@@ -16197,23 +16197,23 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="G47">
-        <v>8.3839</v>
+        <v>7.584</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I47">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -16225,12 +16225,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalif Raymond</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -16246,11 +16246,11 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="G48">
-        <v>8.375</v>
+        <v>7.485</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -16258,11 +16258,11 @@
         </is>
       </c>
       <c r="I48">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -16274,17 +16274,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D49">
@@ -16295,11 +16295,11 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="G49">
-        <v>8.352</v>
+        <v>7.4535</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -16307,11 +16307,11 @@
         </is>
       </c>
       <c r="I49">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16323,12 +16323,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16348,19 +16348,19 @@
         </is>
       </c>
       <c r="G50">
-        <v>8.34</v>
+        <v>7.425</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I50">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -16372,17 +16372,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D51">
@@ -16393,11 +16393,11 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="G51">
-        <v>8.335</v>
+        <v>7.37</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -16405,11 +16405,11 @@
         </is>
       </c>
       <c r="I51">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -16421,17 +16421,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D52">
@@ -16442,11 +16442,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="G52">
-        <v>8.333</v>
+        <v>7.27</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -16454,11 +16454,11 @@
         </is>
       </c>
       <c r="I52">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -16470,17 +16470,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luther Burden III</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D53">
@@ -16491,23 +16491,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="G53">
-        <v>8.328</v>
+        <v>7.2619</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I53">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -16519,12 +16519,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16540,23 +16540,23 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="G54">
-        <v>8.325</v>
+        <v>7.209</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I54">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -16568,17 +16568,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Kaytron Allen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D55">
@@ -16589,45 +16589,45 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="G55">
-        <v>8.285</v>
+        <v>7.125</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I55">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">RB60</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Keaton Mitchell</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D56">
@@ -16638,11 +16638,11 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="G56">
-        <v>8.285</v>
+        <v>6.99</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -16650,11 +16650,11 @@
         </is>
       </c>
       <c r="I56">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">RB59</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -16666,12 +16666,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16687,11 +16687,11 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="G57">
-        <v>8.28</v>
+        <v>6.88</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -16699,11 +16699,11 @@
         </is>
       </c>
       <c r="I57">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16715,17 +16715,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D58">
@@ -16736,40 +16736,40 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="G58">
-        <v>8.278</v>
+        <v>6.73975</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I58">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">MODEL_RANK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16785,11 +16785,11 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="G59">
-        <v>8.276</v>
+        <v>6.355</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -16797,11 +16797,11 @@
         </is>
       </c>
       <c r="I59">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16813,81 +16813,89 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D60">
         <v>6</v>
       </c>
-      <c r="E60">
-        <v>59</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
-        </is>
-      </c>
-      <c r="G60">
-        <v>8.275</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I60">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D61">
         <v>6</v>
       </c>
-      <c r="E61">
-        <v>60</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
-        </is>
-      </c>
-      <c r="G61">
-        <v>8.265</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -16895,77 +16903,81 @@
         </is>
       </c>
       <c r="I61">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D62">
         <v>6</v>
       </c>
-      <c r="E62">
-        <v>61</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
-        </is>
-      </c>
-      <c r="G62">
-        <v>8.24425</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I62">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16976,40 +16988,44 @@
       <c r="D63">
         <v>6</v>
       </c>
-      <c r="E63">
-        <v>62</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
-        </is>
-      </c>
-      <c r="G63">
-        <v>8.235</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I63">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -17019,169 +17035,185 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D64">
         <v>6</v>
       </c>
-      <c r="E64">
-        <v>63</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
-        </is>
-      </c>
-      <c r="G64">
-        <v>8.22685</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I64">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D65">
         <v>6</v>
       </c>
-      <c r="E65">
-        <v>64</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
-        </is>
-      </c>
-      <c r="G65">
-        <v>8.20685</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I65">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D66">
         <v>6</v>
       </c>
-      <c r="E66">
-        <v>65</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
-        </is>
-      </c>
-      <c r="G66">
-        <v>8.205</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I66">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D67">
         <v>6</v>
       </c>
-      <c r="E67">
-        <v>66</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
-        </is>
-      </c>
-      <c r="G67">
-        <v>8.199</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -17189,48 +17221,52 @@
         </is>
       </c>
       <c r="I67">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Higbee</t>
+          <t xml:space="preserve">Bijan Robinson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D68">
         <v>6</v>
       </c>
-      <c r="E68">
-        <v>67</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
-        </is>
-      </c>
-      <c r="G68">
-        <v>8.18835</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -17238,97 +17274,105 @@
         </is>
       </c>
       <c r="I68">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D69">
         <v>6</v>
       </c>
-      <c r="E69">
-        <v>68</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
-        </is>
-      </c>
-      <c r="G69">
-        <v>8.188</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I69">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D70">
         <v>6</v>
       </c>
-      <c r="E70">
-        <v>69</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
-        </is>
-      </c>
-      <c r="G70">
-        <v>8.16525</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -17336,77 +17380,81 @@
         </is>
       </c>
       <c r="I70">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D71">
         <v>6</v>
       </c>
-      <c r="E71">
-        <v>70</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
-        </is>
-      </c>
-      <c r="G71">
-        <v>8.15805</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I71">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17417,45 +17465,49 @@
       <c r="D72">
         <v>6</v>
       </c>
-      <c r="E72">
-        <v>71</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+        </is>
+      </c>
+      <c r="I72">
+        <v>97</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t xml:space="preserve">TE12</t>
         </is>
       </c>
-      <c r="G72">
-        <v>8.14</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
-        </is>
-      </c>
-      <c r="I72">
-        <v>118</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE17</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17466,16 +17518,20 @@
       <c r="D73">
         <v>6</v>
       </c>
-      <c r="E73">
-        <v>72</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
-        </is>
-      </c>
-      <c r="G73">
-        <v>8.1355</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -17483,48 +17539,52 @@
         </is>
       </c>
       <c r="I73">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D74">
         <v>6</v>
       </c>
-      <c r="E74">
-        <v>73</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
-        </is>
-      </c>
-      <c r="G74">
-        <v>8.135</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -17532,48 +17592,52 @@
         </is>
       </c>
       <c r="I74">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D75">
         <v>6</v>
       </c>
-      <c r="E75">
-        <v>74</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
-        </is>
-      </c>
-      <c r="G75">
-        <v>8.11835</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -17581,48 +17645,52 @@
         </is>
       </c>
       <c r="I75">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D76">
         <v>6</v>
       </c>
-      <c r="E76">
-        <v>75</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
-        </is>
-      </c>
-      <c r="G76">
-        <v>8.117</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -17630,28 +17698,28 @@
         </is>
       </c>
       <c r="I76">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -17662,94 +17730,102 @@
       <c r="D77">
         <v>6</v>
       </c>
-      <c r="E77">
-        <v>76</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
-        </is>
-      </c>
-      <c r="G77">
-        <v>8.0934</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I77">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D78">
         <v>6</v>
       </c>
-      <c r="E78">
-        <v>77</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
-        </is>
-      </c>
-      <c r="G78">
-        <v>8.069</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I78">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17760,16 +17836,20 @@
       <c r="D79">
         <v>6</v>
       </c>
-      <c r="E79">
-        <v>78</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
-        </is>
-      </c>
-      <c r="G79">
-        <v>8.055</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -17777,48 +17857,52 @@
         </is>
       </c>
       <c r="I79">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D80">
         <v>6</v>
       </c>
-      <c r="E80">
-        <v>79</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
-        </is>
-      </c>
-      <c r="G80">
-        <v>8.003</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -17826,48 +17910,52 @@
         </is>
       </c>
       <c r="I80">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D81">
         <v>6</v>
       </c>
-      <c r="E81">
-        <v>80</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
-        </is>
-      </c>
-      <c r="G81">
-        <v>7.963</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -17875,48 +17963,52 @@
         </is>
       </c>
       <c r="I81">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D82">
         <v>6</v>
       </c>
-      <c r="E82">
-        <v>81</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
-        </is>
-      </c>
-      <c r="G82">
-        <v>7.953</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -17924,28 +18016,28 @@
         </is>
       </c>
       <c r="I82">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -17956,16 +18048,20 @@
       <c r="D83">
         <v>6</v>
       </c>
-      <c r="E83">
-        <v>82</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
-        </is>
-      </c>
-      <c r="G83">
-        <v>7.948</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -17973,28 +18069,28 @@
         </is>
       </c>
       <c r="I83">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -18005,65 +18101,73 @@
       <c r="D84">
         <v>6</v>
       </c>
-      <c r="E84">
-        <v>83</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
-        </is>
-      </c>
-      <c r="G84">
-        <v>7.939</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I84">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D85">
         <v>6</v>
       </c>
-      <c r="E85">
-        <v>84</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
-        </is>
-      </c>
-      <c r="G85">
-        <v>7.935</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -18071,28 +18175,28 @@
         </is>
       </c>
       <c r="I85">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -18103,16 +18207,20 @@
       <c r="D86">
         <v>6</v>
       </c>
-      <c r="E86">
-        <v>85</v>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
-        </is>
-      </c>
-      <c r="G86">
-        <v>7.933</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -18120,48 +18228,52 @@
         </is>
       </c>
       <c r="I86">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D87">
         <v>6</v>
       </c>
-      <c r="E87">
-        <v>86</v>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
-        </is>
-      </c>
-      <c r="G87">
-        <v>7.892</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -18169,48 +18281,52 @@
         </is>
       </c>
       <c r="I87">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D88">
         <v>6</v>
       </c>
-      <c r="E88">
-        <v>87</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
-        </is>
-      </c>
-      <c r="G88">
-        <v>7.873</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -18218,28 +18334,28 @@
         </is>
       </c>
       <c r="I88">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -18250,16 +18366,20 @@
       <c r="D89">
         <v>6</v>
       </c>
-      <c r="E89">
-        <v>88</v>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
-        </is>
-      </c>
-      <c r="G89">
-        <v>7.856</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -18267,48 +18387,52 @@
         </is>
       </c>
       <c r="I89">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D90">
         <v>6</v>
       </c>
-      <c r="E90">
-        <v>89</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
-        </is>
-      </c>
-      <c r="G90">
-        <v>7.791</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -18316,48 +18440,52 @@
         </is>
       </c>
       <c r="I90">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wan'Dale Robinson</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D91">
         <v>6</v>
       </c>
-      <c r="E91">
-        <v>90</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
-        </is>
-      </c>
-      <c r="G91">
-        <v>7.776</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -18365,28 +18493,28 @@
         </is>
       </c>
       <c r="I91">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR68</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -18397,65 +18525,73 @@
       <c r="D92">
         <v>6</v>
       </c>
-      <c r="E92">
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+        </is>
+      </c>
+      <c r="I92">
         <v>91</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE18</t>
-        </is>
-      </c>
-      <c r="G92">
-        <v>7.765</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
-        </is>
-      </c>
-      <c r="I92">
-        <v>144</v>
-      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rhamondre Stevenson</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D93">
         <v>6</v>
       </c>
-      <c r="E93">
-        <v>92</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
-        </is>
-      </c>
-      <c r="G93">
-        <v>7.761</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -18463,48 +18599,52 @@
         </is>
       </c>
       <c r="I93">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D94">
         <v>6</v>
       </c>
-      <c r="E94">
-        <v>93</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
-        </is>
-      </c>
-      <c r="G94">
-        <v>7.711</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -18512,28 +18652,28 @@
         </is>
       </c>
       <c r="I94">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -18544,16 +18684,20 @@
       <c r="D95">
         <v>6</v>
       </c>
-      <c r="E95">
-        <v>94</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
-        </is>
-      </c>
-      <c r="G95">
-        <v>7.707</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -18561,77 +18705,81 @@
         </is>
       </c>
       <c r="I95">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D96">
         <v>6</v>
       </c>
-      <c r="E96">
-        <v>95</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
-        </is>
-      </c>
-      <c r="G96">
-        <v>7.641</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I96">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -18642,45 +18790,49 @@
       <c r="D97">
         <v>6</v>
       </c>
-      <c r="E97">
-        <v>96</v>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
-        </is>
-      </c>
-      <c r="G97">
-        <v>7.634</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I97">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -18691,45 +18843,49 @@
       <c r="D98">
         <v>6</v>
       </c>
-      <c r="E98">
-        <v>97</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
-        </is>
-      </c>
-      <c r="G98">
-        <v>7.632</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I98">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khalil Shakir</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -18740,45 +18896,49 @@
       <c r="D99">
         <v>6</v>
       </c>
-      <c r="E99">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+        </is>
+      </c>
+      <c r="I99">
         <v>98</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WR41</t>
-        </is>
-      </c>
-      <c r="G99">
-        <v>7.626</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
-        </is>
-      </c>
-      <c r="I99">
-        <v>117</v>
-      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -18789,16 +18949,20 @@
       <c r="D100">
         <v>6</v>
       </c>
-      <c r="E100">
-        <v>99</v>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
-        </is>
-      </c>
-      <c r="G100">
-        <v>7.62325</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -18806,28 +18970,28 @@
         </is>
       </c>
       <c r="I100">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -18838,16 +19002,20 @@
       <c r="D101">
         <v>6</v>
       </c>
-      <c r="E101">
-        <v>100</v>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
-        </is>
-      </c>
-      <c r="G101">
-        <v>7.584</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -18855,77 +19023,81 @@
         </is>
       </c>
       <c r="I101">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D102">
         <v>6</v>
       </c>
-      <c r="E102">
-        <v>101</v>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
-        </is>
-      </c>
-      <c r="G102">
-        <v>7.58</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I102">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18936,16 +19108,20 @@
       <c r="D103">
         <v>6</v>
       </c>
-      <c r="E103">
-        <v>102</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
-        </is>
-      </c>
-      <c r="G103">
-        <v>7.52865</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -18953,28 +19129,28 @@
         </is>
       </c>
       <c r="I103">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18985,16 +19161,20 @@
       <c r="D104">
         <v>6</v>
       </c>
-      <c r="E104">
-        <v>103</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
-        </is>
-      </c>
-      <c r="G104">
-        <v>7.485</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -19002,126 +19182,134 @@
         </is>
       </c>
       <c r="I104">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D105">
         <v>6</v>
       </c>
-      <c r="E105">
-        <v>104</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
-        </is>
-      </c>
-      <c r="G105">
-        <v>7.485</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I105">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D106">
         <v>6</v>
       </c>
-      <c r="E106">
-        <v>105</v>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
-        </is>
-      </c>
-      <c r="G106">
-        <v>7.456</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I106">
-        <v>134</v>
+        <v>40</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -19132,16 +19320,20 @@
       <c r="D107">
         <v>6</v>
       </c>
-      <c r="E107">
-        <v>106</v>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
-        </is>
-      </c>
-      <c r="G107">
-        <v>7.4535</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -19149,97 +19341,105 @@
         </is>
       </c>
       <c r="I107">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D108">
         <v>6</v>
       </c>
-      <c r="E108">
-        <v>107</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
-        </is>
-      </c>
-      <c r="G108">
-        <v>7.425</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I108">
-        <v>161</v>
+        <v>36</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D109">
         <v>6</v>
       </c>
-      <c r="E109">
-        <v>108</v>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
-        </is>
-      </c>
-      <c r="G109">
-        <v>7.37</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -19247,28 +19447,28 @@
         </is>
       </c>
       <c r="I109">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19279,16 +19479,20 @@
       <c r="D110">
         <v>6</v>
       </c>
-      <c r="E110">
-        <v>109</v>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
-        </is>
-      </c>
-      <c r="G110">
-        <v>7.3335</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -19296,48 +19500,52 @@
         </is>
       </c>
       <c r="I110">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D111">
         <v>6</v>
       </c>
-      <c r="E111">
-        <v>110</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
-        </is>
-      </c>
-      <c r="G111">
-        <v>7.3135</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -19345,48 +19553,52 @@
         </is>
       </c>
       <c r="I111">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D112">
         <v>6</v>
       </c>
-      <c r="E112">
-        <v>111</v>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
-        </is>
-      </c>
-      <c r="G112">
-        <v>7.27</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -19394,77 +19606,81 @@
         </is>
       </c>
       <c r="I112">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D113">
         <v>6</v>
       </c>
-      <c r="E113">
-        <v>112</v>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
-        </is>
-      </c>
-      <c r="G113">
-        <v>7.2619</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I113">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrone Tracy Jr.</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -19475,143 +19691,155 @@
       <c r="D114">
         <v>6</v>
       </c>
-      <c r="E114">
-        <v>113</v>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
-        </is>
-      </c>
-      <c r="G114">
-        <v>7.238</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I114">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB56</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D115">
         <v>6</v>
       </c>
-      <c r="E115">
-        <v>114</v>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
-        </is>
-      </c>
-      <c r="G115">
-        <v>7.209</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I115">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaytron Allen</t>
+          <t xml:space="preserve">Ja'Marr Chase</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D116">
         <v>6</v>
       </c>
-      <c r="E116">
-        <v>115</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
-        </is>
-      </c>
-      <c r="G116">
-        <v>7.125</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I116">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB60</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keaton Mitchell</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -19622,45 +19850,49 @@
       <c r="D117">
         <v>6</v>
       </c>
-      <c r="E117">
-        <v>116</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
-        </is>
-      </c>
-      <c r="G117">
-        <v>6.99</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I117">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB59</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19671,45 +19903,49 @@
       <c r="D118">
         <v>6</v>
       </c>
-      <c r="E118">
-        <v>117</v>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
-        </is>
-      </c>
-      <c r="G118">
-        <v>6.9</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I118">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -19720,16 +19956,20 @@
       <c r="D119">
         <v>6</v>
       </c>
-      <c r="E119">
-        <v>118</v>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>6.885</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -19737,28 +19977,28 @@
         </is>
       </c>
       <c r="I119">
-        <v>183</v>
+        <v>2</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -19769,16 +20009,20 @@
       <c r="D120">
         <v>6</v>
       </c>
-      <c r="E120">
-        <v>119</v>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>6.88</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -19786,48 +20030,52 @@
         </is>
       </c>
       <c r="I120">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D121">
         <v>6</v>
       </c>
-      <c r="E121">
-        <v>120</v>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
-        </is>
-      </c>
-      <c r="G121">
-        <v>6.73975</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -19835,146 +20083,158 @@
         </is>
       </c>
       <c r="I121">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D122">
         <v>6</v>
       </c>
-      <c r="E122">
-        <v>121</v>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
-        </is>
-      </c>
-      <c r="G122">
-        <v>6.595</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I122">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D123">
         <v>6</v>
       </c>
-      <c r="E123">
-        <v>122</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
-        </is>
-      </c>
-      <c r="G123">
-        <v>6.401</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I123">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D124">
         <v>6</v>
       </c>
-      <c r="E124">
-        <v>123</v>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
-        </is>
-      </c>
-      <c r="G124">
-        <v>6.355</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -19982,33 +20242,33 @@
         </is>
       </c>
       <c r="I124">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D125">
@@ -20035,11 +20295,11 @@
         </is>
       </c>
       <c r="I125">
-        <v>156</v>
+        <v>33</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -20051,17 +20311,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D126">
@@ -20084,32 +20344,32 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I126">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -20137,37 +20397,37 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I127">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amon-Ra St. Brown</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D128">
@@ -20190,37 +20450,37 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I128">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D129">
@@ -20243,15 +20503,15 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I129">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20263,17 +20523,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D130">
@@ -20296,27 +20556,27 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I130">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -20326,7 +20586,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D131">
@@ -20353,11 +20613,11 @@
         </is>
       </c>
       <c r="I131">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -20369,12 +20629,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -20402,37 +20662,37 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I132">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D133">
@@ -20459,33 +20719,33 @@
         </is>
       </c>
       <c r="I133">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">Jeremiyah Love</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D134">
@@ -20508,32 +20768,32 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I134">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -20565,33 +20825,33 @@
         </is>
       </c>
       <c r="I135">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D136">
@@ -20614,32 +20874,32 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I136">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20671,33 +20931,33 @@
         </is>
       </c>
       <c r="I137">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D138">
@@ -20720,37 +20980,37 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I138">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D139">
@@ -20773,37 +21033,37 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I139">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D140">
@@ -20826,37 +21086,37 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I140">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Jordyn Tyson</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D141">
@@ -20879,37 +21139,37 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I141">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">WR73</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D142">
@@ -20932,32 +21192,32 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I142">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -20985,32 +21245,32 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I143">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -21038,37 +21298,37 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I144">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D145">
@@ -21095,11 +21355,11 @@
         </is>
       </c>
       <c r="I145">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -21111,17 +21371,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">Kalif Raymond</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D146">
@@ -21148,11 +21408,11 @@
         </is>
       </c>
       <c r="I146">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -21164,17 +21424,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D147">
@@ -21197,37 +21457,37 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I147">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D148">
@@ -21254,11 +21514,11 @@
         </is>
       </c>
       <c r="I148">
-        <v>180</v>
+        <v>94</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21270,17 +21530,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja'Marr Chase</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D149">
@@ -21307,28 +21567,28 @@
         </is>
       </c>
       <c r="I149">
-        <v>3</v>
+        <v>141</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -21356,37 +21616,37 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I150">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D151">
@@ -21409,32 +21669,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I151">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahmyr Gibbs</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21462,37 +21722,37 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I152">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D153">
@@ -21519,11 +21779,11 @@
         </is>
       </c>
       <c r="I153">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -21535,12 +21795,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21568,37 +21828,37 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I154">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">Lamar Jackson</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D155">
@@ -21621,37 +21881,37 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I155">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">Luther Burden III</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D156">
@@ -21678,28 +21938,28 @@
         </is>
       </c>
       <c r="I156">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -21727,37 +21987,37 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I157">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D158">
@@ -21780,32 +22040,32 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I158">
-        <v>148</v>
+        <v>99</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Higgins</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -21833,32 +22093,32 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I159">
-        <v>196</v>
+        <v>56</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR75</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Reed</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -21886,37 +22146,37 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I160">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D161">
@@ -21943,33 +22203,33 @@
         </is>
       </c>
       <c r="I161">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D162">
@@ -21992,37 +22252,37 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I162">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D163">
@@ -22045,32 +22305,32 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I163">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -22102,33 +22362,33 @@
         </is>
       </c>
       <c r="I164">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D165">
@@ -22155,11 +22415,11 @@
         </is>
       </c>
       <c r="I165">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -22171,17 +22431,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D166">
@@ -22204,37 +22464,37 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I166">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D167">
@@ -22257,15 +22517,15 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I167">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -22277,17 +22537,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Mason</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D168">
@@ -22310,37 +22570,37 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I168">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordyn Tyson</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D169">
@@ -22363,15 +22623,15 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I169">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR73</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -22383,17 +22643,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D170">
@@ -22420,11 +22680,11 @@
         </is>
       </c>
       <c r="I170">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -22436,12 +22696,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -22473,33 +22733,33 @@
         </is>
       </c>
       <c r="I171">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D172">
@@ -22522,37 +22782,37 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I172">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D173">
@@ -22579,33 +22839,33 @@
         </is>
       </c>
       <c r="I173">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Jackson</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D174">
@@ -22628,37 +22888,37 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I174">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D175">
@@ -22681,32 +22941,32 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I175">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">Rome Odunze</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -22738,33 +22998,33 @@
         </is>
       </c>
       <c r="I176">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D177">
@@ -22791,28 +23051,28 @@
         </is>
       </c>
       <c r="I177">
-        <v>190</v>
+        <v>136</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -22840,37 +23100,37 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I178">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D179">
@@ -22893,37 +23153,37 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I179">
-        <v>142</v>
+        <v>68</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D180">
@@ -22946,32 +23206,32 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I180">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -22999,32 +23259,32 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I181">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -23052,37 +23312,37 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I182">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D183">
@@ -23105,32 +23365,32 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I183">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -23158,32 +23418,32 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I184">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -23215,11 +23475,11 @@
         </is>
       </c>
       <c r="I185">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -23231,12 +23491,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -23268,11 +23528,11 @@
         </is>
       </c>
       <c r="I186">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23284,17 +23544,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D187">
@@ -23317,37 +23577,37 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I187">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D188">
@@ -23370,32 +23630,32 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I188">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -23423,37 +23683,37 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I189">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Trevor Lawrence</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D190">
@@ -23476,37 +23736,37 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I190">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D191">
@@ -23529,37 +23789,37 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I191">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Tyler Shough</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D192">
@@ -23586,33 +23846,33 @@
         </is>
       </c>
       <c r="I192">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">QB24</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Tyler Warren</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D193">
@@ -23635,15 +23895,15 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I193">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -23655,17 +23915,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D194">
@@ -23688,37 +23948,37 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I194">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">RB56</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trevor Lawrence</t>
+          <t xml:space="preserve">Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D195">
@@ -23745,11 +24005,11 @@
         </is>
       </c>
       <c r="I195">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">WR68</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -23761,17 +24021,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Warren</t>
+          <t xml:space="preserve">Woody Marks</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D196">
@@ -23794,32 +24054,32 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I196">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woody Marks</t>
+          <t xml:space="preserve">Zach Charbonnet</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -23847,37 +24107,37 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I197">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">RB66</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zach Charbonnet</t>
+          <t xml:space="preserve">Zay Flowers</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D198">
@@ -23900,20 +24160,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I198">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB66</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -13971,17 +13971,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen</t>
+          <t xml:space="preserve">Christian McCaffrey</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D2">
@@ -13992,11 +13992,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="G2">
-        <v>9.815</v>
+        <v>9.34</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -14004,11 +14004,11 @@
         </is>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -14020,17 +14020,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes II</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D3">
@@ -14041,11 +14041,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="G3">
-        <v>9.683</v>
+        <v>9.286</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -14053,11 +14053,11 @@
         </is>
       </c>
       <c r="I3">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -14069,17 +14069,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D4">
@@ -14090,11 +14090,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="G4">
-        <v>9.386</v>
+        <v>9.276</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -14102,11 +14102,11 @@
         </is>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -14118,7 +14118,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian McCaffrey</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D5">
@@ -14139,11 +14139,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="G5">
-        <v>9.34</v>
+        <v>9.06</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -14151,11 +14151,11 @@
         </is>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -14167,7 +14167,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14188,11 +14188,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="G6">
-        <v>9.286</v>
+        <v>9.028</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -14200,11 +14200,11 @@
         </is>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -14216,12 +14216,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Daniels</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>9.276</v>
+        <v>9.012</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -14249,11 +14249,11 @@
         </is>
       </c>
       <c r="I7">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -14265,17 +14265,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D8">
@@ -14286,11 +14286,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="G8">
-        <v>9.268</v>
+        <v>8.75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -14298,11 +14298,11 @@
         </is>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14314,17 +14314,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D9">
@@ -14335,11 +14335,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="G9">
-        <v>9.26</v>
+        <v>8.601</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14347,11 +14347,11 @@
         </is>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14363,12 +14363,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14384,11 +14384,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="G10">
-        <v>9.256</v>
+        <v>8.28</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14396,11 +14396,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14412,17 +14412,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Herbert</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D11">
@@ -14433,11 +14433,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="G11">
-        <v>9.185</v>
+        <v>8.199</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -14445,11 +14445,11 @@
         </is>
       </c>
       <c r="I11">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14461,7 +14461,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">Mike Evans</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -14471,7 +14471,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D12">
@@ -14482,23 +14482,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="G12">
-        <v>9.06</v>
+        <v>8.188</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I12">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14510,17 +14510,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D13">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="G13">
-        <v>9.028</v>
+        <v>8.1355</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14543,11 +14543,11 @@
         </is>
       </c>
       <c r="I13">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14559,17 +14559,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D14">
@@ -14580,11 +14580,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="G14">
-        <v>9.022</v>
+        <v>7.963</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -14592,11 +14592,11 @@
         </is>
       </c>
       <c r="I14">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14608,17 +14608,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D15">
@@ -14629,11 +14629,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="G15">
-        <v>9.02</v>
+        <v>7.953</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14641,11 +14641,11 @@
         </is>
       </c>
       <c r="I15">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14657,17 +14657,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D16">
@@ -14678,11 +14678,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="G16">
-        <v>9.012</v>
+        <v>7.948</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -14690,11 +14690,11 @@
         </is>
       </c>
       <c r="I16">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14706,17 +14706,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D17">
@@ -14727,11 +14727,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="G17">
-        <v>8.9616</v>
+        <v>7.711</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -14739,11 +14739,11 @@
         </is>
       </c>
       <c r="I17">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -14755,12 +14755,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14776,11 +14776,11 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="G18">
-        <v>8.949</v>
+        <v>7.634</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -14788,11 +14788,11 @@
         </is>
       </c>
       <c r="I18">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14804,17 +14804,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D19">
@@ -14825,11 +14825,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="G19">
-        <v>8.88</v>
+        <v>7.584</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -14837,11 +14837,11 @@
         </is>
       </c>
       <c r="I19">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14853,17 +14853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D20">
@@ -14874,23 +14874,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="G20">
-        <v>8.834</v>
+        <v>7.425</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I20">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14902,17 +14902,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D21">
@@ -14923,11 +14923,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="G21">
-        <v>8.75</v>
+        <v>7.27</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -14935,11 +14935,11 @@
         </is>
       </c>
       <c r="I21">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14951,17 +14951,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D22">
@@ -14972,23 +14972,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="G22">
-        <v>8.73125</v>
+        <v>7.2619</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I22">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -15000,17 +15000,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D23">
@@ -15021,23 +15021,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="G23">
-        <v>8.601</v>
+        <v>7.209</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I23">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -15049,17 +15049,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Kaytron Allen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D24">
@@ -15070,45 +15070,45 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="G24">
-        <v>8.528</v>
+        <v>7.125</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I24">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">RB60</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D25">
@@ -15119,11 +15119,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="G25">
-        <v>8.333</v>
+        <v>6.73975</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -15131,11 +15131,11 @@
         </is>
       </c>
       <c r="I25">
-        <v>111</v>
+        <v>187</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -15147,12 +15147,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15163,261 +15163,285 @@
       <c r="D26">
         <v>6</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUESTIONABLE</t>
+        </is>
+      </c>
+      <c r="I26">
         <v>25</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WR7</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>8.28</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
-        </is>
-      </c>
-      <c r="I26">
-        <v>50</v>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
-      <c r="E27">
-        <v>26</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>8.278</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I27">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
-      <c r="E28">
-        <v>27</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>8.275</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I28">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D29">
         <v>6</v>
       </c>
-      <c r="E29">
-        <v>28</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>8.24425</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I29">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D30">
         <v>6</v>
       </c>
-      <c r="E30">
-        <v>29</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>8.235</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I30">
-        <v>83</v>
+        <v>184</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D31">
         <v>6</v>
       </c>
-      <c r="E31">
-        <v>30</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>8.199</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -15425,48 +15449,52 @@
         </is>
       </c>
       <c r="I31">
-        <v>113</v>
+        <v>6</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Higbee</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D32">
         <v>6</v>
       </c>
-      <c r="E32">
-        <v>31</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
-        </is>
-      </c>
-      <c r="G32">
-        <v>8.18835</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -15474,77 +15502,81 @@
         </is>
       </c>
       <c r="I32">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D33">
         <v>6</v>
       </c>
-      <c r="E33">
-        <v>32</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
-        </is>
-      </c>
-      <c r="G33">
-        <v>8.188</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I33">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15555,16 +15587,20 @@
       <c r="D34">
         <v>6</v>
       </c>
-      <c r="E34">
-        <v>33</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
-        </is>
-      </c>
-      <c r="G34">
-        <v>8.1355</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -15572,48 +15608,52 @@
         </is>
       </c>
       <c r="I34">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Bijan Robinson</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D35">
         <v>6</v>
       </c>
-      <c r="E35">
-        <v>34</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>8.0934</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -15621,48 +15661,52 @@
         </is>
       </c>
       <c r="I35">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D36">
         <v>6</v>
       </c>
-      <c r="E36">
-        <v>35</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
-        </is>
-      </c>
-      <c r="G36">
-        <v>7.963</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -15670,48 +15714,52 @@
         </is>
       </c>
       <c r="I36">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D37">
         <v>6</v>
       </c>
-      <c r="E37">
-        <v>36</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
-        </is>
-      </c>
-      <c r="G37">
-        <v>7.953</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -15719,48 +15767,52 @@
         </is>
       </c>
       <c r="I37">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D38">
         <v>6</v>
       </c>
-      <c r="E38">
-        <v>37</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
-        </is>
-      </c>
-      <c r="G38">
-        <v>7.948</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -15768,77 +15820,81 @@
         </is>
       </c>
       <c r="I38">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D39">
         <v>6</v>
       </c>
-      <c r="E39">
-        <v>38</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
-        </is>
-      </c>
-      <c r="G39">
-        <v>7.873</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I39">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -15849,16 +15905,20 @@
       <c r="D40">
         <v>6</v>
       </c>
-      <c r="E40">
-        <v>39</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
-        </is>
-      </c>
-      <c r="G40">
-        <v>7.765</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -15866,48 +15926,52 @@
         </is>
       </c>
       <c r="I40">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D41">
         <v>6</v>
       </c>
-      <c r="E41">
-        <v>40</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
-        </is>
-      </c>
-      <c r="G41">
-        <v>7.711</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -15915,48 +15979,52 @@
         </is>
       </c>
       <c r="I41">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D42">
         <v>6</v>
       </c>
-      <c r="E42">
-        <v>41</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>7.707</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -15964,48 +16032,52 @@
         </is>
       </c>
       <c r="I42">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D43">
         <v>6</v>
       </c>
-      <c r="E43">
-        <v>42</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
-        </is>
-      </c>
-      <c r="G43">
-        <v>7.634</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -16013,48 +16085,52 @@
         </is>
       </c>
       <c r="I43">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D44">
         <v>6</v>
       </c>
-      <c r="E44">
-        <v>43</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
-        </is>
-      </c>
-      <c r="G44">
-        <v>7.632</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -16062,48 +16138,52 @@
         </is>
       </c>
       <c r="I44">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khalil Shakir</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D45">
         <v>6</v>
       </c>
-      <c r="E45">
-        <v>44</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
-        </is>
-      </c>
-      <c r="G45">
-        <v>7.626</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -16111,146 +16191,158 @@
         </is>
       </c>
       <c r="I45">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D46">
         <v>6</v>
       </c>
-      <c r="E46">
-        <v>45</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
-        </is>
-      </c>
-      <c r="G46">
-        <v>7.62325</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I46">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D47">
         <v>6</v>
       </c>
-      <c r="E47">
-        <v>46</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
-        </is>
-      </c>
-      <c r="G47">
-        <v>7.584</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I47">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D48">
         <v>6</v>
       </c>
-      <c r="E48">
-        <v>47</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
-        </is>
-      </c>
-      <c r="G48">
-        <v>7.485</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -16258,48 +16350,52 @@
         </is>
       </c>
       <c r="I48">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D49">
         <v>6</v>
       </c>
-      <c r="E49">
-        <v>48</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
-        </is>
-      </c>
-      <c r="G49">
-        <v>7.4535</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -16307,28 +16403,28 @@
         </is>
       </c>
       <c r="I49">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16339,65 +16435,73 @@
       <c r="D50">
         <v>6</v>
       </c>
-      <c r="E50">
-        <v>49</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
-        </is>
-      </c>
-      <c r="G50">
-        <v>7.425</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I50">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D51">
         <v>6</v>
       </c>
-      <c r="E51">
-        <v>50</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
-        </is>
-      </c>
-      <c r="G51">
-        <v>7.37</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -16405,48 +16509,52 @@
         </is>
       </c>
       <c r="I51">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D52">
         <v>6</v>
       </c>
-      <c r="E52">
-        <v>51</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
-        </is>
-      </c>
-      <c r="G52">
-        <v>7.27</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -16454,126 +16562,134 @@
         </is>
       </c>
       <c r="I52">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D53">
         <v>6</v>
       </c>
-      <c r="E53">
-        <v>52</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
-        </is>
-      </c>
-      <c r="G53">
-        <v>7.2619</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I53">
-        <v>162</v>
+        <v>27</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D54">
         <v>6</v>
       </c>
-      <c r="E54">
-        <v>53</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
-        </is>
-      </c>
-      <c r="G54">
-        <v>7.209</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I54">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaytron Allen</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16584,65 +16700,73 @@
       <c r="D55">
         <v>6</v>
       </c>
-      <c r="E55">
-        <v>54</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
-        </is>
-      </c>
-      <c r="G55">
-        <v>7.125</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I55">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB60</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keaton Mitchell</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D56">
         <v>6</v>
       </c>
-      <c r="E56">
-        <v>55</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
-        </is>
-      </c>
-      <c r="G56">
-        <v>6.99</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -16650,48 +16774,52 @@
         </is>
       </c>
       <c r="I56">
-        <v>172</v>
+        <v>41</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB59</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D57">
         <v>6</v>
       </c>
-      <c r="E57">
-        <v>56</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
-        </is>
-      </c>
-      <c r="G57">
-        <v>6.88</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -16699,48 +16827,52 @@
         </is>
       </c>
       <c r="I57">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D58">
         <v>6</v>
       </c>
-      <c r="E58">
-        <v>57</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
-        </is>
-      </c>
-      <c r="G58">
-        <v>6.73975</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -16748,48 +16880,52 @@
         </is>
       </c>
       <c r="I58">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D59">
         <v>6</v>
       </c>
-      <c r="E59">
-        <v>58</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
-        </is>
-      </c>
-      <c r="G59">
-        <v>6.355</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -16797,33 +16933,33 @@
         </is>
       </c>
       <c r="I59">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D60">
@@ -16846,15 +16982,15 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I60">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16866,17 +17002,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D61">
@@ -16903,33 +17039,33 @@
         </is>
       </c>
       <c r="I61">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D62">
@@ -16952,27 +17088,27 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I62">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16982,7 +17118,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D63">
@@ -17005,37 +17141,37 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I63">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D64">
@@ -17062,11 +17198,11 @@
         </is>
       </c>
       <c r="I64">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17078,17 +17214,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amon-Ra St. Brown</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D65">
@@ -17115,33 +17251,33 @@
         </is>
       </c>
       <c r="I65">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D66">
@@ -17164,32 +17300,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I66">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -17217,32 +17353,32 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I67">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bijan Robinson</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -17270,37 +17406,37 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I68">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D69">
@@ -17323,37 +17459,37 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I69">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D70">
@@ -17380,11 +17516,11 @@
         </is>
       </c>
       <c r="I70">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -17396,12 +17532,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17429,37 +17565,37 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I71">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D72">
@@ -17486,11 +17622,11 @@
         </is>
       </c>
       <c r="I72">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -17502,17 +17638,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D73">
@@ -17539,11 +17675,11 @@
         </is>
       </c>
       <c r="I73">
-        <v>171</v>
+        <v>23</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -17555,12 +17691,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17588,37 +17724,37 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I74">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D75">
@@ -17645,11 +17781,11 @@
         </is>
       </c>
       <c r="I75">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -17661,17 +17797,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D76">
@@ -17698,11 +17834,11 @@
         </is>
       </c>
       <c r="I76">
-        <v>194</v>
+        <v>93</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -17714,12 +17850,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -17747,32 +17883,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I77">
-        <v>127</v>
+        <v>16</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17800,15 +17936,15 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I78">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -17820,12 +17956,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17857,11 +17993,11 @@
         </is>
       </c>
       <c r="I79">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -17873,12 +18009,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -17910,11 +18046,11 @@
         </is>
       </c>
       <c r="I80">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -17926,12 +18062,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -17963,28 +18099,28 @@
         </is>
       </c>
       <c r="I81">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -18016,33 +18152,33 @@
         </is>
       </c>
       <c r="I82">
-        <v>174</v>
+        <v>30</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D83">
@@ -18069,11 +18205,11 @@
         </is>
       </c>
       <c r="I83">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -18085,17 +18221,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D84">
@@ -18118,15 +18254,15 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I84">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -18138,17 +18274,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D85">
@@ -18175,11 +18311,11 @@
         </is>
       </c>
       <c r="I85">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -18191,17 +18327,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D86">
@@ -18228,11 +18364,11 @@
         </is>
       </c>
       <c r="I86">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -18244,17 +18380,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D87">
@@ -18277,32 +18413,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I87">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -18334,11 +18470,11 @@
         </is>
       </c>
       <c r="I88">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -18350,12 +18486,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">Ja'Marr Chase</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -18387,28 +18523,28 @@
         </is>
       </c>
       <c r="I89">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -18436,37 +18572,37 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I90">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D91">
@@ -18489,37 +18625,37 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I91">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D92">
@@ -18546,33 +18682,33 @@
         </is>
       </c>
       <c r="I92">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D93">
@@ -18599,11 +18735,11 @@
         </is>
       </c>
       <c r="I93">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -18615,12 +18751,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -18652,11 +18788,11 @@
         </is>
       </c>
       <c r="I94">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -18668,17 +18804,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D95">
@@ -18701,37 +18837,37 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I95">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D96">
@@ -18754,37 +18890,37 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I96">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D97">
@@ -18807,37 +18943,37 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I97">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D98">
@@ -18860,37 +18996,37 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I98">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D99">
@@ -18917,11 +19053,11 @@
         </is>
       </c>
       <c r="I99">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -18933,17 +19069,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D100">
@@ -18970,33 +19106,33 @@
         </is>
       </c>
       <c r="I100">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D101">
@@ -19023,28 +19159,28 @@
         </is>
       </c>
       <c r="I101">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -19076,11 +19212,11 @@
         </is>
       </c>
       <c r="I102">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -19092,17 +19228,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D103">
@@ -19125,32 +19261,32 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I103">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -19178,32 +19314,32 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I104">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -19231,37 +19367,37 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I105">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D106">
@@ -19288,11 +19424,11 @@
         </is>
       </c>
       <c r="I106">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -19304,12 +19440,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -19341,11 +19477,11 @@
         </is>
       </c>
       <c r="I107">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -19357,17 +19493,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D108">
@@ -19394,33 +19530,33 @@
         </is>
       </c>
       <c r="I108">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Jeremiyah Love</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D109">
@@ -19443,37 +19579,37 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I109">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D110">
@@ -19500,33 +19636,33 @@
         </is>
       </c>
       <c r="I110">
-        <v>146</v>
+        <v>53</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D111">
@@ -19549,37 +19685,37 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I111">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D112">
@@ -19606,11 +19742,11 @@
         </is>
       </c>
       <c r="I112">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -19622,17 +19758,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D113">
@@ -19655,37 +19791,37 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I113">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D114">
@@ -19708,15 +19844,15 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I114">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -19728,12 +19864,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -19761,32 +19897,32 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I115">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja'Marr Chase</t>
+          <t xml:space="preserve">Jordyn Tyson</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -19814,37 +19950,37 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I116">
-        <v>3</v>
+        <v>193</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">WR73</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Josh Allen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D117">
@@ -19867,37 +20003,37 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I117">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D118">
@@ -19920,32 +20056,32 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I118">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahmyr Gibbs</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -19973,37 +20109,37 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I119">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Justin Herbert</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D120">
@@ -20030,11 +20166,11 @@
         </is>
       </c>
       <c r="I120">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -20046,12 +20182,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -20083,33 +20219,33 @@
         </is>
       </c>
       <c r="I121">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D122">
@@ -20132,37 +20268,37 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I122">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Kalif Raymond</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D123">
@@ -20185,15 +20321,15 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I123">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -20205,17 +20341,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D124">
@@ -20242,11 +20378,11 @@
         </is>
       </c>
       <c r="I124">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -20258,17 +20394,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">Keaton Mitchell</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D125">
@@ -20295,33 +20431,33 @@
         </is>
       </c>
       <c r="I125">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">RB59</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D126">
@@ -20348,33 +20484,33 @@
         </is>
       </c>
       <c r="I126">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D127">
@@ -20401,11 +20537,11 @@
         </is>
       </c>
       <c r="I127">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -20417,17 +20553,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D128">
@@ -20450,37 +20586,37 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I128">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Higgins</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D129">
@@ -20503,37 +20639,37 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I129">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR75</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Reed</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D130">
@@ -20556,32 +20692,32 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I130">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Khalil Shakir</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -20613,11 +20749,11 @@
         </is>
       </c>
       <c r="I131">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -20629,17 +20765,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D132">
@@ -20666,11 +20802,11 @@
         </is>
       </c>
       <c r="I132">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -20682,17 +20818,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D133">
@@ -20719,28 +20855,28 @@
         </is>
       </c>
       <c r="I133">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -20772,11 +20908,11 @@
         </is>
       </c>
       <c r="I134">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -20788,17 +20924,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D135">
@@ -20825,33 +20961,33 @@
         </is>
       </c>
       <c r="I135">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D136">
@@ -20874,32 +21010,32 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I136">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20931,11 +21067,11 @@
         </is>
       </c>
       <c r="I137">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -20947,17 +21083,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D138">
@@ -20980,37 +21116,37 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I138">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">Lamar Jackson</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D139">
@@ -21033,37 +21169,37 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I139">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Mason</t>
+          <t xml:space="preserve">Luther Burden III</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D140">
@@ -21086,32 +21222,32 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I140">
-        <v>137</v>
+        <v>45</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordyn Tyson</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -21143,11 +21279,11 @@
         </is>
       </c>
       <c r="I141">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR73</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -21159,12 +21295,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -21196,11 +21332,11 @@
         </is>
       </c>
       <c r="I142">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -21212,17 +21348,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D143">
@@ -21245,32 +21381,32 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I143">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -21302,11 +21438,11 @@
         </is>
       </c>
       <c r="I144">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -21318,17 +21454,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D145">
@@ -21355,33 +21491,33 @@
         </is>
       </c>
       <c r="I145">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalif Raymond</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D146">
@@ -21404,37 +21540,37 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I146">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D147">
@@ -21461,11 +21597,11 @@
         </is>
       </c>
       <c r="I147">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -21477,12 +21613,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -21510,15 +21646,15 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I148">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21530,17 +21666,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D149">
@@ -21567,11 +21703,11 @@
         </is>
       </c>
       <c r="I149">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -21583,17 +21719,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D150">
@@ -21616,15 +21752,15 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I150">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -21636,17 +21772,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D151">
@@ -21669,15 +21805,15 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I151">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -21689,17 +21825,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D152">
@@ -21722,15 +21858,15 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I152">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -21742,17 +21878,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D153">
@@ -21779,11 +21915,11 @@
         </is>
       </c>
       <c r="I153">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -21795,17 +21931,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D154">
@@ -21832,33 +21968,33 @@
         </is>
       </c>
       <c r="I154">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Jackson</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D155">
@@ -21881,37 +22017,37 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I155">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luther Burden III</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D156">
@@ -21938,33 +22074,33 @@
         </is>
       </c>
       <c r="I156">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D157">
@@ -21987,37 +22123,37 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I157">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D158">
@@ -22044,11 +22180,11 @@
         </is>
       </c>
       <c r="I158">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -22060,12 +22196,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -22097,11 +22233,11 @@
         </is>
       </c>
       <c r="I159">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -22113,17 +22249,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">Patrick Mahomes II</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D160">
@@ -22150,33 +22286,33 @@
         </is>
       </c>
       <c r="I160">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">QB13</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D161">
@@ -22203,33 +22339,33 @@
         </is>
       </c>
       <c r="I161">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D162">
@@ -22252,37 +22388,37 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I162">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D163">
@@ -22305,37 +22441,37 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I163">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D164">
@@ -22358,32 +22494,32 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I164">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -22411,32 +22547,32 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I165">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -22464,15 +22600,15 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I166">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -22484,12 +22620,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22521,33 +22657,33 @@
         </is>
       </c>
       <c r="I167">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D168">
@@ -22570,15 +22706,15 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I168">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -22590,12 +22726,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -22623,32 +22759,32 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I169">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Rome Odunze</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -22676,32 +22812,32 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I170">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -22729,15 +22865,15 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I171">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -22749,17 +22885,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D172">
@@ -22786,11 +22922,11 @@
         </is>
       </c>
       <c r="I172">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -22802,17 +22938,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rhamondre Stevenson</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D173">
@@ -22839,28 +22975,28 @@
         </is>
       </c>
       <c r="I173">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -22888,32 +23024,32 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I174">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -22941,32 +23077,32 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I175">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rome Odunze</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -22994,32 +23130,32 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I176">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -23051,11 +23187,11 @@
         </is>
       </c>
       <c r="I177">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -23067,17 +23203,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D178">
@@ -23104,33 +23240,33 @@
         </is>
       </c>
       <c r="I178">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D179">
@@ -23157,28 +23293,28 @@
         </is>
       </c>
       <c r="I179">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -23206,32 +23342,32 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I180">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -23263,11 +23399,11 @@
         </is>
       </c>
       <c r="I181">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -23279,17 +23415,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D182">
@@ -23312,32 +23448,32 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I182">
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -23369,11 +23505,11 @@
         </is>
       </c>
       <c r="I183">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -23385,12 +23521,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -23418,37 +23554,37 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I184">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D185">
@@ -23471,15 +23607,15 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I185">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -23491,17 +23627,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">Trevor Lawrence</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D186">
@@ -23528,11 +23664,11 @@
         </is>
       </c>
       <c r="I186">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23544,17 +23680,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D187">
@@ -23577,37 +23713,37 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I187">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D188">
@@ -23630,32 +23766,32 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I188">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">TreVeyon Henderson</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -23683,15 +23819,15 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I189">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -23703,17 +23839,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trevor Lawrence</t>
+          <t xml:space="preserve">Tyler Higbee</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D190">
@@ -23740,11 +23876,11 @@
         </is>
       </c>
       <c r="I190">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -23756,17 +23892,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Tyler Shough</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D191">
@@ -23789,15 +23925,15 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I191">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">QB24</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -23809,17 +23945,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Shough</t>
+          <t xml:space="preserve">Tyler Warren</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D192">
@@ -23842,37 +23978,37 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I192">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB24</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Warren</t>
+          <t xml:space="preserve">Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D193">
@@ -23895,37 +24031,37 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I193">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">RB56</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrone Tracy Jr.</t>
+          <t xml:space="preserve">Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D194">
@@ -23952,11 +24088,11 @@
         </is>
       </c>
       <c r="I194">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB56</t>
+          <t xml:space="preserve">WR68</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -23968,17 +24104,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wan'Dale Robinson</t>
+          <t xml:space="preserve">Woody Marks</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D195">
@@ -24005,11 +24141,11 @@
         </is>
       </c>
       <c r="I195">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR68</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -24021,17 +24157,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woody Marks</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D196">
@@ -24058,11 +24194,11 @@
         </is>
       </c>
       <c r="I196">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -17035,7 +17035,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I61">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I138">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -14020,17 +14020,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D3">
@@ -14041,11 +14041,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="G3">
-        <v>9.286</v>
+        <v>9.276</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -14053,11 +14053,11 @@
         </is>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -14069,12 +14069,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Daniels</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14090,11 +14090,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="G4">
-        <v>9.276</v>
+        <v>9.06</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -14102,11 +14102,11 @@
         </is>
       </c>
       <c r="I4">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -14118,17 +14118,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D5">
@@ -14139,11 +14139,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="G5">
-        <v>9.06</v>
+        <v>8.28</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -14151,11 +14151,11 @@
         </is>
       </c>
       <c r="I5">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -14167,12 +14167,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Mike Evans</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14192,19 +14192,19 @@
         </is>
       </c>
       <c r="G6">
-        <v>9.028</v>
+        <v>8.188</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I6">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -14216,17 +14216,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D7">
@@ -14237,11 +14237,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="G7">
-        <v>9.012</v>
+        <v>7.963</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -14249,11 +14249,11 @@
         </is>
       </c>
       <c r="I7">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -14265,17 +14265,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D8">
@@ -14286,11 +14286,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="G8">
-        <v>8.75</v>
+        <v>7.711</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -14298,11 +14298,11 @@
         </is>
       </c>
       <c r="I8">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14314,12 +14314,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>8.601</v>
+        <v>7.634</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14347,11 +14347,11 @@
         </is>
       </c>
       <c r="I9">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14363,17 +14363,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D10">
@@ -14384,11 +14384,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="G10">
-        <v>8.28</v>
+        <v>7.27</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14396,11 +14396,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>50</v>
+        <v>197</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14412,17 +14412,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D11">
@@ -14433,23 +14433,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="G11">
-        <v>8.199</v>
+        <v>7.2619</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I11">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14461,12 +14461,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14482,11 +14482,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="G12">
-        <v>8.188</v>
+        <v>7.209</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -14494,11 +14494,11 @@
         </is>
       </c>
       <c r="I12">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14510,12 +14510,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Kaytron Allen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14531,109 +14531,117 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="G13">
-        <v>8.1355</v>
+        <v>7.125</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I13">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">RB60</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
-      <c r="E14">
-        <v>13</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>7.963</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I14">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15">
-        <v>14</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>7.953</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14641,28 +14649,28 @@
         </is>
       </c>
       <c r="I15">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14673,94 +14681,102 @@
       <c r="D16">
         <v>6</v>
       </c>
-      <c r="E16">
-        <v>15</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>7.948</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I16">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
-      <c r="E17">
-        <v>16</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>7.711</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I17">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14771,45 +14787,49 @@
       <c r="D18">
         <v>6</v>
       </c>
-      <c r="E18">
-        <v>17</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>7.634</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I18">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14820,16 +14840,20 @@
       <c r="D19">
         <v>6</v>
       </c>
-      <c r="E19">
-        <v>18</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>7.584</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -14837,28 +14861,28 @@
         </is>
       </c>
       <c r="I19">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14869,94 +14893,102 @@
       <c r="D20">
         <v>6</v>
       </c>
-      <c r="E20">
-        <v>19</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>7.425</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I20">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
-      <c r="E21">
-        <v>20</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>7.27</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I21">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14967,94 +14999,102 @@
       <c r="D22">
         <v>6</v>
       </c>
-      <c r="E22">
-        <v>21</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>7.2619</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I22">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">Bijan Robinson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
-      <c r="E23">
-        <v>22</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>7.209</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I23">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">RB1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaytron Allen</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -15065,65 +15105,73 @@
       <c r="D24">
         <v>6</v>
       </c>
-      <c r="E24">
-        <v>23</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>7.125</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I24">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB60</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
-      <c r="E25">
-        <v>24</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>6.73975</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -15131,33 +15179,33 @@
         </is>
       </c>
       <c r="I25">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D26">
@@ -15180,15 +15228,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I26">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -15200,12 +15248,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15233,37 +15281,37 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I27">
-        <v>156</v>
+        <v>24</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D28">
@@ -15286,37 +15334,37 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I28">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D29">
@@ -15339,37 +15387,37 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I29">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D30">
@@ -15392,15 +15440,15 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I30">
-        <v>184</v>
+        <v>43</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -15412,17 +15460,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amon-Ra St. Brown</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D31">
@@ -15449,28 +15497,28 @@
         </is>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15502,11 +15550,11 @@
         </is>
       </c>
       <c r="I32">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15518,12 +15566,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15551,37 +15599,37 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I33">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D34">
@@ -15604,37 +15652,37 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I34">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bijan Robinson</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D35">
@@ -15657,15 +15705,15 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB1</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -15677,12 +15725,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15714,11 +15762,11 @@
         </is>
       </c>
       <c r="I36">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -15730,17 +15778,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D37">
@@ -15767,11 +15815,11 @@
         </is>
       </c>
       <c r="I37">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -15783,17 +15831,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D38">
@@ -15820,11 +15868,11 @@
         </is>
       </c>
       <c r="I38">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15836,12 +15884,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -15869,37 +15917,37 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I39">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D40">
@@ -15926,33 +15974,33 @@
         </is>
       </c>
       <c r="I40">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D41">
@@ -15979,11 +16027,11 @@
         </is>
       </c>
       <c r="I41">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -15995,12 +16043,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -16028,15 +16076,15 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I42">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -16048,17 +16096,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D43">
@@ -16085,11 +16133,11 @@
         </is>
       </c>
       <c r="I43">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -16101,17 +16149,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D44">
@@ -16138,11 +16186,11 @@
         </is>
       </c>
       <c r="I44">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -16154,17 +16202,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D45">
@@ -16191,11 +16239,11 @@
         </is>
       </c>
       <c r="I45">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -16207,17 +16255,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D46">
@@ -16240,37 +16288,37 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I46">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D47">
@@ -16293,15 +16341,15 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I47">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -16313,17 +16361,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D48">
@@ -16350,11 +16398,11 @@
         </is>
       </c>
       <c r="I48">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -16366,17 +16414,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D49">
@@ -16403,11 +16451,11 @@
         </is>
       </c>
       <c r="I49">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16419,17 +16467,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D50">
@@ -16456,33 +16504,33 @@
         </is>
       </c>
       <c r="I50">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D51">
@@ -16509,33 +16557,33 @@
         </is>
       </c>
       <c r="I51">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D52">
@@ -16558,15 +16606,15 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I52">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -16578,17 +16626,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D53">
@@ -16611,15 +16659,15 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I53">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -16631,17 +16679,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D54">
@@ -16668,11 +16716,11 @@
         </is>
       </c>
       <c r="I54">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -16684,17 +16732,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D55">
@@ -16717,15 +16765,15 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I55">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -16737,12 +16785,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16774,11 +16822,11 @@
         </is>
       </c>
       <c r="I56">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -16790,17 +16838,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D57">
@@ -16827,11 +16875,11 @@
         </is>
       </c>
       <c r="I57">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16843,17 +16891,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D58">
@@ -16876,32 +16924,32 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I58">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16929,37 +16977,37 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I59">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D60">
@@ -16982,37 +17030,37 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I60">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D61">
@@ -17035,15 +17083,15 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I61">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -17055,17 +17103,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D62">
@@ -17092,11 +17140,11 @@
         </is>
       </c>
       <c r="I62">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17108,17 +17156,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D63">
@@ -17145,11 +17193,11 @@
         </is>
       </c>
       <c r="I63">
-        <v>164</v>
+        <v>87</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17161,12 +17209,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17194,15 +17242,15 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I64">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17214,17 +17262,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D65">
@@ -17247,32 +17295,32 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I65">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -17304,11 +17352,11 @@
         </is>
       </c>
       <c r="I66">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -17320,17 +17368,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D67">
@@ -17353,37 +17401,37 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I67">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D68">
@@ -17406,37 +17454,37 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I68">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D69">
@@ -17459,37 +17507,37 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I69">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D70">
@@ -17516,11 +17564,11 @@
         </is>
       </c>
       <c r="I70">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -17532,17 +17580,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D71">
@@ -17569,11 +17617,11 @@
         </is>
       </c>
       <c r="I71">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -17585,17 +17633,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D72">
@@ -17622,11 +17670,11 @@
         </is>
       </c>
       <c r="I72">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -17638,12 +17686,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17675,11 +17723,11 @@
         </is>
       </c>
       <c r="I73">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -17691,17 +17739,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D74">
@@ -17724,32 +17772,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I74">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17781,11 +17829,11 @@
         </is>
       </c>
       <c r="I75">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -17797,17 +17845,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D76">
@@ -17834,11 +17882,11 @@
         </is>
       </c>
       <c r="I76">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -17850,17 +17898,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D77">
@@ -17887,11 +17935,11 @@
         </is>
       </c>
       <c r="I77">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -17903,17 +17951,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D78">
@@ -17940,11 +17988,11 @@
         </is>
       </c>
       <c r="I78">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -17956,12 +18004,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17989,37 +18037,37 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I79">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D80">
@@ -18046,11 +18094,11 @@
         </is>
       </c>
       <c r="I80">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -18062,17 +18110,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Ja'Marr Chase</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D81">
@@ -18099,33 +18147,33 @@
         </is>
       </c>
       <c r="I81">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">WR1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D82">
@@ -18148,27 +18196,27 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I82">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -18201,37 +18249,37 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I83">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D84">
@@ -18258,28 +18306,28 @@
         </is>
       </c>
       <c r="I84">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">RB2</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -18311,11 +18359,11 @@
         </is>
       </c>
       <c r="I85">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -18327,17 +18375,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D86">
@@ -18364,11 +18412,11 @@
         </is>
       </c>
       <c r="I86">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -18380,17 +18428,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D87">
@@ -18413,37 +18461,37 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I87">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D88">
@@ -18466,32 +18514,32 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I88">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja'Marr Chase</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -18523,33 +18571,33 @@
         </is>
       </c>
       <c r="I89">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR1</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D90">
@@ -18572,37 +18620,37 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I90">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D91">
@@ -18625,32 +18673,32 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I91">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahmyr Gibbs</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -18682,28 +18730,28 @@
         </is>
       </c>
       <c r="I92">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB2</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18735,33 +18783,33 @@
         </is>
       </c>
       <c r="I93">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D94">
@@ -18788,33 +18836,33 @@
         </is>
       </c>
       <c r="I94">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D95">
@@ -18837,32 +18885,32 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I95">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -18894,11 +18942,11 @@
         </is>
       </c>
       <c r="I96">
-        <v>178</v>
+        <v>5</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -18910,12 +18958,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -18943,37 +18991,37 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I97">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D98">
@@ -18996,37 +19044,37 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I98">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D99">
@@ -19049,32 +19097,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I99">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -19106,33 +19154,33 @@
         </is>
       </c>
       <c r="I100">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D101">
@@ -19159,33 +19207,33 @@
         </is>
       </c>
       <c r="I101">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D102">
@@ -19212,33 +19260,33 @@
         </is>
       </c>
       <c r="I102">
-        <v>5</v>
+        <v>155</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Jeremiyah Love</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D103">
@@ -19261,15 +19309,15 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I103">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -19281,17 +19329,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Higgins</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D104">
@@ -19314,37 +19362,37 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I104">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR75</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Reed</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D105">
@@ -19371,11 +19419,11 @@
         </is>
       </c>
       <c r="I105">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -19387,17 +19435,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D106">
@@ -19424,11 +19472,11 @@
         </is>
       </c>
       <c r="I106">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -19440,12 +19488,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -19473,37 +19521,37 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I107">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D108">
@@ -19530,33 +19578,33 @@
         </is>
       </c>
       <c r="I108">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D109">
@@ -19579,32 +19627,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I109">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19636,28 +19684,28 @@
         </is>
       </c>
       <c r="I110">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19689,33 +19737,33 @@
         </is>
       </c>
       <c r="I111">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Jordyn Tyson</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D112">
@@ -19738,37 +19786,37 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I112">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">WR73</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Josh Allen</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D113">
@@ -19791,32 +19839,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I113">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -19844,32 +19892,32 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I114">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Mason</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -19897,37 +19945,37 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I115">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordyn Tyson</t>
+          <t xml:space="preserve">Justin Herbert</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D116">
@@ -19950,37 +19998,37 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I116">
-        <v>193</v>
+        <v>69</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR73</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D117">
@@ -20007,33 +20055,33 @@
         </is>
       </c>
       <c r="I117">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D118">
@@ -20060,11 +20108,11 @@
         </is>
       </c>
       <c r="I118">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -20076,7 +20124,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -20109,37 +20157,37 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I119">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Herbert</t>
+          <t xml:space="preserve">Kalif Raymond</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D120">
@@ -20166,11 +20214,11 @@
         </is>
       </c>
       <c r="I120">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -20182,12 +20230,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -20219,33 +20267,33 @@
         </is>
       </c>
       <c r="I121">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">Keaton Mitchell</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D122">
@@ -20272,11 +20320,11 @@
         </is>
       </c>
       <c r="I122">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB59</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -20288,12 +20336,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalif Raymond</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -20325,11 +20373,11 @@
         </is>
       </c>
       <c r="I123">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -20341,17 +20389,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D124">
@@ -20378,11 +20426,11 @@
         </is>
       </c>
       <c r="I124">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -20394,12 +20442,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keaton Mitchell</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20427,15 +20475,15 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I125">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB59</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -20447,17 +20495,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D126">
@@ -20484,11 +20532,11 @@
         </is>
       </c>
       <c r="I126">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -20500,17 +20548,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D127">
@@ -20533,15 +20581,15 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I127">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -20553,17 +20601,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Khalil Shakir</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D128">
@@ -20586,15 +20634,15 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I128">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -20606,17 +20654,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D129">
@@ -20643,11 +20691,11 @@
         </is>
       </c>
       <c r="I129">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20659,17 +20707,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D130">
@@ -20692,15 +20740,15 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I130">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -20712,17 +20760,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khalil Shakir</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D131">
@@ -20745,37 +20793,37 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I131">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D132">
@@ -20802,11 +20850,11 @@
         </is>
       </c>
       <c r="I132">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -20818,17 +20866,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D133">
@@ -20855,28 +20903,28 @@
         </is>
       </c>
       <c r="I133">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -20904,37 +20952,37 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I134">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D135">
@@ -20957,32 +21005,32 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I135">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">Lamar Jackson</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -21010,37 +21058,37 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I136">
-        <v>175</v>
+        <v>39</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">Luther Burden III</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D137">
@@ -21067,11 +21115,11 @@
         </is>
       </c>
       <c r="I137">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -21083,12 +21131,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -21116,15 +21164,15 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I138">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -21136,17 +21184,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Jackson</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D139">
@@ -21169,32 +21217,32 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I139">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luther Burden III</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -21226,11 +21274,11 @@
         </is>
       </c>
       <c r="I140">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -21242,12 +21290,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -21275,37 +21323,37 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I141">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D142">
@@ -21332,33 +21380,33 @@
         </is>
       </c>
       <c r="I142">
-        <v>99</v>
+        <v>190</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D143">
@@ -21381,37 +21429,37 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I143">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D144">
@@ -21438,33 +21486,33 @@
         </is>
       </c>
       <c r="I144">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D145">
@@ -21491,33 +21539,33 @@
         </is>
       </c>
       <c r="I145">
-        <v>190</v>
+        <v>121</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D146">
@@ -21540,37 +21588,37 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I146">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D147">
@@ -21597,11 +21645,11 @@
         </is>
       </c>
       <c r="I147">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -21613,17 +21661,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D148">
@@ -21646,15 +21694,15 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I148">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21666,17 +21714,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D149">
@@ -21703,11 +21751,11 @@
         </is>
       </c>
       <c r="I149">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -21719,17 +21767,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D150">
@@ -21756,11 +21804,11 @@
         </is>
       </c>
       <c r="I150">
-        <v>179</v>
+        <v>52</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -21772,17 +21820,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D151">
@@ -21805,32 +21853,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I151">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21858,37 +21906,37 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I152">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D153">
@@ -21915,11 +21963,11 @@
         </is>
       </c>
       <c r="I153">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -21931,17 +21979,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D154">
@@ -21968,11 +22016,11 @@
         </is>
       </c>
       <c r="I154">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -21984,17 +22032,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D155">
@@ -22021,28 +22069,28 @@
         </is>
       </c>
       <c r="I155">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -22074,23 +22122,23 @@
         </is>
       </c>
       <c r="I156">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -22100,7 +22148,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D157">
@@ -22127,11 +22175,11 @@
         </is>
       </c>
       <c r="I157">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -22143,17 +22191,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D158">
@@ -22180,11 +22228,11 @@
         </is>
       </c>
       <c r="I158">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -22196,17 +22244,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Patrick Mahomes II</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D159">
@@ -22233,11 +22281,11 @@
         </is>
       </c>
       <c r="I159">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">QB13</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -22249,17 +22297,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes II</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D160">
@@ -22286,11 +22334,11 @@
         </is>
       </c>
       <c r="I160">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -22302,12 +22350,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -22339,11 +22387,11 @@
         </is>
       </c>
       <c r="I161">
-        <v>4</v>
+        <v>129</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -22355,17 +22403,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D162">
@@ -22388,37 +22436,37 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I162">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D163">
@@ -22445,11 +22493,11 @@
         </is>
       </c>
       <c r="I163">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -22461,12 +22509,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -22494,32 +22542,32 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I164">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -22547,15 +22595,15 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I165">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -22567,17 +22615,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D166">
@@ -22600,15 +22648,15 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I166">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -22620,12 +22668,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rhamondre Stevenson</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22653,15 +22701,15 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I167">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -22673,12 +22721,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -22706,15 +22754,15 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I168">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -22726,17 +22774,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Rome Odunze</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D169">
@@ -22763,11 +22811,11 @@
         </is>
       </c>
       <c r="I169">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -22779,12 +22827,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rome Odunze</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -22812,15 +22860,15 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I170">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -22832,17 +22880,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D171">
@@ -22865,15 +22913,15 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I171">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -22885,17 +22933,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D172">
@@ -22922,33 +22970,33 @@
         </is>
       </c>
       <c r="I172">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D173">
@@ -22971,27 +23019,27 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I173">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -23024,15 +23072,15 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I174">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -23044,17 +23092,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D175">
@@ -23081,11 +23129,11 @@
         </is>
       </c>
       <c r="I175">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -23097,12 +23145,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -23130,32 +23178,32 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I176">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -23187,28 +23235,28 @@
         </is>
       </c>
       <c r="I177">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -23240,33 +23288,33 @@
         </is>
       </c>
       <c r="I178">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D179">
@@ -23293,11 +23341,11 @@
         </is>
       </c>
       <c r="I179">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -23309,12 +23357,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -23342,37 +23390,37 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I180">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D181">
@@ -23395,37 +23443,37 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I181">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D182">
@@ -23452,11 +23500,11 @@
         </is>
       </c>
       <c r="I182">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -23468,12 +23516,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -23501,37 +23549,37 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I183">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D184">
@@ -23554,37 +23602,37 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I184">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">TreVeyon Henderson</t>
+          <t xml:space="preserve">Trevor Lawrence</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D185">
@@ -23607,15 +23655,15 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I185">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -23627,17 +23675,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trevor Lawrence</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D186">
@@ -23664,11 +23712,11 @@
         </is>
       </c>
       <c r="I186">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23680,12 +23728,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -23717,11 +23765,11 @@
         </is>
       </c>
       <c r="I187">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -21005,7 +21005,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I135">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -14441,7 +14441,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I11">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I52">
@@ -16871,7 +16871,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I57">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I82">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I115">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
@@ -22860,7 +22860,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I170">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -14441,7 +14441,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I11">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I17">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I19">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I27">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I53">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I55">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I66">
@@ -17185,7 +17185,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I67">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I74">
@@ -17626,7 +17626,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I76">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I77">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I81">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOUBTFUL</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I93">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I99">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I104">
@@ -19606,12 +19606,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -19631,19 +19631,19 @@
         </is>
       </c>
       <c r="G117">
-        <v>7.745</v>
+        <v>7.7213</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I117">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -19655,17 +19655,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D118">
@@ -19676,23 +19676,23 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="G118">
-        <v>7.7213</v>
+        <v>7.641</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I118">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -19704,12 +19704,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -19725,11 +19725,11 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="G119">
-        <v>7.641</v>
+        <v>7.632</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -19737,11 +19737,11 @@
         </is>
       </c>
       <c r="I119">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -19753,7 +19753,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D120">
@@ -19774,11 +19774,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="G120">
-        <v>7.632</v>
+        <v>7.62325</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -19786,11 +19786,11 @@
         </is>
       </c>
       <c r="I120">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -19802,17 +19802,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D121">
@@ -19823,23 +19823,23 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="G121">
-        <v>7.62325</v>
+        <v>7.601</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I121">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -19851,12 +19851,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -19872,23 +19872,23 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="G122">
-        <v>7.601</v>
+        <v>7.584</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I122">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -19900,17 +19900,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D123">
@@ -19921,23 +19921,23 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="G123">
-        <v>7.584</v>
+        <v>7.58</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I123">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -19949,17 +19949,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D124">
@@ -19970,11 +19970,11 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="G124">
-        <v>7.58</v>
+        <v>7.485</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -19982,11 +19982,11 @@
         </is>
       </c>
       <c r="I124">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -19998,17 +19998,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D125">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="G125">
@@ -20031,11 +20031,11 @@
         </is>
       </c>
       <c r="I125">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -20047,12 +20047,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -20072,36 +20072,36 @@
         </is>
       </c>
       <c r="G126">
-        <v>7.485</v>
+        <v>7.456</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I126">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -20121,36 +20121,36 @@
         </is>
       </c>
       <c r="G127">
-        <v>7.456</v>
+        <v>7.4535</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I127">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">MODEL_RANK</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20170,19 +20170,19 @@
         </is>
       </c>
       <c r="G128">
-        <v>7.4535</v>
+        <v>7.425</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I128">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -20194,12 +20194,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -20219,19 +20219,19 @@
         </is>
       </c>
       <c r="G129">
-        <v>7.425</v>
+        <v>7.37485</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I129">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20243,12 +20243,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -20268,7 +20268,7 @@
         </is>
       </c>
       <c r="G130">
-        <v>7.37485</v>
+        <v>7.37</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -20276,11 +20276,11 @@
         </is>
       </c>
       <c r="I130">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -20292,12 +20292,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="G131">
-        <v>7.37</v>
+        <v>7.3335</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -20325,11 +20325,11 @@
         </is>
       </c>
       <c r="I131">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -20341,12 +20341,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -20366,7 +20366,7 @@
         </is>
       </c>
       <c r="G132">
-        <v>7.3335</v>
+        <v>7.3135</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -20374,11 +20374,11 @@
         </is>
       </c>
       <c r="I132">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -20390,12 +20390,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -20415,7 +20415,7 @@
         </is>
       </c>
       <c r="G133">
-        <v>7.3135</v>
+        <v>7.27</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -20423,11 +20423,11 @@
         </is>
       </c>
       <c r="I133">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -20439,12 +20439,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Woody Marks</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -20464,7 +20464,7 @@
         </is>
       </c>
       <c r="G134">
-        <v>7.27</v>
+        <v>7.258</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -20472,11 +20472,11 @@
         </is>
       </c>
       <c r="I134">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -20488,12 +20488,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woody Marks</t>
+          <t xml:space="preserve">Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -20513,7 +20513,7 @@
         </is>
       </c>
       <c r="G135">
-        <v>7.258</v>
+        <v>7.238</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -20521,11 +20521,11 @@
         </is>
       </c>
       <c r="I135">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">RB56</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -20537,12 +20537,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrone Tracy Jr.</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -20562,7 +20562,7 @@
         </is>
       </c>
       <c r="G136">
-        <v>7.238</v>
+        <v>7.155</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -20570,11 +20570,11 @@
         </is>
       </c>
       <c r="I136">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB56</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -20586,12 +20586,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20611,19 +20611,19 @@
         </is>
       </c>
       <c r="G137">
-        <v>7.155</v>
+        <v>7.08335</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I137">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -20635,7 +20635,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D138">
@@ -20656,11 +20656,11 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="G138">
-        <v>7.08335</v>
+        <v>7.08</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -20668,11 +20668,11 @@
         </is>
       </c>
       <c r="I138">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -20684,17 +20684,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D139">
@@ -20705,11 +20705,11 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="G139">
-        <v>7.08</v>
+        <v>6.998</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -20717,11 +20717,11 @@
         </is>
       </c>
       <c r="I139">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -20733,12 +20733,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -20758,19 +20758,19 @@
         </is>
       </c>
       <c r="G140">
-        <v>6.998</v>
+        <v>6.9</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I140">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -20782,12 +20782,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -20807,7 +20807,7 @@
         </is>
       </c>
       <c r="G141">
-        <v>6.9</v>
+        <v>6.885</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -20815,11 +20815,11 @@
         </is>
       </c>
       <c r="I141">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -20831,12 +20831,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -20864,11 +20864,11 @@
         </is>
       </c>
       <c r="I142">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -20880,17 +20880,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D143">
@@ -20901,11 +20901,11 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="G143">
-        <v>6.885</v>
+        <v>6.88</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -20913,11 +20913,11 @@
         </is>
       </c>
       <c r="I143">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -20929,17 +20929,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D144">
@@ -20950,11 +20950,11 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="G144">
-        <v>6.88</v>
+        <v>6.73975</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -20962,11 +20962,11 @@
         </is>
       </c>
       <c r="I144">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -20978,17 +20978,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D145">
@@ -20999,11 +20999,11 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="G145">
-        <v>6.73975</v>
+        <v>6.595</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -21011,11 +21011,11 @@
         </is>
       </c>
       <c r="I145">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -21027,12 +21027,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -21048,23 +21048,23 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="G146">
-        <v>6.595</v>
+        <v>6.55025</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I146">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -21076,17 +21076,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D147">
@@ -21097,23 +21097,23 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="G147">
-        <v>6.55025</v>
+        <v>6.401</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I147">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -21125,17 +21125,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D148">
@@ -21146,11 +21146,11 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="G148">
-        <v>6.401</v>
+        <v>6.355</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -21158,11 +21158,11 @@
         </is>
       </c>
       <c r="I148">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -21174,17 +21174,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Zach Charbonnet</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D149">
@@ -21195,23 +21195,23 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="G149">
-        <v>6.355</v>
+        <v>6.18</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I149">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">RB66</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -22866,17 +22866,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D181">
@@ -22899,32 +22899,32 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I181">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -22952,37 +22952,37 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I182">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D183">
@@ -23005,37 +23005,37 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOUBTFUL</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I183">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D184">
@@ -23058,37 +23058,37 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">DOUBTFUL</t>
         </is>
       </c>
       <c r="I184">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D185">
@@ -23111,27 +23111,27 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I185">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D186">
@@ -23168,11 +23168,11 @@
         </is>
       </c>
       <c r="I186">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23184,17 +23184,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D187">
@@ -23221,11 +23221,11 @@
         </is>
       </c>
       <c r="I187">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23237,12 +23237,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -23274,11 +23274,11 @@
         </is>
       </c>
       <c r="I188">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -23290,17 +23290,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D189">
@@ -23327,11 +23327,11 @@
         </is>
       </c>
       <c r="I189">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -23343,17 +23343,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D190">
@@ -23376,32 +23376,32 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I190">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -23429,37 +23429,37 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I191">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D192">
@@ -23482,37 +23482,37 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I192">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D193">
@@ -23539,11 +23539,11 @@
         </is>
       </c>
       <c r="I193">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -23555,12 +23555,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -23588,37 +23588,37 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I194">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D195">
@@ -23641,37 +23641,37 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I195">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D196">
@@ -23694,37 +23694,37 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I196">
-        <v>176</v>
+        <v>49</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trevor Lawrence</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D197">
@@ -23747,15 +23747,15 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I197">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -23767,17 +23767,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zach Charbonnet</t>
+          <t xml:space="preserve">Trevor Lawrence</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D198">
@@ -23800,20 +23800,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I198">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB66</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -14000,7 +14000,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I2">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I3">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I4">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I5">
@@ -14265,17 +14265,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D8">
@@ -14286,23 +14286,23 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="G8">
-        <v>9.46</v>
+        <v>9.386</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I8">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14314,17 +14314,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D9">
@@ -14335,23 +14335,23 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="G9">
-        <v>9.386</v>
+        <v>9.375</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14363,17 +14363,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D10">
@@ -14384,11 +14384,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="G10">
-        <v>9.375</v>
+        <v>9.373</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14396,11 +14396,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14412,17 +14412,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D11">
@@ -14433,23 +14433,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="G11">
-        <v>9.373</v>
+        <v>9.3675</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14461,12 +14461,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Christian McCaffrey</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14482,23 +14482,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t xml:space="preserve">RB4</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>9.34</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t xml:space="preserve">RB3</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>9.3675</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
-        </is>
-      </c>
-      <c r="I12">
-        <v>10</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14510,17 +14510,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian McCaffrey</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D13">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="G13">
-        <v>9.34</v>
+        <v>9.305</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14543,11 +14543,11 @@
         </is>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14559,12 +14559,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14580,23 +14580,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="G14">
-        <v>9.305</v>
+        <v>9.286</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14608,12 +14608,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14629,11 +14629,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="G15">
-        <v>9.286</v>
+        <v>9.26325</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14641,11 +14641,11 @@
         </is>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14657,17 +14657,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D16">
@@ -14678,11 +14678,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="G16">
-        <v>9.26325</v>
+        <v>9.26</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -14690,11 +14690,11 @@
         </is>
       </c>
       <c r="I16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14706,17 +14706,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D17">
@@ -14727,11 +14727,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="G17">
-        <v>9.26</v>
+        <v>9.256</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -14739,11 +14739,11 @@
         </is>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -14755,12 +14755,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">Rashee Rice</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14776,23 +14776,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="G18">
-        <v>9.256</v>
+        <v>9.113</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14804,17 +14804,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D19">
@@ -14825,23 +14825,23 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="G19">
-        <v>9.14525</v>
+        <v>9.101</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I19">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14853,17 +14853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D20">
@@ -14874,23 +14874,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="G20">
-        <v>9.142</v>
+        <v>9.09</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I20">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14902,17 +14902,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D21">
@@ -14923,23 +14923,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="G21">
-        <v>9.113</v>
+        <v>9.076</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I21">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14951,17 +14951,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D22">
@@ -14972,23 +14972,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="G22">
-        <v>9.101</v>
+        <v>9.06</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I22">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -15000,17 +15000,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D23">
@@ -15021,23 +15021,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="G23">
-        <v>9.09</v>
+        <v>9.058</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I23">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -15049,17 +15049,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D24">
@@ -15070,23 +15070,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="G24">
-        <v>9.076</v>
+        <v>9.028</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I24">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -15098,17 +15098,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D25">
@@ -15119,23 +15119,23 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="G25">
-        <v>9.06</v>
+        <v>9.022</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I25">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -15147,12 +15147,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15168,23 +15168,23 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="G26">
-        <v>9.058</v>
+        <v>9.0216</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I26">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -15196,17 +15196,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D27">
@@ -15217,23 +15217,23 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="G27">
-        <v>9.028</v>
+        <v>9.02</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I27">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -15245,17 +15245,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D28">
@@ -15266,23 +15266,23 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="G28">
-        <v>9.022</v>
+        <v>9.012</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I28">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -15294,17 +15294,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D29">
@@ -15315,23 +15315,23 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="G29">
-        <v>9.0216</v>
+        <v>9.006</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I29">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -15343,12 +15343,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15364,23 +15364,23 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="G30">
-        <v>9.02</v>
+        <v>9.003</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I30">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -15392,12 +15392,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15413,23 +15413,23 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="G31">
-        <v>9.012</v>
+        <v>8.9911</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I31">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15441,17 +15441,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D32">
@@ -15462,23 +15462,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="G32">
-        <v>9.006</v>
+        <v>8.991</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I32">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15490,17 +15490,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D33">
@@ -15511,23 +15511,23 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="G33">
-        <v>9.003</v>
+        <v>8.9816</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I33">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -15539,12 +15539,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15564,7 +15564,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>8.9911</v>
+        <v>8.9616</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -15572,11 +15572,11 @@
         </is>
       </c>
       <c r="I34">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -15588,17 +15588,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D35">
@@ -15609,23 +15609,23 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="G35">
-        <v>8.991</v>
+        <v>8.935</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I35">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -15637,12 +15637,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15662,19 +15662,19 @@
         </is>
       </c>
       <c r="G36">
-        <v>8.9816</v>
+        <v>8.926</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I36">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -15686,17 +15686,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D37">
@@ -15707,23 +15707,23 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB13</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="G37">
-        <v>8.9616</v>
+        <v>8.91525</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I37">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -15735,17 +15735,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D38">
@@ -15756,23 +15756,23 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">QB13</t>
         </is>
       </c>
       <c r="G38">
-        <v>8.935</v>
+        <v>8.8835</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I38">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15784,17 +15784,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D39">
@@ -15805,23 +15805,23 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="G39">
-        <v>8.926</v>
+        <v>8.88</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I39">
-        <v>186</v>
+        <v>14</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -15833,12 +15833,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -15858,19 +15858,19 @@
         </is>
       </c>
       <c r="G40">
-        <v>8.91525</v>
+        <v>8.864</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I40">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -15882,12 +15882,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15903,23 +15903,23 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="G41">
-        <v>8.8835</v>
+        <v>8.834</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I41">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -15931,17 +15931,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Zay Flowers</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D42">
@@ -15952,23 +15952,23 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="G42">
-        <v>8.88</v>
+        <v>8.776</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I42">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -15980,17 +15980,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D43">
@@ -16001,11 +16001,11 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="G43">
-        <v>8.864</v>
+        <v>8.75</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -16013,11 +16013,11 @@
         </is>
       </c>
       <c r="I43">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -16029,17 +16029,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D44">
@@ -16050,23 +16050,23 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="G44">
-        <v>8.834</v>
+        <v>8.68</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I44">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -16078,17 +16078,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">Tyler Shough</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D45">
@@ -16099,23 +16099,23 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="G45">
-        <v>8.825</v>
+        <v>8.62625</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I45">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">QB24</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -16127,12 +16127,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zay Flowers</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -16148,23 +16148,23 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="G46">
-        <v>8.776</v>
+        <v>8.607</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I46">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -16176,17 +16176,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D47">
@@ -16197,23 +16197,23 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="G47">
-        <v>8.75</v>
+        <v>8.601</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I47">
-        <v>188</v>
+        <v>47</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -16225,17 +16225,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D48">
@@ -16246,23 +16246,23 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="G48">
-        <v>8.68</v>
+        <v>8.6</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I48">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -16274,17 +16274,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Shough</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D49">
@@ -16295,23 +16295,23 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="G49">
-        <v>8.62625</v>
+        <v>8.59925</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I49">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB24</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16323,12 +16323,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -16344,23 +16344,23 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="G50">
-        <v>8.607</v>
+        <v>8.549</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I50">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -16372,17 +16372,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D51">
@@ -16393,23 +16393,23 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="G51">
-        <v>8.601</v>
+        <v>8.534</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I51">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -16421,17 +16421,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D52">
@@ -16442,11 +16442,11 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="G52">
-        <v>8.6</v>
+        <v>8.448</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -16454,11 +16454,11 @@
         </is>
       </c>
       <c r="I52">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -16470,12 +16470,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16491,23 +16491,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="G53">
-        <v>8.59925</v>
+        <v>8.4431</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I53">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -16519,17 +16519,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D54">
@@ -16540,11 +16540,11 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="G54">
-        <v>8.549</v>
+        <v>8.4265</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -16552,11 +16552,11 @@
         </is>
       </c>
       <c r="I54">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -16568,17 +16568,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Tyler Warren</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D55">
@@ -16589,11 +16589,11 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="G55">
-        <v>8.534</v>
+        <v>8.406</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -16601,11 +16601,11 @@
         </is>
       </c>
       <c r="I55">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -16617,12 +16617,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16642,19 +16642,19 @@
         </is>
       </c>
       <c r="G56">
-        <v>8.448</v>
+        <v>8.352</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I56">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -16666,17 +16666,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D57">
@@ -16687,23 +16687,23 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="G57">
-        <v>8.4431</v>
+        <v>8.348</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I57">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16715,12 +16715,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16736,23 +16736,23 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="G58">
-        <v>8.435</v>
+        <v>8.34</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I58">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16764,17 +16764,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D59">
@@ -16785,11 +16785,11 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="G59">
-        <v>8.4265</v>
+        <v>8.335</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -16797,11 +16797,11 @@
         </is>
       </c>
       <c r="I59">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16813,17 +16813,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Warren</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D60">
@@ -16834,23 +16834,23 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="G60">
-        <v>8.406</v>
+        <v>8.325</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I60">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16862,12 +16862,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rome Odunze</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16883,23 +16883,23 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="G61">
-        <v>8.405</v>
+        <v>8.285</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I61">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -16911,17 +16911,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TreVeyon Henderson</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D62">
@@ -16932,23 +16932,23 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="G62">
-        <v>8.3839</v>
+        <v>8.285</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I62">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -16960,12 +16960,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalif Raymond</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16981,45 +16981,45 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="G63">
-        <v>8.375</v>
+        <v>8.278</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I63">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D64">
@@ -17030,23 +17030,23 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="G64">
-        <v>8.352</v>
+        <v>8.276</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I64">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17058,17 +17058,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D65">
@@ -17079,11 +17079,11 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="G65">
-        <v>8.348</v>
+        <v>8.275</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -17091,11 +17091,11 @@
         </is>
       </c>
       <c r="I65">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -17107,17 +17107,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D66">
@@ -17128,11 +17128,11 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="G66">
-        <v>8.34</v>
+        <v>8.265</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -17140,11 +17140,11 @@
         </is>
       </c>
       <c r="I66">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -17156,17 +17156,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D67">
@@ -17177,23 +17177,23 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="G67">
-        <v>8.335</v>
+        <v>8.25685</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I67">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -17205,17 +17205,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luther Burden III</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D68">
@@ -17226,23 +17226,23 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="G68">
-        <v>8.328</v>
+        <v>8.24425</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I68">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -17254,12 +17254,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -17279,19 +17279,19 @@
         </is>
       </c>
       <c r="G69">
-        <v>8.325</v>
+        <v>8.235</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I69">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -17303,7 +17303,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D70">
@@ -17324,23 +17324,23 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="G70">
-        <v>8.285</v>
+        <v>8.22685</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I70">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -17352,12 +17352,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -17373,23 +17373,23 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="G71">
-        <v>8.285</v>
+        <v>8.20685</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I71">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -17401,12 +17401,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -17422,40 +17422,40 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="G72">
-        <v>8.278</v>
+        <v>8.205</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I72">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">MODEL_RANK</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17471,23 +17471,23 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="G73">
-        <v>8.276</v>
+        <v>8.199</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I73">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -17499,12 +17499,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">Tyler Higbee</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17520,23 +17520,23 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t xml:space="preserve">TE12</t>
+        </is>
+      </c>
+      <c r="G74">
+        <v>8.18835</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+        </is>
+      </c>
+      <c r="I74">
+        <v>81</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t xml:space="preserve">TE8</t>
-        </is>
-      </c>
-      <c r="G74">
-        <v>8.275</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
-        </is>
-      </c>
-      <c r="I74">
-        <v>132</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -17548,12 +17548,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">Mike Evans</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17569,23 +17569,23 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="G75">
-        <v>8.265</v>
+        <v>8.188</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I75">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -17597,17 +17597,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D76">
@@ -17618,23 +17618,23 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="G76">
-        <v>8.25685</v>
+        <v>8.16525</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I76">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -17646,17 +17646,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D77">
@@ -17667,23 +17667,23 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="G77">
-        <v>8.24425</v>
+        <v>8.15805</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I77">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -17695,17 +17695,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D78">
@@ -17716,23 +17716,23 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="G78">
-        <v>8.235</v>
+        <v>8.148</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I78">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -17744,17 +17744,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D79">
@@ -17765,11 +17765,11 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="G79">
-        <v>8.22685</v>
+        <v>8.1355</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -17777,11 +17777,11 @@
         </is>
       </c>
       <c r="I79">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -17793,12 +17793,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -17814,23 +17814,23 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="G80">
-        <v>8.20685</v>
+        <v>8.135</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I80">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -17842,12 +17842,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -17867,19 +17867,19 @@
         </is>
       </c>
       <c r="G81">
-        <v>8.205</v>
+        <v>8.13</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I81">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -17891,12 +17891,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -17912,23 +17912,23 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="G82">
-        <v>8.199</v>
+        <v>8.11835</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I82">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -17940,17 +17940,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Higbee</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D83">
@@ -17961,23 +17961,23 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="G83">
-        <v>8.18835</v>
+        <v>8.11805</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I83">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -17989,12 +17989,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -18010,23 +18010,23 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="G84">
-        <v>8.188</v>
+        <v>8.117</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I84">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -18038,12 +18038,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -18059,11 +18059,11 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="G85">
-        <v>8.16525</v>
+        <v>8.0934</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -18071,11 +18071,11 @@
         </is>
       </c>
       <c r="I85">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -18087,17 +18087,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D86">
@@ -18108,23 +18108,23 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="G86">
-        <v>8.15805</v>
+        <v>8.069</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I86">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -18136,17 +18136,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D87">
@@ -18157,23 +18157,23 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="G87">
-        <v>8.148</v>
+        <v>8.055</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I87">
-        <v>68</v>
+        <v>140</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -18185,17 +18185,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D88">
@@ -18206,23 +18206,23 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="G88">
-        <v>8.14</v>
+        <v>8.031</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I88">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -18234,17 +18234,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D89">
@@ -18255,23 +18255,23 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="G89">
-        <v>8.1355</v>
+        <v>8.01</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I89">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -18283,17 +18283,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D90">
@@ -18304,23 +18304,23 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="G90">
-        <v>8.135</v>
+        <v>8.003</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I90">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -18332,17 +18332,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D91">
@@ -18353,23 +18353,23 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="G91">
-        <v>8.13</v>
+        <v>7.963</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I91">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -18381,12 +18381,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -18406,19 +18406,19 @@
         </is>
       </c>
       <c r="G92">
-        <v>8.11835</v>
+        <v>7.953</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I92">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -18430,12 +18430,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18455,7 +18455,7 @@
         </is>
       </c>
       <c r="G93">
-        <v>8.11805</v>
+        <v>7.94805</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -18463,11 +18463,11 @@
         </is>
       </c>
       <c r="I93">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -18479,12 +18479,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -18504,19 +18504,19 @@
         </is>
       </c>
       <c r="G94">
-        <v>8.117</v>
+        <v>7.948</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I94">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -18528,17 +18528,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D95">
@@ -18549,11 +18549,11 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="G95">
-        <v>8.0934</v>
+        <v>7.9413</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -18561,11 +18561,11 @@
         </is>
       </c>
       <c r="I95">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -18577,17 +18577,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D96">
@@ -18598,23 +18598,23 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="G96">
-        <v>8.069</v>
+        <v>7.939</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I96">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -18626,17 +18626,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D97">
@@ -18647,23 +18647,23 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="G97">
-        <v>8.055</v>
+        <v>7.935</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I97">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -18675,12 +18675,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -18696,23 +18696,23 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="G98">
-        <v>8.031</v>
+        <v>7.933</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I98">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -18724,17 +18724,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D99">
@@ -18745,23 +18745,23 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="G99">
-        <v>8.01</v>
+        <v>7.893</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I99">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -18773,17 +18773,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D100">
@@ -18794,23 +18794,23 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="G100">
-        <v>8.003</v>
+        <v>7.892</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I100">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -18822,17 +18822,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D101">
@@ -18843,23 +18843,23 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="G101">
-        <v>7.963</v>
+        <v>7.856</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I101">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -18871,17 +18871,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D102">
@@ -18892,23 +18892,23 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="G102">
-        <v>7.953</v>
+        <v>7.81</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I102">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -18920,17 +18920,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">Jeremiyah Love</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D103">
@@ -18941,11 +18941,11 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="G103">
-        <v>7.94805</v>
+        <v>7.802</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -18953,11 +18953,11 @@
         </is>
       </c>
       <c r="I103">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -18969,12 +18969,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18994,19 +18994,19 @@
         </is>
       </c>
       <c r="G104">
-        <v>7.948</v>
+        <v>7.791</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I104">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -19018,17 +19018,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D105">
@@ -19039,23 +19039,23 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="G105">
-        <v>7.9413</v>
+        <v>7.776</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I105">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">WR68</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -19067,17 +19067,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D106">
@@ -19088,23 +19088,23 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="G106">
-        <v>7.939</v>
+        <v>7.7213</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I106">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -19116,17 +19116,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D107">
@@ -19137,23 +19137,23 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="G107">
-        <v>7.935</v>
+        <v>7.641</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I107">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -19165,17 +19165,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D108">
@@ -19186,23 +19186,23 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="G108">
-        <v>7.933</v>
+        <v>7.632</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I108">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -19214,12 +19214,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19235,23 +19235,23 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="G109">
-        <v>7.893</v>
+        <v>7.62325</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I109">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -19263,12 +19263,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19284,11 +19284,11 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="G110">
-        <v>7.892</v>
+        <v>7.601</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -19296,11 +19296,11 @@
         </is>
       </c>
       <c r="I110">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -19312,12 +19312,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -19333,23 +19333,23 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="G111">
-        <v>7.856</v>
+        <v>7.584</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I111">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -19361,17 +19361,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D112">
@@ -19382,23 +19382,23 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="G112">
-        <v>7.81</v>
+        <v>7.58</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I112">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -19410,17 +19410,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D113">
@@ -19431,23 +19431,23 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="G113">
-        <v>7.802</v>
+        <v>7.485</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I113">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -19459,17 +19459,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D114">
@@ -19480,23 +19480,23 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="G114">
-        <v>7.791</v>
+        <v>7.485</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I114">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -19508,17 +19508,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wan'Dale Robinson</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D115">
@@ -19529,40 +19529,40 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="G115">
-        <v>7.776</v>
+        <v>7.456</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I115">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR68</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rhamondre Stevenson</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -19578,23 +19578,23 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="G116">
-        <v>7.761</v>
+        <v>7.4535</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I116">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -19606,12 +19606,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -19627,23 +19627,23 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="G117">
-        <v>7.7213</v>
+        <v>7.425</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I117">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -19655,17 +19655,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D118">
@@ -19676,23 +19676,23 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="G118">
-        <v>7.641</v>
+        <v>7.37485</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I118">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -19704,17 +19704,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D119">
@@ -19725,23 +19725,23 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="G119">
-        <v>7.632</v>
+        <v>7.37</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I119">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -19753,12 +19753,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -19774,23 +19774,23 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="G120">
-        <v>7.62325</v>
+        <v>7.3335</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I120">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -19802,17 +19802,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D121">
@@ -19823,23 +19823,23 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="G121">
-        <v>7.601</v>
+        <v>7.3135</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I121">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -19851,17 +19851,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D122">
@@ -19872,23 +19872,23 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="G122">
-        <v>7.584</v>
+        <v>7.27</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I122">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -19900,12 +19900,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">Woody Marks</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -19921,23 +19921,23 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="G123">
-        <v>7.58</v>
+        <v>7.258</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I123">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -19949,17 +19949,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D124">
@@ -19970,11 +19970,11 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="G124">
-        <v>7.485</v>
+        <v>7.238</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -19982,11 +19982,11 @@
         </is>
       </c>
       <c r="I124">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">RB56</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -19998,12 +19998,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20019,11 +20019,11 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="G125">
-        <v>7.485</v>
+        <v>7.155</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -20031,11 +20031,11 @@
         </is>
       </c>
       <c r="I125">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -20047,12 +20047,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -20068,45 +20068,45 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="G126">
-        <v>7.456</v>
+        <v>7.08335</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I126">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">MODEL_RANK</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D127">
@@ -20117,23 +20117,23 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="G127">
-        <v>7.4535</v>
+        <v>7.08</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I127">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -20145,12 +20145,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="G128">
-        <v>7.425</v>
+        <v>6.998</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -20178,11 +20178,11 @@
         </is>
       </c>
       <c r="I128">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -20194,12 +20194,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -20215,23 +20215,23 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="G129">
-        <v>7.37485</v>
+        <v>6.9</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I129">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20243,12 +20243,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -20264,23 +20264,23 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="G130">
-        <v>7.37</v>
+        <v>6.885</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I130">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -20292,17 +20292,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D131">
@@ -20313,23 +20313,23 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="G131">
-        <v>7.3335</v>
+        <v>6.88</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I131">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -20341,17 +20341,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D132">
@@ -20362,23 +20362,23 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="G132">
-        <v>7.3135</v>
+        <v>6.73975</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I132">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -20390,17 +20390,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D133">
@@ -20411,23 +20411,23 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="G133">
-        <v>7.27</v>
+        <v>6.595</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I133">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -20439,17 +20439,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woody Marks</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D134">
@@ -20460,11 +20460,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="G134">
-        <v>7.258</v>
+        <v>6.55025</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -20472,11 +20472,11 @@
         </is>
       </c>
       <c r="I134">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -20488,12 +20488,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrone Tracy Jr.</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -20509,23 +20509,23 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="G135">
-        <v>7.238</v>
+        <v>6.401</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I135">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB56</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -20537,17 +20537,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D136">
@@ -20558,23 +20558,23 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="G136">
-        <v>7.155</v>
+        <v>6.355</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I136">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -20586,12 +20586,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Zach Charbonnet</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20607,11 +20607,11 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="G137">
-        <v>7.08335</v>
+        <v>6.18</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -20619,11 +20619,11 @@
         </is>
       </c>
       <c r="I137">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">RB66</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -20635,12 +20635,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -20651,16 +20651,20 @@
       <c r="D138">
         <v>7</v>
       </c>
-      <c r="E138">
-        <v>137</v>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>7.08</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -20668,77 +20672,81 @@
         </is>
       </c>
       <c r="I138">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D139">
         <v>7</v>
       </c>
-      <c r="E139">
-        <v>138</v>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>6.998</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I139">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -20749,45 +20757,49 @@
       <c r="D140">
         <v>7</v>
       </c>
-      <c r="E140">
-        <v>139</v>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
-        </is>
-      </c>
-      <c r="G140">
-        <v>6.9</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I140">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -20798,94 +20810,102 @@
       <c r="D141">
         <v>7</v>
       </c>
-      <c r="E141">
-        <v>140</v>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
-        </is>
-      </c>
-      <c r="G141">
-        <v>6.885</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I141">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D142">
         <v>7</v>
       </c>
-      <c r="E142">
-        <v>141</v>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
-        </is>
-      </c>
-      <c r="G142">
-        <v>6.885</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I142">
-        <v>183</v>
+        <v>97</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -20896,290 +20916,314 @@
       <c r="D143">
         <v>7</v>
       </c>
-      <c r="E143">
-        <v>142</v>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
-        </is>
-      </c>
-      <c r="G143">
-        <v>6.88</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I143">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D144">
         <v>7</v>
       </c>
-      <c r="E144">
-        <v>143</v>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
-        </is>
-      </c>
-      <c r="G144">
-        <v>6.73975</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I144">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D145">
         <v>7</v>
       </c>
-      <c r="E145">
-        <v>144</v>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
-        </is>
-      </c>
-      <c r="G145">
-        <v>6.595</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I145">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D146">
         <v>7</v>
       </c>
-      <c r="E146">
-        <v>145</v>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
-        </is>
-      </c>
-      <c r="G146">
-        <v>6.55025</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I146">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D147">
         <v>7</v>
       </c>
-      <c r="E147">
-        <v>146</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
-        </is>
-      </c>
-      <c r="G147">
-        <v>6.401</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I147">
-        <v>184</v>
+        <v>41</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D148">
         <v>7</v>
       </c>
-      <c r="E148">
-        <v>147</v>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
-        </is>
-      </c>
-      <c r="G148">
-        <v>6.355</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I148">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zach Charbonnet</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -21190,50 +21234,54 @@
       <c r="D149">
         <v>7</v>
       </c>
-      <c r="E149">
-        <v>148</v>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
-        </is>
-      </c>
-      <c r="G149">
-        <v>6.18</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I149">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB66</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D150">
@@ -21256,37 +21304,37 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I150">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D151">
@@ -21309,32 +21357,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I151">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21362,37 +21410,37 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I152">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D153">
@@ -21415,32 +21463,32 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I153">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21468,15 +21516,15 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I154">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -21488,17 +21536,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D155">
@@ -21521,37 +21569,37 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I155">
-        <v>139</v>
+        <v>40</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D156">
@@ -21574,37 +21622,37 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I156">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D157">
@@ -21627,37 +21675,37 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I157">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D158">
@@ -21684,28 +21732,28 @@
         </is>
       </c>
       <c r="I158">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -21737,11 +21785,11 @@
         </is>
       </c>
       <c r="I159">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -21753,12 +21801,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -21786,37 +21834,37 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I160">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D161">
@@ -21839,32 +21887,32 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I161">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -21892,37 +21940,37 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I162">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D163">
@@ -21949,33 +21997,33 @@
         </is>
       </c>
       <c r="I163">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D164">
@@ -21998,32 +22046,32 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I164">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -22051,37 +22099,37 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I165">
-        <v>95</v>
+        <v>196</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D166">
@@ -22108,11 +22156,11 @@
         </is>
       </c>
       <c r="I166">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">WR50</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -22124,12 +22172,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22157,37 +22205,37 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I167">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Jonathon Brooks</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D168">
@@ -22214,11 +22262,11 @@
         </is>
       </c>
       <c r="I168">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">RB45</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -22230,17 +22278,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Daniels</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D169">
@@ -22263,32 +22311,32 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I169">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB12</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Higgins</t>
+          <t xml:space="preserve">Jordyn Tyson</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -22320,11 +22368,11 @@
         </is>
       </c>
       <c r="I170">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR75</t>
+          <t xml:space="preserve">WR73</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -22336,17 +22384,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jayden Reed</t>
+          <t xml:space="preserve">Josh Allen</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D171">
@@ -22369,37 +22417,37 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I171">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
+          <t xml:space="preserve">QB1</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonah Coleman</t>
+          <t xml:space="preserve">Justin Herbert</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D172">
@@ -22422,37 +22470,37 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I172">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB48</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathon Brooks</t>
+          <t xml:space="preserve">Kalif Raymond</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D173">
@@ -22475,32 +22523,32 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I173">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Mason</t>
+          <t xml:space="preserve">Kaytron Allen</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -22528,37 +22576,37 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I174">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">RB60</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordyn Tyson</t>
+          <t xml:space="preserve">Keaton Mitchell</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D175">
@@ -22581,27 +22629,27 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I175">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR73</t>
+          <t xml:space="preserve">RB59</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen</t>
+          <t xml:space="preserve">Khalil Shakir</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -22611,7 +22659,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D176">
@@ -22634,15 +22682,15 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I176">
-        <v>31</v>
+        <v>117</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB1</t>
+          <t xml:space="preserve">WR53</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -22654,17 +22702,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Herbert</t>
+          <t xml:space="preserve">Kyle Monangai</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D177">
@@ -22687,37 +22735,37 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I177">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaytron Allen</t>
+          <t xml:space="preserve">Ladd McConkey</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D178">
@@ -22740,15 +22788,15 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I178">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB60</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -22760,17 +22808,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keaton Mitchell</t>
+          <t xml:space="preserve">Luther Burden III</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D179">
@@ -22793,32 +22841,32 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I179">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB59</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khalil Shakir</t>
+          <t xml:space="preserve">Mack Hollins</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -22846,37 +22894,37 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I180">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR53</t>
+          <t xml:space="preserve">WR55</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Monangai</t>
+          <t xml:space="preserve">Marcus Mariota</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D181">
@@ -22899,32 +22947,32 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">DOUBTFUL</t>
         </is>
       </c>
       <c r="I181">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">QB9</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladd McConkey</t>
+          <t xml:space="preserve">Michael Pittman Jr.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -22952,37 +23000,37 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I182">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">WR62</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mack Hollins</t>
+          <t xml:space="preserve">Omarion Hampton</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D183">
@@ -23005,37 +23053,37 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I183">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR55</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota</t>
+          <t xml:space="preserve">Oronde Gadsden II</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D184">
@@ -23058,15 +23106,15 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOUBTFUL</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I184">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB9</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -23078,12 +23126,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Pittman Jr.</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -23111,27 +23159,27 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I185">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR62</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omarion Hampton</t>
+          <t xml:space="preserve">Quentin Johnston</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -23141,7 +23189,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D186">
@@ -23164,15 +23212,15 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I186">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">WR57</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -23184,17 +23232,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oronde Gadsden II</t>
+          <t xml:space="preserve">Rachaad White</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D187">
@@ -23217,15 +23265,15 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I187">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -23237,17 +23285,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Rhamondre Stevenson</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D188">
@@ -23270,32 +23318,32 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I188">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quentin Johnston</t>
+          <t xml:space="preserve">Rome Odunze</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -23323,37 +23371,37 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I189">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR57</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rachaad White</t>
+          <t xml:space="preserve">Romeo Doubs</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D190">
@@ -23376,32 +23424,32 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I190">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">WR60</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romeo Doubs</t>
+          <t xml:space="preserve">Stefon Diggs</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -23429,37 +23477,37 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I191">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR60</t>
+          <t xml:space="preserve">WR64</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stefon Diggs</t>
+          <t xml:space="preserve">Tank Bigsby</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D192">
@@ -23482,37 +23530,37 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I192">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR64</t>
+          <t xml:space="preserve">RB62</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Bigsby</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D193">
@@ -23539,11 +23587,11 @@
         </is>
       </c>
       <c r="I193">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB62</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -23555,12 +23603,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tank Dell</t>
+          <t xml:space="preserve">Terry McLaurin</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -23588,37 +23636,37 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I194">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR74</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terry McLaurin</t>
+          <t xml:space="preserve">Travis Etienne Jr.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D195">
@@ -23641,37 +23689,37 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I195">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Etienne Jr.</t>
+          <t xml:space="preserve">Tre' Harris</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Los Angeles Chargers</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D196">
@@ -23694,37 +23742,37 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I196">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">WR70</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre' Harris</t>
+          <t xml:space="preserve">TreVeyon Henderson</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Chargers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D197">
@@ -23747,20 +23795,20 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I197">
-        <v>176</v>
+        <v>54</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR70</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
@@ -23800,7 +23848,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I198">

--- a/exports/fantasy-2026-current.xlsx
+++ b/exports/fantasy-2026-current.xlsx
@@ -14147,7 +14147,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I5">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I6">
@@ -14216,17 +14216,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Jackson</t>
+          <t xml:space="preserve">Trey McBride</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D7">
@@ -14237,23 +14237,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="G7">
-        <v>9.54</v>
+        <v>9.386</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB2</t>
+          <t xml:space="preserve">TE1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -14265,17 +14265,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trey McBride</t>
+          <t xml:space="preserve">Joe Burrow</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D8">
@@ -14286,11 +14286,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB2</t>
         </is>
       </c>
       <c r="G8">
-        <v>9.386</v>
+        <v>9.375</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -14298,11 +14298,11 @@
         </is>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE1</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -14314,17 +14314,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joe Burrow</t>
+          <t xml:space="preserve">Justin Jefferson</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D9">
@@ -14335,11 +14335,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="G9">
-        <v>9.375</v>
+        <v>9.373</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -14347,11 +14347,11 @@
         </is>
       </c>
       <c r="I9">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -14363,17 +14363,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justin Jefferson</t>
+          <t xml:space="preserve">Jonathan Taylor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D10">
@@ -14384,11 +14384,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">RB3</t>
         </is>
       </c>
       <c r="G10">
-        <v>9.373</v>
+        <v>9.3675</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -14396,11 +14396,11 @@
         </is>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -14412,12 +14412,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Christian McCaffrey</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14433,23 +14433,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t xml:space="preserve">RB4</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>9.34</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t xml:space="preserve">RB3</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>9.3675</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14461,17 +14461,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian McCaffrey</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D12">
@@ -14482,11 +14482,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">WR4</t>
         </is>
       </c>
       <c r="G12">
-        <v>9.34</v>
+        <v>9.305</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -14494,11 +14494,11 @@
         </is>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB3</t>
+          <t xml:space="preserve">WR3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14510,12 +14510,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">CeeDee Lamb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14531,23 +14531,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR4</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="G13">
-        <v>9.305</v>
+        <v>9.286</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR3</t>
+          <t xml:space="preserve">WR5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14559,12 +14559,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CeeDee Lamb</t>
+          <t xml:space="preserve">Nico Collins</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14580,11 +14580,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">WR6</t>
         </is>
       </c>
       <c r="G14">
-        <v>9.286</v>
+        <v>9.26325</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -14592,11 +14592,11 @@
         </is>
       </c>
       <c r="I14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR5</t>
+          <t xml:space="preserve">WR8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14608,17 +14608,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nico Collins</t>
+          <t xml:space="preserve">Brock Bowers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D15">
@@ -14629,11 +14629,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR6</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="G15">
-        <v>9.26325</v>
+        <v>9.26</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14641,11 +14641,11 @@
         </is>
       </c>
       <c r="I15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR8</t>
+          <t xml:space="preserve">TE2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14657,17 +14657,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Bowers</t>
+          <t xml:space="preserve">Puka Nacua</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D16">
@@ -14678,23 +14678,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="G16">
-        <v>9.26</v>
+        <v>9.256</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I16">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE2</t>
+          <t xml:space="preserve">WR2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14706,17 +14706,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Puka Nacua</t>
+          <t xml:space="preserve">Derrick Henry</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D17">
@@ -14727,23 +14727,23 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">RB5</t>
         </is>
       </c>
       <c r="G17">
-        <v>9.256</v>
+        <v>9.101</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR2</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -14755,12 +14755,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashee Rice</t>
+          <t xml:space="preserve">Drake London</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14780,19 +14780,19 @@
         </is>
       </c>
       <c r="G18">
-        <v>9.113</v>
+        <v>9.09</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I18">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">WR7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14804,17 +14804,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derrick Henry</t>
+          <t xml:space="preserve">Bo Nix</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D19">
@@ -14825,11 +14825,11 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB5</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="G19">
-        <v>9.101</v>
+        <v>9.076</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -14837,11 +14837,11 @@
         </is>
       </c>
       <c r="I19">
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14853,17 +14853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake London</t>
+          <t xml:space="preserve">Brock Purdy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D20">
@@ -14874,11 +14874,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="G20">
-        <v>9.09</v>
+        <v>9.06</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -14886,11 +14886,11 @@
         </is>
       </c>
       <c r="I20">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR7</t>
+          <t xml:space="preserve">QB20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14902,12 +14902,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Nix</t>
+          <t xml:space="preserve">Jared Goff</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -14923,11 +14923,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">QB5</t>
         </is>
       </c>
       <c r="G21">
-        <v>9.076</v>
+        <v>9.058</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -14935,11 +14935,11 @@
         </is>
       </c>
       <c r="I21">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">QB21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14951,17 +14951,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brock Purdy</t>
+          <t xml:space="preserve">George Pickens</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D22">
@@ -14972,11 +14972,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB5</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="G22">
-        <v>9.06</v>
+        <v>9.028</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -14984,11 +14984,11 @@
         </is>
       </c>
       <c r="I22">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -15000,17 +15000,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff</t>
+          <t xml:space="preserve">Kyren Williams</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D23">
@@ -15021,11 +15021,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="G23">
-        <v>9.058</v>
+        <v>9.022</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -15033,11 +15033,11 @@
         </is>
       </c>
       <c r="I23">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB21</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -15049,17 +15049,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Pickens</t>
+          <t xml:space="preserve">Michael Penix Jr.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D24">
@@ -15070,23 +15070,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="G24">
-        <v>9.028</v>
+        <v>9.0216</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I24">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">QB4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -15098,12 +15098,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyren Williams</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15119,11 +15119,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="G25">
-        <v>9.022</v>
+        <v>9.02</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -15131,11 +15131,11 @@
         </is>
       </c>
       <c r="I25">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -15147,12 +15147,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Penix Jr.</t>
+          <t xml:space="preserve">Dak Prescott</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="G26">
-        <v>9.0216</v>
+        <v>9.012</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -15180,11 +15180,11 @@
         </is>
       </c>
       <c r="I26">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB4</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -15196,12 +15196,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Saquon Barkley</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15217,23 +15217,23 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">RB8</t>
         </is>
       </c>
       <c r="G27">
-        <v>9.02</v>
+        <v>9.006</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I27">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -15245,17 +15245,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dak Prescott</t>
+          <t xml:space="preserve">Chase Brown</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D28">
@@ -15266,11 +15266,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="G28">
-        <v>9.012</v>
+        <v>9.003</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -15278,11 +15278,11 @@
         </is>
       </c>
       <c r="I28">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">RB9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -15294,17 +15294,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saquon Barkley</t>
+          <t xml:space="preserve">Jalon Daniels</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D29">
@@ -15315,23 +15315,23 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB8</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="G29">
-        <v>9.006</v>
+        <v>8.9911</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I29">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">QB6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -15343,17 +15343,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chase Brown</t>
+          <t xml:space="preserve">Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D30">
@@ -15364,11 +15364,11 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="G30">
-        <v>9.003</v>
+        <v>8.991</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -15376,11 +15376,11 @@
         </is>
       </c>
       <c r="I30">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB9</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -15392,12 +15392,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalon Daniels</t>
+          <t xml:space="preserve">Jameis Winston</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15417,7 +15417,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>8.9911</v>
+        <v>8.9816</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -15425,11 +15425,11 @@
         </is>
       </c>
       <c r="I31">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB6</t>
+          <t xml:space="preserve">QB8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15441,17 +15441,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tetairoa McMillan</t>
+          <t xml:space="preserve">Kirk Cousins</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D32">
@@ -15462,11 +15462,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">QB10</t>
         </is>
       </c>
       <c r="G32">
-        <v>8.991</v>
+        <v>8.9616</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -15474,11 +15474,11 @@
         </is>
       </c>
       <c r="I32">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">QB7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15490,17 +15490,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D33">
@@ -15511,23 +15511,23 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB10</t>
+          <t xml:space="preserve">RB10</t>
         </is>
       </c>
       <c r="G33">
-        <v>8.9816</v>
+        <v>8.935</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I33">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB8</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -15539,12 +15539,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirk Cousins</t>
+          <t xml:space="preserve">Baker Mayfield</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15564,19 +15564,19 @@
         </is>
       </c>
       <c r="G34">
-        <v>8.9616</v>
+        <v>8.926</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I34">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB7</t>
+          <t xml:space="preserve">QB25</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -15588,17 +15588,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Chris Olave</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D35">
@@ -15609,23 +15609,23 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB10</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="G35">
-        <v>8.935</v>
+        <v>8.91525</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I35">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">WR11</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -15637,12 +15637,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baker Mayfield</t>
+          <t xml:space="preserve">Kyler Murray</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15662,19 +15662,19 @@
         </is>
       </c>
       <c r="G36">
-        <v>8.926</v>
+        <v>8.8835</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I36">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB25</t>
+          <t xml:space="preserve">QB22</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -15686,17 +15686,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Olave</t>
+          <t xml:space="preserve">Ashton Jeanty</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D37">
@@ -15707,11 +15707,11 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR12</t>
+          <t xml:space="preserve">RB11</t>
         </is>
       </c>
       <c r="G37">
-        <v>8.91525</v>
+        <v>8.88</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -15719,11 +15719,11 @@
         </is>
       </c>
       <c r="I37">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR11</t>
+          <t xml:space="preserve">RB7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -15735,12 +15735,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyler Murray</t>
+          <t xml:space="preserve">Matthew Stafford</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -15760,7 +15760,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>8.8835</v>
+        <v>8.834</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -15768,11 +15768,11 @@
         </is>
       </c>
       <c r="I38">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB22</t>
+          <t xml:space="preserve">QB23</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15784,17 +15784,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ashton Jeanty</t>
+          <t xml:space="preserve">Zay Flowers</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D39">
@@ -15805,11 +15805,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB11</t>
+          <t xml:space="preserve">WR12</t>
         </is>
       </c>
       <c r="G39">
-        <v>8.88</v>
+        <v>8.776</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -15817,11 +15817,11 @@
         </is>
       </c>
       <c r="I39">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB7</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -15833,17 +15833,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeVonta Smith</t>
+          <t xml:space="preserve">Jordan Love</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D40">
@@ -15854,23 +15854,23 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR13</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="G40">
-        <v>8.864</v>
+        <v>8.75</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I40">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR9</t>
+          <t xml:space="preserve">QB26</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -15882,17 +15882,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Stafford</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D41">
@@ -15903,11 +15903,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">WR13</t>
         </is>
       </c>
       <c r="G41">
-        <v>8.834</v>
+        <v>8.68</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -15915,11 +15915,11 @@
         </is>
       </c>
       <c r="I41">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB23</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -15931,17 +15931,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zay Flowers</t>
+          <t xml:space="preserve">Tyler Shough</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D42">
@@ -15952,11 +15952,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">QB15</t>
         </is>
       </c>
       <c r="G42">
-        <v>8.776</v>
+        <v>8.62625</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -15964,11 +15964,11 @@
         </is>
       </c>
       <c r="I42">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">QB24</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -15980,17 +15980,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Love</t>
+          <t xml:space="preserve">Tee Higgins</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Cincinnati Bengals</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D43">
@@ -16001,23 +16001,23 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB15</t>
+          <t xml:space="preserve">WR14</t>
         </is>
       </c>
       <c r="G43">
-        <v>8.75</v>
+        <v>8.607</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I43">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB26</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -16029,17 +16029,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Javonte Williams</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D44">
@@ -16050,11 +16050,11 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR15</t>
+          <t xml:space="preserve">RB12</t>
         </is>
       </c>
       <c r="G44">
-        <v>8.68</v>
+        <v>8.601</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -16062,11 +16062,11 @@
         </is>
       </c>
       <c r="I44">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR14</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -16078,17 +16078,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Shough</t>
+          <t xml:space="preserve">Kyle Pitts</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D45">
@@ -16099,23 +16099,23 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB16</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="G45">
-        <v>8.62625</v>
+        <v>8.6</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I45">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB24</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -16127,12 +16127,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tee Higgins</t>
+          <t xml:space="preserve">Jaylen Waddle</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cincinnati Bengals</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -16148,11 +16148,11 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">WR15</t>
         </is>
       </c>
       <c r="G46">
-        <v>8.607</v>
+        <v>8.59925</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -16160,11 +16160,11 @@
         </is>
       </c>
       <c r="I46">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -16176,17 +16176,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Javonte Williams</t>
+          <t xml:space="preserve">Jameson Williams</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D47">
@@ -16197,11 +16197,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB12</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="G47">
-        <v>8.601</v>
+        <v>8.549</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -16209,11 +16209,11 @@
         </is>
       </c>
       <c r="I47">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">WR16</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -16225,17 +16225,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyle Pitts</t>
+          <t xml:space="preserve">Sam Darnold</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D48">
@@ -16246,23 +16246,23 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">QB16</t>
         </is>
       </c>
       <c r="G48">
-        <v>8.6</v>
+        <v>8.448</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I48">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">QB28</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -16274,12 +16274,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Waddle</t>
+          <t xml:space="preserve">Malik Nabers</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -16299,19 +16299,19 @@
         </is>
       </c>
       <c r="G49">
-        <v>8.59925</v>
+        <v>8.4431</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I49">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16323,17 +16323,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameson Williams</t>
+          <t xml:space="preserve">C.J. Stroud</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D50">
@@ -16344,11 +16344,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR18</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="G50">
-        <v>8.549</v>
+        <v>8.4265</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -16356,11 +16356,11 @@
         </is>
       </c>
       <c r="I50">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR16</t>
+          <t xml:space="preserve">QB29</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -16372,17 +16372,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emeka Egbuka</t>
+          <t xml:space="preserve">Daniel Jones</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D51">
@@ -16393,23 +16393,23 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="G51">
-        <v>8.534</v>
+        <v>8.352</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I51">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR19</t>
+          <t xml:space="preserve">QB18</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -16421,17 +16421,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold</t>
+          <t xml:space="preserve">Bucky Irving</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D52">
@@ -16442,23 +16442,23 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>
+          <t xml:space="preserve">RB13</t>
         </is>
       </c>
       <c r="G52">
-        <v>8.448</v>
+        <v>8.34</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I52">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB28</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -16470,12 +16470,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Nabers</t>
+          <t xml:space="preserve">Rashod Bateman</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16491,23 +16491,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR20</t>
+          <t xml:space="preserve">WR18</t>
         </is>
       </c>
       <c r="G53">
-        <v>8.4431</v>
+        <v>8.335</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I53">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -16519,17 +16519,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud</t>
+          <t xml:space="preserve">Ted Hurst III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D54">
@@ -16540,23 +16540,23 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="G54">
-        <v>8.4265</v>
+        <v>8.325</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I54">
-        <v>194</v>
+        <v>75</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB29</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -16568,17 +16568,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Warren</t>
+          <t xml:space="preserve">Devaughn Vele</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D55">
@@ -16589,23 +16589,23 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">WR20</t>
         </is>
       </c>
       <c r="G55">
-        <v>8.406</v>
+        <v>8.285</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I55">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE4</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -16617,17 +16617,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel Jones</t>
+          <t xml:space="preserve">Mark Andrews</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Baltimore Ravens</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D56">
@@ -16638,11 +16638,11 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB19</t>
+          <t xml:space="preserve">TE4</t>
         </is>
       </c>
       <c r="G56">
-        <v>8.352</v>
+        <v>8.285</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -16650,11 +16650,11 @@
         </is>
       </c>
       <c r="I56">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB18</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -16666,17 +16666,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Montgomery</t>
+          <t xml:space="preserve">Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D57">
@@ -16687,45 +16687,45 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB13</t>
+          <t xml:space="preserve">WR21</t>
         </is>
       </c>
       <c r="G57">
-        <v>8.348</v>
+        <v>8.278</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I57">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bucky Irving</t>
+          <t xml:space="preserve">Harold Fannin Jr.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D58">
@@ -16736,23 +16736,23 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB14</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="G58">
-        <v>8.34</v>
+        <v>8.276</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I58">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">TE5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16764,17 +16764,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashod Bateman</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D59">
@@ -16785,23 +16785,23 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR21</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="G59">
-        <v>8.335</v>
+        <v>8.275</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I59">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">TE21</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16813,17 +16813,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ted Hurst III</t>
+          <t xml:space="preserve">Dalton Schultz</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D60">
@@ -16834,11 +16834,11 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR22</t>
+          <t xml:space="preserve">TE7</t>
         </is>
       </c>
       <c r="G60">
-        <v>8.325</v>
+        <v>8.25685</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -16846,11 +16846,11 @@
         </is>
       </c>
       <c r="I60">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16862,17 +16862,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devaughn Vele</t>
+          <t xml:space="preserve">Mike Washington Jr.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D61">
@@ -16883,23 +16883,23 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">RB14</t>
         </is>
       </c>
       <c r="G61">
-        <v>8.285</v>
+        <v>8.24425</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I61">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">RB46</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -16911,17 +16911,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Andrews</t>
+          <t xml:space="preserve">Tre Tucker</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baltimore Ravens</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D62">
@@ -16932,11 +16932,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">WR22</t>
         </is>
       </c>
       <c r="G62">
-        <v>8.285</v>
+        <v>8.235</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -16944,11 +16944,11 @@
         </is>
       </c>
       <c r="I62">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -16960,17 +16960,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marvin Harrison Jr.</t>
+          <t xml:space="preserve">Juwan Johnson</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D63">
@@ -16981,11 +16981,11 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR24</t>
+          <t xml:space="preserve">TE8</t>
         </is>
       </c>
       <c r="G63">
-        <v>8.278</v>
+        <v>8.22685</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -16993,28 +16993,28 @@
         </is>
       </c>
       <c r="I63">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">MODEL_RANK</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harold Fannin Jr.</t>
+          <t xml:space="preserve">Kenyon Sadiq</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -17030,11 +17030,11 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="G64">
-        <v>8.276</v>
+        <v>8.20685</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -17042,11 +17042,11 @@
         </is>
       </c>
       <c r="I64">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE5</t>
+          <t xml:space="preserve">TE9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17058,17 +17058,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">Denzel Boston</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D65">
@@ -17079,23 +17079,23 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE7</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="G65">
-        <v>8.275</v>
+        <v>8.205</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I65">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE21</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -17107,17 +17107,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dontayvion Wicks</t>
+          <t xml:space="preserve">Jake Ferguson</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Dallas Cowboys</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D66">
@@ -17128,23 +17128,23 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR25</t>
+          <t xml:space="preserve">TE10</t>
         </is>
       </c>
       <c r="G66">
-        <v>8.265</v>
+        <v>8.199</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I66">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -17156,12 +17156,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Schultz</t>
+          <t xml:space="preserve">Tyler Higbee</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -17177,23 +17177,23 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t xml:space="preserve">TE11</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>8.18835</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I67">
+        <v>81</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t xml:space="preserve">TE8</t>
-        </is>
-      </c>
-      <c r="G67">
-        <v>8.25685</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
-        </is>
-      </c>
-      <c r="I67">
-        <v>91</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TE11</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -17205,17 +17205,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Washington Jr.</t>
+          <t xml:space="preserve">Josh Downs</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D68">
@@ -17226,23 +17226,23 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB15</t>
+          <t xml:space="preserve">WR24</t>
         </is>
       </c>
       <c r="G68">
-        <v>8.24425</v>
+        <v>8.16525</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I68">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB46</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -17254,12 +17254,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tre Tucker</t>
+          <t xml:space="preserve">Keenan Allen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -17275,11 +17275,11 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR26</t>
+          <t xml:space="preserve">WR25</t>
         </is>
       </c>
       <c r="G69">
-        <v>8.235</v>
+        <v>8.15805</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -17287,11 +17287,11 @@
         </is>
       </c>
       <c r="I69">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -17303,12 +17303,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juwan Johnson</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17324,11 +17324,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="G70">
-        <v>8.22685</v>
+        <v>8.148</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -17336,11 +17336,11 @@
         </is>
       </c>
       <c r="I70">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">TE6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -17352,17 +17352,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenyon Sadiq</t>
+          <t xml:space="preserve">MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D71">
@@ -17373,11 +17373,11 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE10</t>
+          <t xml:space="preserve">RB15</t>
         </is>
       </c>
       <c r="G71">
-        <v>8.20685</v>
+        <v>8.1355</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -17385,11 +17385,11 @@
         </is>
       </c>
       <c r="I71">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE9</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -17401,17 +17401,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denzel Boston</t>
+          <t xml:space="preserve">Dallas Goedert</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D72">
@@ -17422,23 +17422,23 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="G72">
-        <v>8.205</v>
+        <v>8.135</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I72">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">TE20</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -17450,17 +17450,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake Ferguson</t>
+          <t xml:space="preserve">Courtland Sutton</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Cowboys</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D73">
@@ -17471,11 +17471,11 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE11</t>
+          <t xml:space="preserve">WR26</t>
         </is>
       </c>
       <c r="G73">
-        <v>8.199</v>
+        <v>8.13</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -17483,11 +17483,11 @@
         </is>
       </c>
       <c r="I73">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -17499,12 +17499,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Higbee</t>
+          <t xml:space="preserve">Darren Waller</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17520,23 +17520,23 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="G74">
-        <v>8.18835</v>
+        <v>8.11835</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I74">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE8</t>
+          <t xml:space="preserve">TE14</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -17548,12 +17548,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Evans</t>
+          <t xml:space="preserve">Adonai Mitchell</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17569,23 +17569,23 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR28</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="G75">
-        <v>8.188</v>
+        <v>8.11805</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I75">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">WR52</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -17597,12 +17597,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Downs</t>
+          <t xml:space="preserve">Carnell Tate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -17618,11 +17618,11 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR29</t>
+          <t xml:space="preserve">WR28</t>
         </is>
       </c>
       <c r="G76">
-        <v>8.16525</v>
+        <v>8.117</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -17630,11 +17630,11 @@
         </is>
       </c>
       <c r="I76">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">WR27</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -17646,12 +17646,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keenan Allen</t>
+          <t xml:space="preserve">Konata Mumpfield</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -17667,11 +17667,11 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">WR29</t>
         </is>
       </c>
       <c r="G77">
-        <v>8.15805</v>
+        <v>8.0934</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -17679,11 +17679,11 @@
         </is>
       </c>
       <c r="I77">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">WR48</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -17695,17 +17695,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam LaPorta</t>
+          <t xml:space="preserve">Cam Skattebo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D78">
@@ -17716,11 +17716,11 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">RB16</t>
         </is>
       </c>
       <c r="G78">
-        <v>8.148</v>
+        <v>8.069</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -17728,11 +17728,11 @@
         </is>
       </c>
       <c r="I78">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE6</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -17744,12 +17744,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">MarShawn Lloyd</t>
+          <t xml:space="preserve">Chuba Hubbard</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17765,23 +17765,23 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB16</t>
+          <t xml:space="preserve">RB17</t>
         </is>
       </c>
       <c r="G79">
-        <v>8.1355</v>
+        <v>8.055</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I79">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -17793,17 +17793,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas Goedert</t>
+          <t xml:space="preserve">Quinshon Judkins</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D80">
@@ -17814,23 +17814,23 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">RB18</t>
         </is>
       </c>
       <c r="G80">
-        <v>8.135</v>
+        <v>8.031</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I80">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -17842,12 +17842,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Courtland Sutton</t>
+          <t xml:space="preserve">Jordan Addison</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -17863,11 +17863,11 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR31</t>
+          <t xml:space="preserve">WR30</t>
         </is>
       </c>
       <c r="G81">
-        <v>8.13</v>
+        <v>8.01</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -17875,11 +17875,11 @@
         </is>
       </c>
       <c r="I81">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR30</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -17891,17 +17891,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darren Waller</t>
+          <t xml:space="preserve">Jaylen Warren</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D82">
@@ -17912,11 +17912,11 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE15</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="G82">
-        <v>8.11835</v>
+        <v>8.003</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -17924,11 +17924,11 @@
         </is>
       </c>
       <c r="I82">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE14</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -17940,17 +17940,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adonai Mitchell</t>
+          <t xml:space="preserve">George Kittle</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D83">
@@ -17961,23 +17961,23 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR32</t>
+          <t xml:space="preserve">TE15</t>
         </is>
       </c>
       <c r="G83">
-        <v>8.11805</v>
+        <v>7.963</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I83">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR52</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -17989,17 +17989,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carnell Tate</t>
+          <t xml:space="preserve">Tucker Kraft</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D84">
@@ -18010,11 +18010,11 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR33</t>
+          <t xml:space="preserve">TE16</t>
         </is>
       </c>
       <c r="G84">
-        <v>8.117</v>
+        <v>7.953</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -18022,11 +18022,11 @@
         </is>
       </c>
       <c r="I84">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR27</t>
+          <t xml:space="preserve">TE24</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -18038,12 +18038,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Konata Mumpfield</t>
+          <t xml:space="preserve">Caleb Douglas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -18059,23 +18059,23 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR34</t>
+          <t xml:space="preserve">WR31</t>
         </is>
       </c>
       <c r="G85">
-        <v>8.0934</v>
+        <v>7.94805</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I85">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">WR56</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -18087,17 +18087,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cam Skattebo</t>
+          <t xml:space="preserve">Christian Watson</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D86">
@@ -18108,11 +18108,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB17</t>
+          <t xml:space="preserve">WR32</t>
         </is>
       </c>
       <c r="G86">
-        <v>8.069</v>
+        <v>7.948</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -18120,11 +18120,11 @@
         </is>
       </c>
       <c r="I86">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -18136,12 +18136,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chuba Hubbard</t>
+          <t xml:space="preserve">Emanuel Wilson</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -18157,11 +18157,11 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB18</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="G87">
-        <v>8.055</v>
+        <v>7.9413</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -18169,11 +18169,11 @@
         </is>
       </c>
       <c r="I87">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -18185,17 +18185,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quinshon Judkins</t>
+          <t xml:space="preserve">DK Metcalf</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D88">
@@ -18206,23 +18206,23 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB19</t>
+          <t xml:space="preserve">WR33</t>
         </is>
       </c>
       <c r="G88">
-        <v>8.031</v>
+        <v>7.939</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I88">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">WR49</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -18234,17 +18234,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan Addison</t>
+          <t xml:space="preserve">Isaiah Likely</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D89">
@@ -18255,23 +18255,23 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR35</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="G89">
-        <v>8.01</v>
+        <v>7.935</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I89">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">TE13</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -18283,12 +18283,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Warren</t>
+          <t xml:space="preserve">Tony Pollard</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -18304,11 +18304,11 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">RB21</t>
         </is>
       </c>
       <c r="G90">
-        <v>8.003</v>
+        <v>7.933</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -18316,11 +18316,11 @@
         </is>
       </c>
       <c r="I90">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -18332,17 +18332,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Kittle</t>
+          <t xml:space="preserve">RJ Harvey</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D91">
@@ -18353,11 +18353,11 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">RB22</t>
         </is>
       </c>
       <c r="G91">
-        <v>7.963</v>
+        <v>7.893</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -18365,11 +18365,11 @@
         </is>
       </c>
       <c r="I91">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE16</t>
+          <t xml:space="preserve">RB51</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -18381,17 +18381,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tucker Kraft</t>
+          <t xml:space="preserve">Makai Lemon</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D92">
@@ -18402,23 +18402,23 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">WR34</t>
         </is>
       </c>
       <c r="G92">
-        <v>7.953</v>
+        <v>7.892</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I92">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE24</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -18430,12 +18430,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Douglas</t>
+          <t xml:space="preserve">Chris Godwin Jr.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18451,23 +18451,23 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">WR35</t>
         </is>
       </c>
       <c r="G93">
-        <v>7.94805</v>
+        <v>7.856</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I93">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR56</t>
+          <t xml:space="preserve">WR65</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -18479,17 +18479,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Watson</t>
+          <t xml:space="preserve">Malik Willis</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D94">
@@ -18500,23 +18500,23 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR37</t>
+          <t xml:space="preserve">QB19</t>
         </is>
       </c>
       <c r="G94">
-        <v>7.948</v>
+        <v>7.81</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I94">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR36</t>
+          <t xml:space="preserve">QB27</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -18528,17 +18528,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emanuel Wilson</t>
+          <t xml:space="preserve">Jalen Coker</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Carolina Panthers</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D95">
@@ -18549,23 +18549,23 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB21</t>
+          <t xml:space="preserve">WR36</t>
         </is>
       </c>
       <c r="G95">
-        <v>7.9413</v>
+        <v>7.791</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I95">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">WR61</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -18577,12 +18577,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">DK Metcalf</t>
+          <t xml:space="preserve">Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">Tennessee Titans</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -18598,11 +18598,11 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR38</t>
+          <t xml:space="preserve">WR37</t>
         </is>
       </c>
       <c r="G96">
-        <v>7.939</v>
+        <v>7.776</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -18610,11 +18610,11 @@
         </is>
       </c>
       <c r="I96">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
+          <t xml:space="preserve">WR68</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -18626,17 +18626,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaiah Likely</t>
+          <t xml:space="preserve">Ollie Gordon II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D97">
@@ -18647,11 +18647,11 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE18</t>
+          <t xml:space="preserve">RB23</t>
         </is>
       </c>
       <c r="G97">
-        <v>7.935</v>
+        <v>7.7213</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -18659,11 +18659,11 @@
         </is>
       </c>
       <c r="I97">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE13</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -18675,17 +18675,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony Pollard</t>
+          <t xml:space="preserve">KC Concepcion</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">Cleveland Browns</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D98">
@@ -18696,11 +18696,11 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">WR38</t>
         </is>
       </c>
       <c r="G98">
-        <v>7.933</v>
+        <v>7.641</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -18708,11 +18708,11 @@
         </is>
       </c>
       <c r="I98">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">WR58</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -18724,17 +18724,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RJ Harvey</t>
+          <t xml:space="preserve">Michael Wilson</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D99">
@@ -18745,11 +18745,11 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB23</t>
+          <t xml:space="preserve">WR39</t>
         </is>
       </c>
       <c r="G99">
-        <v>7.893</v>
+        <v>7.632</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -18757,11 +18757,11 @@
         </is>
       </c>
       <c r="I99">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB51</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -18773,17 +18773,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makai Lemon</t>
+          <t xml:space="preserve">Tyler Allgeier</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Arizona Cardinals</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D100">
@@ -18794,11 +18794,11 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR39</t>
+          <t xml:space="preserve">RB24</t>
         </is>
       </c>
       <c r="G100">
-        <v>7.892</v>
+        <v>7.62325</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -18806,11 +18806,11 @@
         </is>
       </c>
       <c r="I100">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -18822,12 +18822,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Godwin Jr.</t>
+          <t xml:space="preserve">Rashid Shaheed</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -18847,19 +18847,19 @@
         </is>
       </c>
       <c r="G101">
-        <v>7.856</v>
+        <v>7.601</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I101">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR65</t>
+          <t xml:space="preserve">WR63</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -18871,17 +18871,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Willis</t>
+          <t xml:space="preserve">Matthew Golden</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D102">
@@ -18892,23 +18892,23 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB20</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="G102">
-        <v>7.81</v>
+        <v>7.584</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
         </is>
       </c>
       <c r="I102">
-        <v>190</v>
+        <v>122</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB27</t>
+          <t xml:space="preserve">WR54</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -18920,12 +18920,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeremiyah Love</t>
+          <t xml:space="preserve">Rico Dowdle</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Pittsburgh Steelers</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -18941,11 +18941,11 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB24</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="G103">
-        <v>7.802</v>
+        <v>7.58</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -18953,11 +18953,11 @@
         </is>
       </c>
       <c r="I103">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB22</t>
+          <t xml:space="preserve">RB47</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -18969,12 +18969,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Coker</t>
+          <t xml:space="preserve">Xavier Worthy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina Panthers</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18990,11 +18990,11 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR41</t>
+          <t xml:space="preserve">WR42</t>
         </is>
       </c>
       <c r="G104">
-        <v>7.791</v>
+        <v>7.485</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -19002,11 +19002,11 @@
         </is>
       </c>
       <c r="I104">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR61</t>
+          <t xml:space="preserve">WR59</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -19018,7 +19018,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wan'Dale Robinson</t>
+          <t xml:space="preserve">Tyjae Spears</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -19028,7 +19028,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D105">
@@ -19039,23 +19039,23 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR42</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="G105">
-        <v>7.776</v>
+        <v>7.485</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I105">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR68</t>
+          <t xml:space="preserve">RB55</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -19067,12 +19067,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollie Gordon II</t>
+          <t xml:space="preserve">Kenneth Gainwell</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -19088,11 +19088,11 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">RB27</t>
         </is>
       </c>
       <c r="G106">
-        <v>7.7213</v>
+        <v>7.456</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -19100,33 +19100,33 @@
         </is>
       </c>
       <c r="I106">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">KC Concepcion</t>
+          <t xml:space="preserve">Emmett Johnson</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleveland Browns</t>
+          <t xml:space="preserve">Kansas City Chiefs</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D107">
@@ -19137,23 +19137,23 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="G107">
-        <v>7.641</v>
+        <v>7.4535</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I107">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR58</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -19165,17 +19165,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Wilson</t>
+          <t xml:space="preserve">Kaleb Johnson</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D108">
@@ -19186,11 +19186,11 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">RB29</t>
         </is>
       </c>
       <c r="G108">
-        <v>7.632</v>
+        <v>7.425</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -19198,11 +19198,11 @@
         </is>
       </c>
       <c r="I108">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR44</t>
+          <t xml:space="preserve">RB53</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -19214,12 +19214,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyler Allgeier</t>
+          <t xml:space="preserve">Jordan Mason</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arizona Cardinals</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -19235,23 +19235,23 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="G109">
-        <v>7.62325</v>
+        <v>7.389</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I109">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -19263,7 +19263,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rashid Shaheed</t>
+          <t xml:space="preserve">George Holani</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -19273,7 +19273,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D110">
@@ -19284,23 +19284,23 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR45</t>
+          <t xml:space="preserve">RB31</t>
         </is>
       </c>
       <c r="G110">
-        <v>7.601</v>
+        <v>7.37485</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I110">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR63</t>
+          <t xml:space="preserve">RB44</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -19312,17 +19312,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthew Golden</t>
+          <t xml:space="preserve">Blake Corum</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D111">
@@ -19333,23 +19333,23 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR46</t>
+          <t xml:space="preserve">RB32</t>
         </is>
       </c>
       <c r="G111">
-        <v>7.584</v>
+        <v>7.37</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I111">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR54</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -19361,12 +19361,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rico Dowdle</t>
+          <t xml:space="preserve">Kendre Miller</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pittsburgh Steelers</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19382,23 +19382,23 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB27</t>
+          <t xml:space="preserve">RB33</t>
         </is>
       </c>
       <c r="G112">
-        <v>7.58</v>
+        <v>7.3335</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I112">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB47</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -19410,17 +19410,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xavier Worthy</t>
+          <t xml:space="preserve">Braelon Allen</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New York Jets</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D113">
@@ -19431,11 +19431,11 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR47</t>
+          <t xml:space="preserve">RB34</t>
         </is>
       </c>
       <c r="G113">
-        <v>7.485</v>
+        <v>7.3135</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -19443,11 +19443,11 @@
         </is>
       </c>
       <c r="I113">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR59</t>
+          <t xml:space="preserve">RB52</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -19459,12 +19459,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyjae Spears</t>
+          <t xml:space="preserve">Kaelon Black</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennessee Titans</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -19480,11 +19480,11 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">RB35</t>
         </is>
       </c>
       <c r="G114">
-        <v>7.485</v>
+        <v>7.27</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -19492,11 +19492,11 @@
         </is>
       </c>
       <c r="I114">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB55</t>
+          <t xml:space="preserve">RB67</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -19508,12 +19508,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Gainwell</t>
+          <t xml:space="preserve">Woody Marks</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampa Bay Buccaneers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -19529,11 +19529,11 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB29</t>
+          <t xml:space="preserve">RB36</t>
         </is>
       </c>
       <c r="G115">
-        <v>7.456</v>
+        <v>7.258</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -19541,28 +19541,28 @@
         </is>
       </c>
       <c r="I115">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROVISIONAL_AVAILABILITY_REVIEW</t>
+          <t xml:space="preserve">MODEL_RANK</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emmett Johnson</t>
+          <t xml:space="preserve">Tyrone Tracy Jr.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kansas City Chiefs</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -19578,11 +19578,11 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">RB37</t>
         </is>
       </c>
       <c r="G116">
-        <v>7.4535</v>
+        <v>7.238</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -19590,11 +19590,11 @@
         </is>
       </c>
       <c r="I116">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
+          <t xml:space="preserve">RB56</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -19606,7 +19606,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaleb Johnson</t>
+          <t xml:space="preserve">Josh Jacobs</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -19627,11 +19627,11 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB31</t>
+          <t xml:space="preserve">RB38</t>
         </is>
       </c>
       <c r="G117">
-        <v>7.425</v>
+        <v>7.155</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -19639,11 +19639,11 @@
         </is>
       </c>
       <c r="I117">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB53</t>
+          <t xml:space="preserve">RB28</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -19655,12 +19655,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">George Holani</t>
+          <t xml:space="preserve">Jaylen Wright</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19676,11 +19676,11 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB32</t>
+          <t xml:space="preserve">RB39</t>
         </is>
       </c>
       <c r="G118">
-        <v>7.37485</v>
+        <v>7.08335</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -19688,11 +19688,11 @@
         </is>
       </c>
       <c r="I118">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
+          <t xml:space="preserve">RB49</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -19704,12 +19704,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blake Corum</t>
+          <t xml:space="preserve">Jonah Coleman</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -19725,23 +19725,23 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB33</t>
+          <t xml:space="preserve">RB40</t>
         </is>
       </c>
       <c r="G119">
-        <v>7.37</v>
+        <v>7.08</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I119">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">RB48</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -19753,17 +19753,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kendre Miller</t>
+          <t xml:space="preserve">Malik Washington</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D120">
@@ -19774,11 +19774,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB34</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="G120">
-        <v>7.3335</v>
+        <v>7.08</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -19786,11 +19786,11 @@
         </is>
       </c>
       <c r="I120">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">WR67</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -19802,12 +19802,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Braelon Allen</t>
+          <t xml:space="preserve">J.K. Dobbins</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Jets</t>
+          <t xml:space="preserve">Denver Broncos</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -19823,11 +19823,11 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB35</t>
+          <t xml:space="preserve">RB41</t>
         </is>
       </c>
       <c r="G121">
-        <v>7.3135</v>
+        <v>6.998</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -19835,11 +19835,11 @@
         </is>
       </c>
       <c r="I121">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB52</t>
+          <t xml:space="preserve">RB61</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -19851,12 +19851,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaelon Black</t>
+          <t xml:space="preserve">Aaron Jones Sr.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">Minnesota Vikings</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -19872,11 +19872,11 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB36</t>
+          <t xml:space="preserve">RB42</t>
         </is>
       </c>
       <c r="G122">
-        <v>7.27</v>
+        <v>6.885</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -19884,11 +19884,11 @@
         </is>
       </c>
       <c r="I122">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB67</t>
+          <t xml:space="preserve">RB50</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -19900,17 +19900,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woody Marks</t>
+          <t xml:space="preserve">Jalen Nailor</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houston Texans</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D123">
@@ -19921,11 +19921,11 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB37</t>
+          <t xml:space="preserve">WR44</t>
         </is>
       </c>
       <c r="G123">
-        <v>7.258</v>
+        <v>6.88</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -19933,11 +19933,11 @@
         </is>
       </c>
       <c r="I123">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">WR72</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -19949,17 +19949,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrone Tracy Jr.</t>
+          <t xml:space="preserve">Jonnu Smith</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D124">
@@ -19970,23 +19970,23 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB38</t>
+          <t xml:space="preserve">TE18</t>
         </is>
       </c>
       <c r="G124">
-        <v>7.238</v>
+        <v>6.73975</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I124">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB56</t>
+          <t xml:space="preserve">TE26</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -19998,17 +19998,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Jacobs</t>
+          <t xml:space="preserve">Tank Dell</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D125">
@@ -20019,23 +20019,23 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB39</t>
+          <t xml:space="preserve">WR45</t>
         </is>
       </c>
       <c r="G125">
-        <v>7.155</v>
+        <v>6.67</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I125">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB28</t>
+          <t xml:space="preserve">WR74</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -20047,17 +20047,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaylen Wright</t>
+          <t xml:space="preserve">Darnell Mooney</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D126">
@@ -20068,23 +20068,23 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB40</t>
+          <t xml:space="preserve">WR46</t>
         </is>
       </c>
       <c r="G126">
-        <v>7.08335</v>
+        <v>6.595</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I126">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB49</t>
+          <t xml:space="preserve">WR71</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -20096,7 +20096,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malik Washington</t>
+          <t xml:space="preserve">Chris Bell</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -20117,11 +20117,11 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR48</t>
+          <t xml:space="preserve">WR47</t>
         </is>
       </c>
       <c r="G127">
-        <v>7.08</v>
+        <v>6.55025</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -20129,11 +20129,11 @@
         </is>
       </c>
       <c r="I127">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR67</t>
+          <t xml:space="preserve">WR69</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -20145,12 +20145,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">J.K. Dobbins</t>
+          <t xml:space="preserve">Alvin Kamara</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denver Broncos</t>
+          <t xml:space="preserve">New Orleans Saints</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -20166,11 +20166,11 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB41</t>
+          <t xml:space="preserve">RB43</t>
         </is>
       </c>
       <c r="G128">
-        <v>6.998</v>
+        <v>6.401</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -20178,11 +20178,11 @@
         </is>
       </c>
       <c r="I128">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB61</t>
+          <t xml:space="preserve">RB64</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -20194,17 +20194,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Robinson Jr.</t>
+          <t xml:space="preserve">Michael Mayer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atlanta Falcons</t>
+          <t xml:space="preserve">Las Vegas Raiders</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D129">
@@ -20215,23 +20215,23 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB42</t>
+          <t xml:space="preserve">TE19</t>
         </is>
       </c>
       <c r="G129">
-        <v>6.9</v>
+        <v>6.355</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I129">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB58</t>
+          <t xml:space="preserve">TE25</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -20243,32 +20243,36 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Jones Sr.</t>
+          <t xml:space="preserve">A.J. Brown</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minnesota Vikings</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D130">
         <v>7</v>
       </c>
-      <c r="E130">
-        <v>129</v>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB43</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>6.885</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -20276,28 +20280,28 @@
         </is>
       </c>
       <c r="I130">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB50</t>
+          <t xml:space="preserve">WR10</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Nailor</t>
+          <t xml:space="preserve">Alec Pierce</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Indianapolis Colts</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -20308,65 +20312,73 @@
       <c r="D131">
         <v>7</v>
       </c>
-      <c r="E131">
-        <v>130</v>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR49</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>6.88</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I131">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR72</t>
+          <t xml:space="preserve">WR40</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonnu Smith</t>
+          <t xml:space="preserve">Austin Ekeler</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bay Packers</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D132">
         <v>7</v>
       </c>
-      <c r="E132">
-        <v>131</v>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE19</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>6.73975</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -20374,48 +20386,52 @@
         </is>
       </c>
       <c r="I132">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE26</t>
+          <t xml:space="preserve">RB54</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darnell Mooney</t>
+          <t xml:space="preserve">Bhayshul Tuten</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D133">
         <v>7</v>
       </c>
-      <c r="E133">
-        <v>132</v>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR50</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>6.595</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -20423,77 +20439,81 @@
         </is>
       </c>
       <c r="I133">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR71</t>
+          <t xml:space="preserve">RB26</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Bell</t>
+          <t xml:space="preserve">Brenton Strange</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D134">
         <v>7</v>
       </c>
-      <c r="E134">
-        <v>133</v>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
-        </is>
-      </c>
-      <c r="G134">
-        <v>6.55025</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I134">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR69</t>
+          <t xml:space="preserve">TE12</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alvin Kamara</t>
+          <t xml:space="preserve">Brian Robinson Jr.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Orleans Saints</t>
+          <t xml:space="preserve">Atlanta Falcons</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -20504,65 +20524,73 @@
       <c r="D135">
         <v>7</v>
       </c>
-      <c r="E135">
-        <v>134</v>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB44</t>
-        </is>
-      </c>
-      <c r="G135">
-        <v>6.401</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I135">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB64</t>
+          <t xml:space="preserve">RB58</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Mayer</t>
+          <t xml:space="preserve">Brian Thomas Jr.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las Vegas Raiders</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D136">
         <v>7</v>
       </c>
-      <c r="E136">
-        <v>135</v>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE20</t>
-        </is>
-      </c>
-      <c r="G136">
-        <v>6.355</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -20570,82 +20598,86 @@
         </is>
       </c>
       <c r="I136">
-        <v>179</v>
+        <v>43</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE25</t>
+          <t xml:space="preserve">WR23</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zach Charbonnet</t>
+          <t xml:space="preserve">Caleb Williams</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D137">
         <v>7</v>
       </c>
-      <c r="E137">
-        <v>136</v>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB45</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>6.18</v>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I137">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB66</t>
+          <t xml:space="preserve">QB11</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL_RANK</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">A.J. Brown</t>
+          <t xml:space="preserve">Chig Okonkwo</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D138">
@@ -20668,37 +20700,37 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I138">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR10</t>
+          <t xml:space="preserve">TE22</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alec Pierce</t>
+          <t xml:space="preserve">Chris Rodriguez Jr.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indianapolis Colts</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D139">
@@ -20721,37 +20753,37 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I139">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR40</t>
+          <t xml:space="preserve">RB57</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin Ekeler</t>
+          <t xml:space="preserve">Colston Loveland</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D140">
@@ -20774,32 +20806,32 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_ADVERSE_STATUS_REPORTED</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I140">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB54</t>
+          <t xml:space="preserve">TE3</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhayshul Tuten</t>
+          <t xml:space="preserve">Corey Kiner</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -20831,33 +20863,33 @@
         </is>
       </c>
       <c r="I141">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB26</t>
+          <t xml:space="preserve">RB63</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenton Strange</t>
+          <t xml:space="preserve">D'Andre Swift</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Chicago Bears</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D142">
@@ -20884,33 +20916,33 @@
         </is>
       </c>
       <c r="I142">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE12</t>
+          <t xml:space="preserve">RB20</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brian Thomas Jr.</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D143">
@@ -20937,11 +20969,11 @@
         </is>
       </c>
       <c r="I143">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR23</t>
+          <t xml:space="preserve">TE23</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -20953,17 +20985,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caleb Williams</t>
+          <t xml:space="preserve">Davante Adams</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Los Angeles Rams</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D144">
@@ -20986,37 +21018,37 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I144">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB11</t>
+          <t xml:space="preserve">WR51</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chig Okonkwo</t>
+          <t xml:space="preserve">David Montgomery</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D145">
@@ -21039,32 +21071,32 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I145">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE22</t>
+          <t xml:space="preserve">RB19</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Rodriguez Jr.</t>
+          <t xml:space="preserve">De'Von Achane</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">Miami Dolphins</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -21092,37 +21124,37 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I146">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB57</t>
+          <t xml:space="preserve">RB4</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colston Loveland</t>
+          <t xml:space="preserve">Deebo Samuel</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">San Francisco 49ers</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D147">
@@ -21145,37 +21177,37 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I147">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE3</t>
+          <t xml:space="preserve">WR66</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey Kiner</t>
+          <t xml:space="preserve">DeVonta Smith</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D148">
@@ -21198,37 +21230,37 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I148">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB63</t>
+          <t xml:space="preserve">WR9</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">D'Andre Swift</t>
+          <t xml:space="preserve">DJ Moore</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago Bears</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D149">
@@ -21251,37 +21283,37 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">QUESTIONABLE</t>
         </is>
       </c>
       <c r="I149">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB20</t>
+          <t xml:space="preserve">WR17</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">Dontayvion Wicks</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D150">
@@ -21304,37 +21336,37 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I150">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE23</t>
+          <t xml:space="preserve">WR41</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Davante Adams</t>
+          <t xml:space="preserve">Drake Maye</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los Angeles Rams</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D151">
@@ -21357,37 +21389,37 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I151">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR51</t>
+          <t xml:space="preserve">QB3</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">De'Von Achane</t>
+          <t xml:space="preserve">Emeka Egbuka</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miami Dolphins</t>
+          <t xml:space="preserve">Tampa Bay Buccaneers</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D152">
@@ -21410,15 +21442,15 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">OUT</t>
         </is>
       </c>
       <c r="I152">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB4</t>
+          <t xml:space="preserve">WR19</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -21430,17 +21462,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deebo Samuel</t>
+          <t xml:space="preserve">Hunter Henry</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Francisco 49ers</t>
+          <t xml:space="preserve">New England Patriots</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D153">
@@ -21463,37 +21495,37 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUT</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I153">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR66</t>
+          <t xml:space="preserve">TE17</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ Moore</t>
+          <t xml:space="preserve">Isiah Pacheco</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Detroit Lions</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D154">
@@ -21516,37 +21548,37 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUESTIONABLE</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I154">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR17</t>
+          <t xml:space="preserve">RB65</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drake Maye</t>
+          <t xml:space="preserve">Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D155">
@@ -21569,37 +21601,37 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I155">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB3</t>
+          <t xml:space="preserve">RB25</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hunter Henry</t>
+          <t xml:space="preserve">Jadarian Price</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">New England Patriots</t>
+          <t xml:space="preserve">Seattle Seahawks</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE</t>
+          <t xml:space="preserve">RB</t>
         </is>
       </c>
       <c r="D156">
@@ -21622,37 +21654,37 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I156">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE17</t>
+          <t xml:space="preserve">RB30</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAME_STARTED_NO_ORIGINAL_WEEKLY_RANK</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isiah Pacheco</t>
+          <t xml:space="preserve">Jakobi Meyers</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detroit Lions</t>
+          <t xml:space="preserve">Jacksonville Jaguars</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D157">
@@ -21675,37 +21707,37 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I157">
-        <v>189</v>
+        <v>95</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB65</t>
+          <t xml:space="preserve">WR43</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacory Croskey-Merritt</t>
+          <t xml:space="preserve">Jalen Hurts</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Washington Commanders</t>
+          <t xml:space="preserve">Philadelphia Eagles</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D158">
@@ -21732,28 +21764,28 @@
         </is>
       </c>
       <c r="I158">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB25</t>
+          <t xml:space="preserve">QB14</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jadarian Price</t>
+          <t xml:space="preserve">James Cook</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seattle Seahawks</t>
+          <t xml:space="preserve">Buffalo Bills</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -21781,37 +21813,37 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I159">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB30</t>
+          <t xml:space="preserve">RB6</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jakobi Meyers</t>
+          <t xml:space="preserve">Jaxson Dart</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jacksonville Jaguars</t>
+          <t xml:space="preserve">New York Giants</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR</t>
+          <t xml:space="preserve">QB</t>
         </is>
       </c>
       <c r="D160">
@@ -21834,32 +21866,32 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I160">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">WR43</t>
+          <t xml:space="preserve">QB17</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jalen Hurts</t>
+          <t xml:space="preserve">Jayden Daniels</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philadelphia Eagles</t>
+          <t xml:space="preserve">Washington Commanders</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -21887,37 +21919,37 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">INJURED_RESERVE</t>
+          <t xml:space="preserve">UNKNOWN</t>
         </is>
       </c>
       <c r="I161">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB14</t>
+          <t xml:space="preserve">QB12</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
+          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">James Cook</t>
+          <t xml:space="preserve">Jayden Higgins</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buffalo Bills</t>
+          <t xml:space="preserve">Houston Texans</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D162">
@@ -21940,37 +21972,37 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNKNOWN</t>
+          <t xml:space="preserve">INJURED_RESERVE</t>
         </is>
       </c>
       <c r="I162">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">RB6</t>
+          <t xml:space="preserve">WR75</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO_CURRENT_WEEK_GAME</t>
+          <t xml:space="preserve">NOT_EXPECTED_TO_PLAY</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxson Dart</t>
+          <t xml:space="preserve">Jayden Reed</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">New York Giants</t>
+          <t xml:space="preserve">Green Bay Packers</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB</t>
+          <t xml:space="preserve">WR</t>
         </is>
       </c>
       <c r="D163">
@@ -21997,11 +22029,11 @@
         </is>
       </c>
       <c r="I163">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">QB17</t>